--- a/Results/Model bridging outputs.xlsx
+++ b/Results/Model bridging outputs.xlsx
@@ -353,56 +353,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>2023 Rceattle</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean L@A</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean W@A</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean A@AE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean A@AC</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean L@A W@A</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean L@A W@A A@AE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean L@A W@A A@AC</t>
         </is>
@@ -410,2369 +415,2591 @@
     </row>
     <row r="2">
       <c r="A2">
+        <v>1977</v>
+      </c>
+      <c r="B2">
         <v>1270992.078794064</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>1281684.591266106</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>1504086.90315226</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>1525787.029938394</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>1453981.372054342</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1580986.477865727</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1576220.135698695</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>1476818.106513873</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>1545163.474964341</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>1540897.742383468</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
+        <v>1978</v>
+      </c>
+      <c r="B3">
         <v>1260760.248169834</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>1270856.494622041</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1499000.244437364</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>1519083.290344778</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>1446900.441687675</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1574842.808077489</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1570073.600760674</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1468757.612826034</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>1536740.259360753</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>1532458.665515638</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
+        <v>1979</v>
+      </c>
+      <c r="B4">
         <v>1257163.680528443</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>1266179.952299369</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>1497665.074791715</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>1515478.809337291</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>1443813.035543105</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>1571885.272473956</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>1567172.192944205</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>1463961.179357795</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>1531210.460152539</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>1526918.273645719</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
+        <v>1980</v>
+      </c>
+      <c r="B5">
         <v>1255661.26115658</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>1263497.063998782</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>1499911.297089376</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>1515017.776184112</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>1444357.089753479</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>1572081.075847748</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>1567340.383950214</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>1462183.862802921</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>1528302.22445761</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>1523998.573920624</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
+        <v>1981</v>
+      </c>
+      <c r="B6">
         <v>1250168.427621922</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>1257076.682510897</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>1504261.676172229</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>1516594.295199407</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>1447128.55899397</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>1573978.662225274</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>1569122.758190677</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>1462243.80123103</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>1526872.450549466</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>1522512.618115389</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
+        <v>1982</v>
+      </c>
+      <c r="B7">
         <v>1241625.29840498</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>1248083.10288029</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>1511028.133159342</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>1521160.56866604</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>1452517.858541909</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>1577838.930772227</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>1573102.740773611</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>1464946.93085072</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>1527751.569689834</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>1523346.810423736</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
+        <v>1983</v>
+      </c>
+      <c r="B8">
         <v>1237395.659387482</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>1243600.953673358</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>1522049.185877231</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>1531298.833539293</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>1462428.904404929</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>1585441.677104134</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1580844.056861436</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>1472824.879504027</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>1533344.870246066</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>1528941.400116005</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
+        <v>1984</v>
+      </c>
+      <c r="B9">
         <v>1241289.964758538</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>1247181.534279157</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>1532514.985721695</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>1542180.039205052</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>1471718.565718016</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>1591794.264877846</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>1587545.079188583</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>1481135.340921927</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>1538626.910851453</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>1534299.301309814</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
+        <v>1985</v>
+      </c>
+      <c r="B10">
         <v>1279454.009924183</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>1285125.336908981</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>1549216.123652715</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>1559704.514751705</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>1485649.808703877</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>1605447.196180705</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>1601401.702553765</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>1495142.129025163</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>1549182.201119072</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>1544943.344326942</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
+        <v>1986</v>
+      </c>
+      <c r="B11">
         <v>1332261.800735511</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>1337276.710874633</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>1571917.880527588</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>1582603.934494323</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>1504057.627150749</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>1623081.922686318</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>1618992.178215082</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>1514067.165166952</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>1564174.30107424</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>1559973.87559151</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
+        <v>1987</v>
+      </c>
+      <c r="B12">
         <v>1394409.416988673</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>1398990.355990305</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>1600813.091117056</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>1610817.000448748</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>1526664.399962401</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>1646138.981756186</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>1642364.58342729</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>1536884.602582023</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>1582431.408493605</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>1578317.423225933</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
+        <v>1988</v>
+      </c>
+      <c r="B13">
         <v>1460896.40191376</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>1465654.616489346</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>1633157.224682642</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>1641599.322117365</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>1551022.505731651</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>1671207.009515726</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>1667384.464868827</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>1560610.907264992</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>1600701.010251107</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>1596678.153895752</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
+        <v>1989</v>
+      </c>
+      <c r="B14">
         <v>1527585.868418448</v>
       </c>
-      <c r="B14">
+      <c r="C14">
         <v>1531826.006929347</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>1663407.331125254</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>1670325.194054578</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>1579381.554661069</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>1694526.426524248</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>1690333.717850256</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>1587659.84232718</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>1621641.128553812</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>1617597.046606912</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
+        <v>1990</v>
+      </c>
+      <c r="B15">
         <v>1584612.966891939</v>
       </c>
-      <c r="B15">
+      <c r="C15">
         <v>1587878.413829526</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>1690584.084220447</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>1696664.878336456</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>1610178.112844399</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>1715952.311971258</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>1711382.946418257</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>1617107.522503872</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>1645071.533115859</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>1640838.066585913</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
+        <v>1991</v>
+      </c>
+      <c r="B16">
         <v>1635172.561065602</v>
       </c>
-      <c r="B16">
+      <c r="C16">
         <v>1637605.663476845</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>1711361.676988079</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>1717990.977736311</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>1633114.415591432</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>1732141.369235866</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>1727112.672678341</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>1639285.495502072</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>1661990.720728719</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>1657434.090097579</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
+        <v>1992</v>
+      </c>
+      <c r="B17">
         <v>1669868.105105132</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>1670352.700684899</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>1720174.452767116</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>1728678.520302491</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>1643615.308469975</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>1736345.026421823</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>1730627.714186476</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>1650034.028927599</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>1668150.304258755</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>1663150.867575289</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
+        <v>1993</v>
+      </c>
+      <c r="B18">
         <v>1683696.649711254</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>1682572.699718705</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>1715852.048868727</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>1726453.892183398</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>1645709.668253065</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>1729431.736092618</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>1723324.725879754</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>1653361.77708305</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>1667831.119733718</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>1662388.63861153</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
+        <v>1994</v>
+      </c>
+      <c r="B19">
         <v>1689876.9430268</v>
       </c>
-      <c r="B19">
+      <c r="C19">
         <v>1687325.065500527</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>1708606.323510506</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>1721479.290652189</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>1645324.609606515</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>1720736.531874092</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>1714509.022361486</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>1654974.131609446</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>1666989.077539861</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>1661252.556716889</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
+        <v>1995</v>
+      </c>
+      <c r="B20">
         <v>1686742.305265364</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>1683229.627046005</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>1695893.014214189</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>1711152.332085483</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>1636186.522494178</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>1708368.464874085</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>1701469.156449874</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>1648168.821542741</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>1659105.607028386</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>1653065.688606462</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
+        <v>1996</v>
+      </c>
+      <c r="B21">
         <v>1680825.31298585</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>1676463.646040059</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>1685017.7215131</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>1702318.631006128</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>1628915.81537478</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>1698080.83334685</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>1691090.081492912</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>1643313.912584278</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>1654099.202598095</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>1647796.712088366</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
+        <v>1997</v>
+      </c>
+      <c r="B22">
         <v>1672755.73121383</v>
       </c>
-      <c r="B22">
+      <c r="C22">
         <v>1667777.844718358</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>1673319.852322756</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>1690915.168500509</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>1617295.310623834</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>1688249.616328885</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>1680372.712463464</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>1633289.392660324</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>1644522.130944718</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>1637839.618514184</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
+        <v>1998</v>
+      </c>
+      <c r="B23">
         <v>1689755.183095852</v>
       </c>
-      <c r="B23">
+      <c r="C23">
         <v>1684395.407988582</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>1684165.237357176</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>1697516.479002975</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>1618714.862720867</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>1698596.87537249</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>1690463.885655329</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>1634019.057938113</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>1645705.819997711</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>1638616.856239522</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
+        <v>1999</v>
+      </c>
+      <c r="B24">
         <v>1713839.015574609</v>
       </c>
-      <c r="B24">
+      <c r="C24">
         <v>1708630.511913224</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>1706518.683792678</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>1715090.750733286</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>1633528.484898746</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>1722606.847634887</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>1713666.923403589</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>1645690.461405743</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>1658041.91966047</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>1650425.109251128</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
+        <v>2000</v>
+      </c>
+      <c r="B25">
         <v>1796577.248254717</v>
       </c>
-      <c r="B25">
+      <c r="C25">
         <v>1788191.286696026</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>1770208.184428651</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>1775016.68484178</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>1665413.943775549</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>1775242.084214867</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>1765976.407948329</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>1673321.283160484</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>1683046.605390835</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>1674860.377223497</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
+        <v>2001</v>
+      </c>
+      <c r="B26">
         <v>1840428.741117157</v>
       </c>
-      <c r="B26">
+      <c r="C26">
         <v>1830204.173689626</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>1806863.371380031</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>1808534.845349399</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>1702965.177343606</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>1807054.240619774</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>1797719.770650114</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>1706684.929745869</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>1711276.442209971</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>1702686.406981682</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
+        <v>2002</v>
+      </c>
+      <c r="B27">
         <v>1882412.330821825</v>
       </c>
-      <c r="B27">
+      <c r="C27">
         <v>1869715.534904175</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>1841629.81916084</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>1839594.82758464</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>1746512.206965116</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>1836774.232787203</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>1827613.484414445</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>1746442.284330202</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>1745432.713801882</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>1736718.811109076</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
+        <v>2003</v>
+      </c>
+      <c r="B28">
         <v>1907552.439357017</v>
       </c>
-      <c r="B28">
+      <c r="C28">
         <v>1893340.308934402</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>1862649.101368084</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>1856920.179539763</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>1780122.576354178</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>1855885.016716788</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>1846555.536550738</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>1776386.450068044</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>1771162.650219527</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>1762442.761140957</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
+        <v>2004</v>
+      </c>
+      <c r="B29">
         <v>1914529.21530383</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>1897255.979948272</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>1864763.599534484</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>1856243.995714896</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>1792384.763499172</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>1855379.344028385</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>1846389.476976266</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>1785064.54916834</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>1777009.60352657</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>1768417.328544835</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
+        <v>2005</v>
+      </c>
+      <c r="B30">
         <v>1930183.090111142</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>1908859.329166343</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>1873920.781377375</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>1864397.729750885</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>1808452.650868334</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>1862894.062118214</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>1853781.621696417</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>1798657.19051268</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>1788765.080867093</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>1780291.068708601</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
+        <v>2006</v>
+      </c>
+      <c r="B31">
         <v>1932244.218389702</v>
       </c>
-      <c r="B31">
+      <c r="C31">
         <v>1905865.251304342</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>1869612.269094626</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>1861635.855833285</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>1809218.287064321</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>1857582.266539839</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>1848958.705588775</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>1798715.746137056</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>1787624.269963574</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>1779380.016047775</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
+        <v>2007</v>
+      </c>
+      <c r="B32">
         <v>1905435.015971922</v>
       </c>
-      <c r="B32">
+      <c r="C32">
         <v>1874452.587898443</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>1840511.260670429</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>1835924.191206905</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>1790042.303175352</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>1828885.437383896</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>1820677.204366626</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>1780881.292240382</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>1769372.255181461</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>1761493.122117134</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
+        <v>2008</v>
+      </c>
+      <c r="B33">
         <v>1869900.081442137</v>
       </c>
-      <c r="B33">
+      <c r="C33">
         <v>1833848.988781691</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>1802829.313133263</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>1802961.671086474</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>1760805.058020875</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>1792810.142771489</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>1785007.928291604</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>1755003.492783483</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>1743970.529143021</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>1736529.938454762</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
+        <v>2009</v>
+      </c>
+      <c r="B34">
         <v>1812152.837832744</v>
       </c>
-      <c r="B34">
+      <c r="C34">
         <v>1772011.430039798</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>1746285.714253421</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>1750623.991041695</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>1714294.366510733</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>1739938.208122981</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>1732439.630011292</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>1712899.93650527</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>1703675.077030068</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>1696690.279267278</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
+        <v>2010</v>
+      </c>
+      <c r="B35">
         <v>1746820.065129069</v>
       </c>
-      <c r="B35">
+      <c r="C35">
         <v>1703275.031899427</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>1684842.912232699</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>1691774.324864715</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>1660382.358677209</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>1682950.951644951</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>1675851.067304496</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>1663187.035705631</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>1657102.198810226</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>1650578.360792035</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
+        <v>2011</v>
+      </c>
+      <c r="B36">
         <v>1682684.196537743</v>
       </c>
-      <c r="B36">
+      <c r="C36">
         <v>1635522.781699583</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>1623190.474159648</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>1630430.748180967</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>1599183.777281201</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>1626322.781715876</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>1619437.384098002</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>1604741.106116495</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>1602875.557881142</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>1596760.576835921</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
+        <v>2012</v>
+      </c>
+      <c r="B37">
         <v>1616567.954201521</v>
       </c>
-      <c r="B37">
+      <c r="C37">
         <v>1565671.119195798</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>1558841.175411629</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>1565383.897371504</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>1529418.934270248</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>1565251.749419146</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>1558756.128732306</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>1535852.631763204</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>1538382.584547921</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>1532634.70804703</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
+        <v>2013</v>
+      </c>
+      <c r="B38">
         <v>1569036.083339877</v>
       </c>
-      <c r="B38">
+      <c r="C38">
         <v>1515925.272778413</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>1512944.403129734</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>1518703.067347227</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>1474520.541182145</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>1522837.74170199</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>1516596.790178872</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>1480757.297599907</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>1487468.551576475</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>1482028.71713274</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
+        <v>2014</v>
+      </c>
+      <c r="B39">
         <v>1518153.766470484</v>
       </c>
-      <c r="B39">
+      <c r="C39">
         <v>1466492.881840924</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>1467917.227391018</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>1472237.3444704</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>1424274.824231292</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>1481108.420469707</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>1475242.699715263</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>1429656.214283217</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>1440152.617852858</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>1434983.722906676</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
+        <v>2015</v>
+      </c>
+      <c r="B40">
         <v>1452980.941618328</v>
       </c>
-      <c r="B40">
+      <c r="C40">
         <v>1407408.586749829</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>1412640.279900028</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>1414695.019955705</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>1365434.537082157</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>1429775.463988561</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>1423808.295964359</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>1369091.890876026</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>1383265.527262751</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>1378217.413092992</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
+        <v>2016</v>
+      </c>
+      <c r="B41">
         <v>1411014.202769245</v>
       </c>
-      <c r="B41">
+      <c r="C41">
         <v>1379023.49982292</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>1386717.260794467</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>1386410.39387775</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>1333414.90010482</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>1406142.6494514</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>1400229.469534991</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>1334939.868835353</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>1352403.452657085</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>1347366.240499512</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
+        <v>2017</v>
+      </c>
+      <c r="B42">
         <v>1375168.034000436</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>1365307.357326655</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>1372672.791599431</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>1372018.549129233</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>1311517.802862228</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>1393742.189392856</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>1387420.001649989</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>1311268.573685091</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>1331230.34338734</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>1325957.732793714</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
+        <v>2018</v>
+      </c>
+      <c r="B43">
         <v>1343703.290737016</v>
       </c>
-      <c r="B43">
+      <c r="C43">
         <v>1356984.198496754</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>1362710.838988438</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>1364456.843128681</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>1294891.956593087</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>1383506.883291569</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>1377043.532055517</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>1294373.935741077</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>1315313.753356518</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>1309701.638912784</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
+        <v>2019</v>
+      </c>
+      <c r="B44">
         <v>1320974.401836435</v>
       </c>
-      <c r="B44">
+      <c r="C44">
         <v>1354614.405499577</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>1360779.717944511</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>1366153.850097126</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>1295522.886404081</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>1382964.026198161</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>1376276.425141697</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>1296975.311432145</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>1318072.007029374</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>1312092.760539993</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
+        <v>2020</v>
+      </c>
+      <c r="B45">
         <v>1300486.723581266</v>
       </c>
-      <c r="B45">
+      <c r="C45">
         <v>1345157.636044825</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>1353055.282065594</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>1362039.317736077</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>1293745.035117925</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>1376543.382396521</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>1369658.923845417</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>1298487.211083913</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>1319564.09977372</v>
       </c>
-      <c r="J45">
+      <c r="K45">
         <v>1313279.193563012</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
+        <v>2021</v>
+      </c>
+      <c r="B46">
         <v>1283800.329738885</v>
       </c>
-      <c r="B46">
+      <c r="C46">
         <v>1330983.566537772</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>1343841.983908598</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>1355468.961435849</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>1293492.429261113</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>1371033.237045661</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>1363989.724436381</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>1301728.67574062</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>1324098.736010588</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>1317566.226764019</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
+        <v>2022</v>
+      </c>
+      <c r="B47">
         <v>1283070.791689515</v>
       </c>
-      <c r="B47">
+      <c r="C47">
         <v>1327647.918195144</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>1347275.574238896</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>1360461.464273582</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>1302969.981186865</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>1378460.163933877</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>1371284.522047541</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>1314278.979719842</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>1338965.942013435</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>1332233.989027495</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
+        <v>2023</v>
+      </c>
+      <c r="B48">
         <v>1282813.952124937</v>
       </c>
-      <c r="B48">
+      <c r="C48">
         <v>1320591.404550668</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>1349519.556194983</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>1363611.383971118</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>1308691.862023163</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>1384631.196330645</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>1377559.781046343</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>1322199.615810691</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>1350014.145260967</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>1343188.703742903</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
+        <v>2024</v>
+      </c>
+      <c r="B49">
         <v>1293552.717777698</v>
       </c>
-      <c r="B49">
+      <c r="C49">
         <v>1317504.07039234</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>1356964.716590226</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>1371637.206598587</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>1316652.720313843</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>1395446.723088165</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>1388503.799361708</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>1331592.16287047</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <v>1362719.787270075</v>
       </c>
-      <c r="J49">
+      <c r="K49">
         <v>1355932.50219855</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
+        <v>2025</v>
+      </c>
+      <c r="B50">
         <v>1318147.47092542</v>
       </c>
-      <c r="B50">
+      <c r="C50">
         <v>1312868.618159466</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>1360110.807073697</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>1374881.216731442</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>1317060.888952621</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>1400690.828012738</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>1393829.367355183</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>1332592.560874612</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>1366678.020078369</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>1359973.489125087</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
+        <v>2026</v>
+      </c>
+      <c r="B51">
         <v>1345402.446141205</v>
       </c>
-      <c r="B51">
+      <c r="C51">
         <v>1332460.394947425</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>1385626.227713827</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>1400533.848824689</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>1339504.033585215</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>1427313.192779641</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>1420574.703299911</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>1355473.933341263</v>
       </c>
-      <c r="I51">
+      <c r="J51">
         <v>1391664.906841211</v>
       </c>
-      <c r="J51">
+      <c r="K51">
         <v>1385092.226454242</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
+        <v>2027</v>
+      </c>
+      <c r="B52">
         <v>1373400.85586205</v>
       </c>
-      <c r="B52">
+      <c r="C52">
         <v>1354691.877058831</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>1412050.312478997</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>1427052.557096075</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>1363598.100626414</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>1453975.042676097</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>1447306.220151088</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>1379857.570055158</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>1417185.061603407</v>
       </c>
-      <c r="J52">
+      <c r="K52">
         <v>1410725.352469865</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
+        <v>2028</v>
+      </c>
+      <c r="B53">
         <v>1402285.007272857</v>
       </c>
-      <c r="B53">
+      <c r="C53">
         <v>1379488.760394823</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>1439221.583013566</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>1454282.187383472</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>1389004.377143802</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>1480666.474743379</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>1474049.346956566</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>1405442.977227173</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>1443012.130843956</v>
       </c>
-      <c r="J53">
+      <c r="K53">
         <v>1436653.590106123</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
+        <v>2029</v>
+      </c>
+      <c r="B54">
         <v>1430398.92426906</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <v>1405078.606018007</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>1465913.377767833</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>1480951.356449856</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>1414697.414265834</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>1506396.996589872</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>1499810.116618858</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>1431216.462209982</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>1468325.81125503</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>1462048.848675905</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
+        <v>2030</v>
+      </c>
+      <c r="B55">
         <v>1457719.382269657</v>
       </c>
-      <c r="B55">
+      <c r="C55">
         <v>1431009.287986596</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>1491880.898506762</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>1506855.862804561</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>1440050.355111224</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>1530987.588284003</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>1524428.732287201</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>1456591.447051275</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>1492688.642562954</v>
       </c>
-      <c r="J55">
+      <c r="K55">
         <v>1486479.067868928</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
+        <v>2031</v>
+      </c>
+      <c r="B56">
         <v>1484166.390925437</v>
       </c>
-      <c r="B56">
+      <c r="C56">
         <v>1456861.840451044</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <v>1516893.400927806</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>1531796.119153213</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>1464499.563517853</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>1554405.298103259</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>1547850.153949961</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>1481035.10591112</v>
       </c>
-      <c r="I56">
+      <c r="J56">
         <v>1515773.054756401</v>
       </c>
-      <c r="J56">
+      <c r="K56">
         <v>1509609.585639154</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
+        <v>2032</v>
+      </c>
+      <c r="B57">
         <v>1508914.861257694</v>
       </c>
-      <c r="B57">
+      <c r="C57">
         <v>1481674.517374607</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>1540379.877481796</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>1555323.133111032</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>1487454.775785225</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>1576073.919895494</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>1569536.078658976</v>
       </c>
-      <c r="H57">
+      <c r="I57">
         <v>1504015.868482961</v>
       </c>
-      <c r="I57">
+      <c r="J57">
         <v>1537151.60840371</v>
       </c>
-      <c r="J57">
+      <c r="K57">
         <v>1531028.284531349</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
+        <v>2033</v>
+      </c>
+      <c r="B58">
         <v>1531590.178908889</v>
       </c>
-      <c r="B58">
+      <c r="C58">
         <v>1504982.948768344</v>
       </c>
-      <c r="C58">
+      <c r="D58">
         <v>1562020.272407891</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>1577068.391799484</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>1508578.577620224</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <v>1596001.233779117</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>1589454.334525829</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>1525174.555866813</v>
       </c>
-      <c r="I58">
+      <c r="J58">
         <v>1556670.22005186</v>
       </c>
-      <c r="J58">
+      <c r="K58">
         <v>1550568.353123055</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
+        <v>2034</v>
+      </c>
+      <c r="B59">
         <v>1551304.352683701</v>
       </c>
-      <c r="B59">
+      <c r="C59">
         <v>1525813.015892987</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <v>1581185.835036974</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>1596306.358465077</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>1527529.974597477</v>
       </c>
-      <c r="F59">
+      <c r="G59">
         <v>1613497.618552247</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>1606953.984045807</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>1544131.947801822</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>1573982.25134761</v>
       </c>
-      <c r="J59">
+      <c r="K59">
         <v>1567902.245406768</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
+        <v>2035</v>
+      </c>
+      <c r="B60">
         <v>1569049.919588532</v>
       </c>
-      <c r="B60">
+      <c r="C60">
         <v>1544902.972877049</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>1598464.627621733</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>1613640.590718476</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>1544512.422136717</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <v>1629223.69380236</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>1622646.638444453</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>1561107.481255099</v>
       </c>
-      <c r="I60">
+      <c r="J60">
         <v>1589386.290426479</v>
       </c>
-      <c r="J60">
+      <c r="K60">
         <v>1583308.430593964</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
+        <v>2036</v>
+      </c>
+      <c r="B61">
         <v>1585206.769125601</v>
       </c>
-      <c r="B61">
+      <c r="C61">
         <v>1562637.272034851</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>1614299.013100121</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <v>1629545.194532172</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>1559702.101361805</v>
       </c>
-      <c r="F61">
+      <c r="G61">
         <v>1643448.84143742</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <v>1636871.584581652</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>1576297.491308474</v>
       </c>
-      <c r="I61">
+      <c r="J61">
         <v>1603045.169254379</v>
       </c>
-      <c r="J61">
+      <c r="K61">
         <v>1596977.303648572</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
+        <v>2037</v>
+      </c>
+      <c r="B62">
         <v>1599658.051104954</v>
       </c>
-      <c r="B62">
+      <c r="C62">
         <v>1578715.491355019</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>1628455.859716931</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>1643909.714838742</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>1573037.081441526</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>1656166.562836091</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>1649559.619152973</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>1589688.761773818</v>
       </c>
-      <c r="I62">
+      <c r="J62">
         <v>1615038.318603355</v>
       </c>
-      <c r="J62">
+      <c r="K62">
         <v>1608965.827441992</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
+        <v>2038</v>
+      </c>
+      <c r="B63">
         <v>1612582.06900956</v>
       </c>
-      <c r="B63">
+      <c r="C63">
         <v>1592671.953094701</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>1640707.91791781</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <v>1656418.251521022</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <v>1584486.665295081</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>1667053.841215442</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>1660456.931041155</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>1601203.251839947</v>
       </c>
-      <c r="I63">
+      <c r="J63">
         <v>1625265.87286171</v>
       </c>
-      <c r="J63">
+      <c r="K63">
         <v>1619206.375600104</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
+        <v>2039</v>
+      </c>
+      <c r="B64">
         <v>1623105.932015176</v>
       </c>
-      <c r="B64">
+      <c r="C64">
         <v>1603915.355469722</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>1650577.836013457</v>
       </c>
-      <c r="D64">
+      <c r="E64">
         <v>1666369.442723598</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>1594013.735541515</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>1675909.193709417</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>1669308.202112075</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>1610708.508548449</v>
       </c>
-      <c r="I64">
+      <c r="J64">
         <v>1633729.808963435</v>
       </c>
-      <c r="J64">
+      <c r="K64">
         <v>1627674.263441846</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
+        <v>2040</v>
+      </c>
+      <c r="B65">
         <v>1632471.811536468</v>
       </c>
-      <c r="B65">
+      <c r="C65">
         <v>1613626.017956271</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>1659045.264133574</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>1674808.252204879</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>1602172.956059813</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>1683423.639097008</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>1676814.612244872</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>1618800.718059263</v>
       </c>
-      <c r="I65">
+      <c r="J65">
         <v>1640879.804012458</v>
       </c>
-      <c r="J65">
+      <c r="K65">
         <v>1634823.939516905</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
+        <v>2041</v>
+      </c>
+      <c r="B66">
         <v>1640587.051066677</v>
       </c>
-      <c r="B66">
+      <c r="C66">
         <v>1622206.75273764</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>1666435.463740338</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>1682120.749356627</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>1609202.888985764</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>1689990.444110586</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>1683377.164049496</v>
       </c>
-      <c r="H66">
+      <c r="I66">
         <v>1625752.12240824</v>
       </c>
-      <c r="I66">
+      <c r="J66">
         <v>1647006.606786146</v>
       </c>
-      <c r="J66">
+      <c r="K66">
         <v>1640950.360157589</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
+        <v>2042</v>
+      </c>
+      <c r="B67">
         <v>1647502.656848007</v>
       </c>
-      <c r="B67">
+      <c r="C67">
         <v>1629935.711848536</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>1673074.196822292</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>1688678.793657158</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>1615307.936915629</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>1695829.548788959</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>1689211.55318297</v>
       </c>
-      <c r="H67">
+      <c r="I67">
         <v>1631788.580695271</v>
       </c>
-      <c r="I67">
+      <c r="J67">
         <v>1652291.408251481</v>
       </c>
-      <c r="J67">
+      <c r="K67">
         <v>1646232.797818531</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
+        <v>2043</v>
+      </c>
+      <c r="B68">
         <v>1653379.218273162</v>
       </c>
-      <c r="B68">
+      <c r="C68">
         <v>1636659.818499878</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>1678840.517618298</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>1694412.644092173</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>1620505.259463834</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>1700838.141110142</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>1694230.941575968</v>
       </c>
-      <c r="H68">
+      <c r="I68">
         <v>1636946.403682351</v>
       </c>
-      <c r="I68">
+      <c r="J68">
         <v>1656774.673979582</v>
       </c>
-      <c r="J68">
+      <c r="K68">
         <v>1650719.402641219</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
+        <v>2044</v>
+      </c>
+      <c r="B69">
         <v>1658786.438258412</v>
       </c>
-      <c r="B69">
+      <c r="C69">
         <v>1642626.044159678</v>
       </c>
-      <c r="C69">
+      <c r="D69">
         <v>1683864.970188591</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>1699430.569127376</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>1624922.616278231</v>
       </c>
-      <c r="F69">
+      <c r="G69">
         <v>1705192.601928136</v>
       </c>
-      <c r="G69">
+      <c r="H69">
         <v>1698574.682319202</v>
       </c>
-      <c r="H69">
+      <c r="I69">
         <v>1641340.181397992</v>
       </c>
-      <c r="I69">
+      <c r="J69">
         <v>1660584.719506729</v>
       </c>
-      <c r="J69">
+      <c r="K69">
         <v>1654523.675913993</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
+        <v>2045</v>
+      </c>
+      <c r="B70">
         <v>1663204.427540736</v>
       </c>
-      <c r="B70">
+      <c r="C70">
         <v>1648155.726597074</v>
       </c>
-      <c r="C70">
+      <c r="D70">
         <v>1688281.142921372</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>1703840.484834897</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>1628673.334450709</v>
       </c>
-      <c r="F70">
+      <c r="G70">
         <v>1708970.172496852</v>
       </c>
-      <c r="G70">
+      <c r="H70">
         <v>1702340.800628921</v>
       </c>
-      <c r="H70">
+      <c r="I70">
         <v>1645071.038082518</v>
       </c>
-      <c r="I70">
+      <c r="J70">
         <v>1663798.948483688</v>
       </c>
-      <c r="J70">
+      <c r="K70">
         <v>1657732.147912338</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
+        <v>2046</v>
+      </c>
+      <c r="B71">
         <v>1666815.181115526</v>
       </c>
-      <c r="B71">
+      <c r="C71">
         <v>1652672.743036455</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>1691889.652815183</v>
       </c>
-      <c r="D71">
+      <c r="E71">
         <v>1707443.935819636</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>1631738.354177758</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>1712057.267835197</v>
       </c>
-      <c r="G71">
+      <c r="H71">
         <v>1705418.567106208</v>
       </c>
-      <c r="H71">
+      <c r="I71">
         <v>1648119.877152602</v>
       </c>
-      <c r="I71">
+      <c r="J71">
         <v>1666425.938158198</v>
       </c>
-      <c r="J71">
+      <c r="K71">
         <v>1660354.457113287</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
+        <v>2047</v>
+      </c>
+      <c r="B72">
         <v>1669766.913069358</v>
       </c>
-      <c r="B72">
+      <c r="C72">
         <v>1656363.701759709</v>
       </c>
-      <c r="C72">
+      <c r="D72">
         <v>1694839.014761047</v>
       </c>
-      <c r="D72">
+      <c r="E72">
         <v>1710389.200917635</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>1634243.686845085</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>1714580.738419822</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>1707934.433306772</v>
       </c>
-      <c r="H72">
+      <c r="I72">
         <v>1650612.018983929</v>
       </c>
-      <c r="I72">
+      <c r="J72">
         <v>1668573.494929403</v>
       </c>
-      <c r="J72">
+      <c r="K72">
         <v>1662498.205050596</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
+        <v>2048</v>
+      </c>
+      <c r="B73">
         <v>1672180.413556404</v>
       </c>
-      <c r="B73">
+      <c r="C73">
         <v>1659380.486048513</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>1697250.199224613</v>
       </c>
-      <c r="D73">
+      <c r="E73">
         <v>1712797.062902596</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>1636291.995287633</v>
       </c>
-      <c r="F73">
+      <c r="G73">
         <v>1716643.941987599</v>
       </c>
-      <c r="G73">
+      <c r="H73">
         <v>1709991.4344972</v>
       </c>
-      <c r="H73">
+      <c r="I73">
         <v>1652649.567685329</v>
       </c>
-      <c r="I73">
+      <c r="J73">
         <v>1670329.482186053</v>
       </c>
-      <c r="J73">
+      <c r="K73">
         <v>1664251.090256252</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
+        <v>2049</v>
+      </c>
+      <c r="B74">
         <v>1674154.184484412</v>
       </c>
-      <c r="B74">
+      <c r="C74">
         <v>1661846.814143227</v>
       </c>
-      <c r="C74">
+      <c r="D74">
         <v>1699221.80925446</v>
       </c>
-      <c r="D74">
+      <c r="E74">
         <v>1714765.97508153</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>1637966.975757514</v>
       </c>
-      <c r="F74">
+      <c r="G74">
         <v>1718331.149303975</v>
       </c>
-      <c r="G74">
+      <c r="H74">
         <v>1711673.580342996</v>
       </c>
-      <c r="H74">
+      <c r="I74">
         <v>1654315.767013132</v>
       </c>
-      <c r="I74">
+      <c r="J74">
         <v>1671765.553788616</v>
       </c>
-      <c r="J74">
+      <c r="K74">
         <v>1665684.633641874</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
+        <v>2050</v>
+      </c>
+      <c r="B75">
         <v>1675768.595659149</v>
       </c>
-      <c r="B75">
+      <c r="C75">
         <v>1663863.531711849</v>
       </c>
-      <c r="C75">
+      <c r="D75">
         <v>1700834.264705527</v>
       </c>
-      <c r="D75">
+      <c r="E75">
         <v>1716376.237479083</v>
       </c>
-      <c r="E75">
+      <c r="F75">
         <v>1639336.90139912</v>
       </c>
-      <c r="F75">
+      <c r="G75">
         <v>1719711.107814241</v>
       </c>
-      <c r="G75">
+      <c r="H75">
         <v>1713049.406574043</v>
       </c>
-      <c r="H75">
+      <c r="I75">
         <v>1655678.523128049</v>
       </c>
-      <c r="I75">
+      <c r="J75">
         <v>1672940.175812812</v>
       </c>
-      <c r="J75">
+      <c r="K75">
         <v>1666857.193860475</v>
       </c>
     </row>
@@ -2783,56 +3010,61 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>2023 Rceattle</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean L@A</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean W@A</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean A@AE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean A@AC</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean L@A W@A</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean L@A W@A A@AE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean L@A W@A A@AC</t>
         </is>
@@ -2840,2369 +3072,2591 @@
     </row>
     <row r="2">
       <c r="A2">
+        <v>1977</v>
+      </c>
+      <c r="B2">
         <v>746657.9289938222</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>753086.043682688</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>880427.1949234953</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>893648.584689917</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>921122.040536306</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>925849.7824650558</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>923055.4278914541</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>935760.8743012613</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>979156.4147357706</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>976455.7365017</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
+        <v>1978</v>
+      </c>
+      <c r="B3">
         <v>738622.5683549435</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>745066.2494082984</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>872406.2252106979</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>885913.0115364321</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>913005.3676746022</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>917814.8105874883</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>915028.0678680805</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>927877.093843863</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>971259.8936263336</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>968567.9899867006</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
+        <v>1979</v>
+      </c>
+      <c r="B4">
         <v>732061.3445646089</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>738485.9784267005</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>865847.3070930016</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>879328.4807740821</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>906394.9262168586</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>911254.5575682146</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>908470.1627575159</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>921173.0970326567</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>964558.4522363336</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>961867.7193650826</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
+        <v>1980</v>
+      </c>
+      <c r="B5">
         <v>726768.8276789418</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>733152.8256860431</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>860632.0365531354</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>873893.5697923281</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>901169.7293237122</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>906033.4044548087</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>903248.0633332147</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>915656.7543588041</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>959046.1270495108</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>956350.7769083314</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
+        <v>1981</v>
+      </c>
+      <c r="B6">
         <v>721672.4305438112</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>727984.1133796213</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>855986.3500443978</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>868899.8393110561</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>896540.1549162312</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>901328.9390040431</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>898541.8127050032</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>910610.9163017687</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>953971.1785384859</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>951267.9821786986</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
+        <v>1982</v>
+      </c>
+      <c r="B7">
         <v>717098.6195316534</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>723234.8757594115</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>853083.4256886439</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>865335.5341562541</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>893711.6855581172</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>898176.9265413862</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>895387.5531635807</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>907061.8178904504</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>950263.2852482195</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>947546.9188742433</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
+        <v>1983</v>
+      </c>
+      <c r="B8">
         <v>715055.6677221631</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>720776.5472627047</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>854876.5845776905</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>865790.9627602149</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>895758.9654893496</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>899287.8979255273</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>896496.3715197409</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>907714.7170556847</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>950445.593573668</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>947707.0123017202</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
+        <v>1984</v>
+      </c>
+      <c r="B9">
         <v>713230.1649453456</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>718236.4925062817</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>857494.2057219436</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>866600.9944608533</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>898822.3362919375</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>900687.261400378</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>897904.1826659126</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>908869.6981524618</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>950708.6749262068</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>947953.4661483726</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
+        <v>1985</v>
+      </c>
+      <c r="B10">
         <v>716786.9854581881</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>720862.9995046461</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>864082.3334892569</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>871026.5196093222</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>906009.7913080932</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>905673.33442985</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>902901.1912467331</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>913769.975275757</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>954379.7819494492</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>951612.2117756627</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
+        <v>1986</v>
+      </c>
+      <c r="B11">
         <v>721936.8645922822</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>725172.8780867716</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>873283.4350144934</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>878164.5481164407</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>915770.5605098114</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>913029.0734057876</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>910238.4361120302</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>921339.582571059</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>960492.9069859476</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>957690.1886684014</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
+        <v>1987</v>
+      </c>
+      <c r="B12">
         <v>723519.2722836859</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>726328.7065902967</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>883452.0988255871</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>886831.2373095299</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>926331.2755220244</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>921155.0106616819</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>918341.6429068905</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>930283.7014803016</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>967789.504741026</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>964933.3395790654</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
+        <v>1988</v>
+      </c>
+      <c r="B13">
         <v>719531.1712496694</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>722360.1325398337</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>890880.2174026235</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>893857.0289238796</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>933919.3383739959</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>926279.7973564179</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>923563.32241565</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>937372.2715040034</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>972886.0627412385</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>970062.8724881364</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
+        <v>1989</v>
+      </c>
+      <c r="B14">
         <v>720759.3166541178</v>
       </c>
-      <c r="B14">
+      <c r="C14">
         <v>723746.4099877994</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>898710.3088710679</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>902346.9650639748</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>941738.7890018367</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>931533.4966062529</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>929037.0431427539</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>945818.0554728383</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>978778.6683769674</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>976080.436137807</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
+        <v>1990</v>
+      </c>
+      <c r="B15">
         <v>739542.7431561797</v>
       </c>
-      <c r="B15">
+      <c r="C15">
         <v>742527.438457645</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>909935.8869089242</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>914825.2458866544</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>952888.6233325165</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>940045.5444613057</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>937787.035039376</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>958280.3650582533</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>988180.0258917564</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>985600.6882838598</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
+        <v>1991</v>
+      </c>
+      <c r="B16">
         <v>775237.3096139878</v>
       </c>
-      <c r="B16">
+      <c r="C16">
         <v>778025.5573487421</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>919533.4443791978</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>925653.0562454017</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>962369.8896471321</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>946872.0120688516</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>944744.1329722508</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>969053.9420226545</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>995786.545334033</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>993248.1405862512</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
+        <v>1992</v>
+      </c>
+      <c r="B17">
         <v>816138.7309053635</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>818587.7691195182</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>925394.0898839228</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>931848.0415600123</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>968203.5778562513</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>949172.6912073328</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>947033.2562889517</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>975152.6145299673</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>998347.5640547667</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>995808.3178843982</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
+        <v>1993</v>
+      </c>
+      <c r="B18">
         <v>853990.8425901762</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>856151.5381182492</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>932659.9453495117</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>938067.3260266518</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>975801.5055266083</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>951753.0136495441</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>949588.9217543745</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>981458.9241005802</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>1000349.778029216</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>997867.2856913693</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
+        <v>1994</v>
+      </c>
+      <c r="B19">
         <v>890483.008659397</v>
       </c>
-      <c r="B19">
+      <c r="C19">
         <v>892514.3182755566</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>945547.0628138266</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>948953.1945248032</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>989571.49857372</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>959642.6578260977</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>957335.0283651323</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>992877.3544601599</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>1007119.371732361</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>1004579.287433008</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
+        <v>1995</v>
+      </c>
+      <c r="B20">
         <v>917258.5303135117</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>918874.7834450819</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>952919.2184503657</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>954798.2109383427</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>998002.4613103982</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>962779.3668801375</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>960080.5155242011</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>999408.4669371223</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>1009576.157712967</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>1006718.054002682</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
+        <v>1996</v>
+      </c>
+      <c r="B21">
         <v>938611.7295828732</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>939271.5238762163</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>958696.5891112729</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>960017.4068874704</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>1004629.474779133</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>965858.60760454</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>962689.0407436332</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>1005248.142947738</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>1012756.546241364</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>1009453.525707471</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
+        <v>1997</v>
+      </c>
+      <c r="B22">
         <v>949809.7145887943</v>
       </c>
-      <c r="B22">
+      <c r="C22">
         <v>949269.428825453</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>957678.951569682</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>960080.9659515843</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>1003912.510804804</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>963256.1439920485</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>959666.9589431008</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>1005605.946147276</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>1011524.441495533</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>1007811.880769928</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
+        <v>1998</v>
+      </c>
+      <c r="B23">
         <v>961477.6751479943</v>
       </c>
-      <c r="B23">
+      <c r="C23">
         <v>959581.337715533</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>959723.4821674514</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>963958.2765077237</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>1006108.394186599</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>964279.9935714134</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>960316.2729444703</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>1009870.640442038</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>1014672.918438456</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>1010635.283795842</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
+        <v>1999</v>
+      </c>
+      <c r="B24">
         <v>966815.3847426815</v>
       </c>
-      <c r="B24">
+      <c r="C24">
         <v>963718.4154085313</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>959767.8400916076</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>965977.6842969377</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>1006073.096126842</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>964104.455670285</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>959932.6623243416</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>1012218.945640823</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>1016718.285573868</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>1012535.019082959</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
+        <v>2000</v>
+      </c>
+      <c r="B25">
         <v>960580.6402163891</v>
       </c>
-      <c r="B25">
+      <c r="C25">
         <v>956844.0611005109</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>952338.0783882041</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>960415.9567540581</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>998398.042174162</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>957547.5837356054</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>953297.5699902081</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>1006827.350701396</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>1012142.953478625</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>1007941.465092597</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
+        <v>2001</v>
+      </c>
+      <c r="B26">
         <v>945202.8474735353</v>
       </c>
-      <c r="B26">
+      <c r="C26">
         <v>941271.5978551146</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>937670.1948891898</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>947395.4053212276</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>983942.3089438577</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>944449.8659592719</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>939998.8516686307</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>994268.4273541906</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>1000914.594217355</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>996551.4194022387</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
+        <v>2002</v>
+      </c>
+      <c r="B27">
         <v>936810.2191116547</v>
       </c>
-      <c r="B27">
+      <c r="C27">
         <v>932825.8696302589</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>930315.7159089355</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>940318.2652501719</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>977990.2940930257</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>938684.288648737</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>933938.7756894889</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>988586.2427327833</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>996293.5004044831</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>991645.7007087823</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
+        <v>2003</v>
+      </c>
+      <c r="B28">
         <v>937173.9286718194</v>
       </c>
-      <c r="B28">
+      <c r="C28">
         <v>933128.8385838519</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>930235.2810846663</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>938506.8584643059</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>980438.9160702437</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>939523.5333074386</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>934389.9044158217</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>988899.7396416469</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>997008.103583292</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>991986.0258570426</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
+        <v>2004</v>
+      </c>
+      <c r="B29">
         <v>947766.0165447857</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>943562.8495363195</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>937347.6367514939</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>941732.9805566028</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>990614.2371389982</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>945931.474923432</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>940434.3565856405</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>994383.8384657078</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>1001825.685454149</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>996401.3261434588</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
+        <v>2005</v>
+      </c>
+      <c r="B30">
         <v>991233.6744566784</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>986255.7176819837</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>973546.3036123004</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>972515.177697744</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>1029899.859646485</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>979049.2137328279</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>973249.3468837927</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>1027607.67282366</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>1032302.007163876</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>1026469.101666278</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
+        <v>2006</v>
+      </c>
+      <c r="B31">
         <v>1046782.607239028</v>
       </c>
-      <c r="B31">
+      <c r="C31">
         <v>1039810.658347879</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>1019154.385343614</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>1014626.002227084</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>1077900.681010836</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>1017840.167855902</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>1011920.391855986</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>1071950.258288261</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>1070081.659355455</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>1064025.811837211</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
+        <v>2007</v>
+      </c>
+      <c r="B32">
         <v>1085838.140905828</v>
       </c>
-      <c r="B32">
+      <c r="C32">
         <v>1076605.028535006</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>1050566.503093033</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>1044013.537308328</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>1110614.096814428</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>1043049.898950226</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>1037339.536417749</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>1102775.783531603</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>1094760.111434238</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>1088888.26496296</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
+        <v>2008</v>
+      </c>
+      <c r="B33">
         <v>1097947.306100805</v>
       </c>
-      <c r="B33">
+      <c r="C33">
         <v>1087095.621188559</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>1061204.650978377</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>1052552.408059777</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>1120767.525607639</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>1051835.418277992</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>1046360.912787148</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>1110943.086623079</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>1101228.330674235</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>1095674.960688148</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
+        <v>2009</v>
+      </c>
+      <c r="B34">
         <v>1089404.598914832</v>
       </c>
-      <c r="B34">
+      <c r="C34">
         <v>1077050.014647993</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>1053123.057729486</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>1042766.703411005</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>1110726.734890636</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>1044315.045286724</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>1038956.657001667</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>1099156.011555317</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>1090165.600936876</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>1084820.05827523</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
+        <v>2010</v>
+      </c>
+      <c r="B35">
         <v>1078543.255922426</v>
       </c>
-      <c r="B35">
+      <c r="C35">
         <v>1063948.318082591</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>1042085.224164404</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>1031142.48701782</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>1096925.806704394</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>1033930.535711095</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>1028689.242103958</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>1084704.440383508</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>1076487.810037551</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>1071305.490748708</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
+        <v>2011</v>
+      </c>
+      <c r="B36">
         <v>1067073.991439415</v>
       </c>
-      <c r="B36">
+      <c r="C36">
         <v>1049156.348207649</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>1028141.460460247</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>1018654.41949252</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>1079699.878469755</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>1020106.823527158</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>1015038.953853823</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>1068948.4295421</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>1060955.70299524</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>1055964.403685358</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
+        <v>2012</v>
+      </c>
+      <c r="B37">
         <v>1044730.372125454</v>
       </c>
-      <c r="B37">
+      <c r="C37">
         <v>1023004.458896125</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>1002978.715391488</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>997042.4169716114</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>1051196.667158829</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>995410.6053805721</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>990639.9485758566</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>1044147.280578514</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>1036618.973036928</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>1031955.42125762</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
+        <v>2013</v>
+      </c>
+      <c r="B38">
         <v>1019872.01880103</v>
       </c>
-      <c r="B38">
+      <c r="C38">
         <v>994823.2171077598</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>977357.7432075716</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>975417.407699361</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>1022482.518880383</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>971430.3468184826</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>967063.1173724213</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>1019824.488694216</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>1013681.891893768</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>1009458.930062194</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
+        <v>2014</v>
+      </c>
+      <c r="B39">
         <v>982619.3490137039</v>
       </c>
-      <c r="B39">
+      <c r="C39">
         <v>954904.1097498045</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>941469.2466090951</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>943446.649414384</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>983037.6073527311</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>938273.880619225</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>934210.9412345199</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>984773.6654907285</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>981101.7444634596</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>977239.5931970383</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
+        <v>2015</v>
+      </c>
+      <c r="B40">
         <v>924801.9340973758</v>
       </c>
-      <c r="B40">
+      <c r="C40">
         <v>895119.0309619108</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>886701.815331101</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>891511.8301963932</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>924116.2869416031</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>887186.4530881755</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>883288.8682306225</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>929016.0368905495</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>928927.5444924238</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>925330.9779336224</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
+        <v>2016</v>
+      </c>
+      <c r="B41">
         <v>880509.7588115616</v>
       </c>
-      <c r="B41">
+      <c r="C41">
         <v>849376.1132585921</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>846265.5640603658</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>850982.3412514178</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>879725.7315092592</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>850538.7274923364</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>846811.1711329161</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>884744.9384103419</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>888619.9290223167</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>885243.072120054</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
+        <v>2017</v>
+      </c>
+      <c r="B42">
         <v>842081.3379766567</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>809547.5305048672</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>810411.4274914009</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>813519.46019139</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>840172.0180407576</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>817828.8636573192</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>814202.0109680177</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>843627.2366196446</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>851008.7485074758</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>847779.6446145696</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
+        <v>2018</v>
+      </c>
+      <c r="B43">
         <v>808281.5481791621</v>
       </c>
-      <c r="B43">
+      <c r="C43">
         <v>774739.9935854535</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>777692.1376372693</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>778986.8094961685</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>804254.7810837061</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>786880.0137068511</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>783450.1464529067</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>805888.9087513833</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>815644.5048911221</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>812560.3453505734</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
+        <v>2019</v>
+      </c>
+      <c r="B44">
         <v>787647.5955494447</v>
       </c>
-      <c r="B44">
+      <c r="C44">
         <v>755078.2186938955</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>759416.6461492572</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>759064.6999897435</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>784521.0745292061</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>770007.331452078</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>766699.8163650732</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>784422.0481609819</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>795924.1660190042</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>792898.3768875285</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
+        <v>2020</v>
+      </c>
+      <c r="B45">
         <v>764506.6473120456</v>
       </c>
-      <c r="B45">
+      <c r="C45">
         <v>736676.6049150284</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>741560.6946576232</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>740161.1916720525</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>765690.2165279993</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>753090.754141839</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>749863.3106894514</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>764301.0877461438</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>777336.0402942862</v>
       </c>
-      <c r="J45">
+      <c r="K45">
         <v>774306.7186355286</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
+        <v>2021</v>
+      </c>
+      <c r="B46">
         <v>737923.2360218903</v>
       </c>
-      <c r="B46">
+      <c r="C46">
         <v>720196.440764036</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>726867.996960915</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>724101.1996986707</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>753482.2446818175</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>740421.7042247769</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>737094.7569982166</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>750401.8034249388</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>765337.064984823</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>762138.1366637533</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
+        <v>2022</v>
+      </c>
+      <c r="B47">
         <v>724853.2040680789</v>
       </c>
-      <c r="B47">
+      <c r="C47">
         <v>722415.9306135171</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>729300.8325974124</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>725368.5564076899</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>759698.7439343135</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>743896.2729554829</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>740324.9535218326</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>755200.0923780837</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>771061.1020925633</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>767508.2216157548</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
+        <v>2023</v>
+      </c>
+      <c r="B48">
         <v>716702.2369444078</v>
       </c>
-      <c r="B48">
+      <c r="C48">
         <v>733153.6660365923</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>738641.0217880518</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>735846.9585996445</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>773945.3919174089</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>753266.5404784899</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>749385.6447297478</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>770554.9495428894</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>785919.8543595688</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>781931.1813634594</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
+        <v>2024</v>
+      </c>
+      <c r="B49">
         <v>717084.9805191775</v>
       </c>
-      <c r="B49">
+      <c r="C49">
         <v>750013.026519359</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>753936.9890145172</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>754468.4020568507</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>794391.4882958052</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>768061.7542965428</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>763977.5685067893</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>794682.9050368753</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <v>808697.8669673275</v>
       </c>
-      <c r="J49">
+      <c r="K49">
         <v>804387.7736829745</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
+        <v>2025</v>
+      </c>
+      <c r="B50">
         <v>726666.1032370173</v>
       </c>
-      <c r="B50">
+      <c r="C50">
         <v>753502.3081995877</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>757939.144014151</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>762781.7610043132</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>802557.5587577436</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>772606.5097516632</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>768397.6814638064</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>807721.6667830356</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>821365.2571679463</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>816922.5198344819</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
+        <v>2026</v>
+      </c>
+      <c r="B51">
         <v>735406.0334080382</v>
       </c>
-      <c r="B51">
+      <c r="C51">
         <v>762905.1736837428</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>770673.1251160493</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>777946.2525570928</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>818177.3024917761</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>787461.5057158046</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>783191.0878057498</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>826372.8070684612</v>
       </c>
-      <c r="I51">
+      <c r="J51">
         <v>841588.1322488773</v>
       </c>
-      <c r="J51">
+      <c r="K51">
         <v>837087.7284249328</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
+        <v>2027</v>
+      </c>
+      <c r="B52">
         <v>744114.0949604358</v>
       </c>
-      <c r="B52">
+      <c r="C52">
         <v>765336.7906403395</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>778678.3208799902</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>787187.8767626106</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>827953.3536246524</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>798535.0120359762</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>794202.3675624598</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>837847.2772368306</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>855963.3645086188</v>
       </c>
-      <c r="J52">
+      <c r="K52">
         <v>851428.4446468863</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
+        <v>2028</v>
+      </c>
+      <c r="B53">
         <v>754477.525936779</v>
       </c>
-      <c r="B53">
+      <c r="C53">
         <v>766562.3953206657</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>786651.0841360036</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>795418.0346508649</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>836636.1063487517</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>809646.6954840404</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>805339.6315449984</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>847071.2798260753</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>868430.3234620448</v>
       </c>
-      <c r="J53">
+      <c r="K53">
         <v>863937.3158849636</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
+        <v>2029</v>
+      </c>
+      <c r="B54">
         <v>766348.9952965893</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <v>768897.3493719987</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>796533.9453934075</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>805104.9628080728</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>846840.2387234725</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>822003.4248927301</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>817835.5560259168</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>857257.954540719</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>881286.6416421256</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>876947.0782656193</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
+        <v>2030</v>
+      </c>
+      <c r="B55">
         <v>782133.188903661</v>
       </c>
-      <c r="B55">
+      <c r="C55">
         <v>775127.4869365044</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>809569.1722672426</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>817956.9121077996</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>859884.1746903816</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>836401.6914095557</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>832414.4519324681</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>870237.0222353939</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>895845.6960789922</v>
       </c>
-      <c r="J55">
+      <c r="K55">
         <v>891703.5135616723</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
+        <v>2031</v>
+      </c>
+      <c r="B56">
         <v>801908.1778345566</v>
       </c>
-      <c r="B56">
+      <c r="C56">
         <v>787678.5379494631</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <v>826147.171398851</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>834457.4634033942</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>876234.2883690943</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>853194.3861004002</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>849301.8167441115</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>886594.6240830858</v>
       </c>
-      <c r="I56">
+      <c r="J56">
         <v>912569.8776889351</v>
       </c>
-      <c r="J56">
+      <c r="K56">
         <v>908554.5519917329</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
+        <v>2032</v>
+      </c>
+      <c r="B57">
         <v>822690.1587831541</v>
       </c>
-      <c r="B57">
+      <c r="C57">
         <v>805055.0970099829</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>844737.7109821215</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>853123.3470314104</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>894573.8344097594</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>870972.0722120963</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>867135.5764315792</v>
       </c>
-      <c r="H57">
+      <c r="I57">
         <v>905005.8196356754</v>
       </c>
-      <c r="I57">
+      <c r="J57">
         <v>930320.2849427001</v>
       </c>
-      <c r="J57">
+      <c r="K57">
         <v>926378.9862029013</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
+        <v>2033</v>
+      </c>
+      <c r="B58">
         <v>842681.8715421202</v>
       </c>
-      <c r="B58">
+      <c r="C58">
         <v>824004.0799767638</v>
       </c>
-      <c r="C58">
+      <c r="D58">
         <v>863344.2811358831</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>871870.1752988687</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>912923.4594622715</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <v>888453.2782735466</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>884626.0178135624</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>923433.0749445333</v>
       </c>
-      <c r="I58">
+      <c r="J58">
         <v>947640.039498201</v>
       </c>
-      <c r="J58">
+      <c r="K58">
         <v>943735.4198443748</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
+        <v>2034</v>
+      </c>
+      <c r="B59">
         <v>860454.7830581063</v>
       </c>
-      <c r="B59">
+      <c r="C59">
         <v>841891.8281200358</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <v>880407.6897748635</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>889033.9447313303</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>929995.6828840662</v>
       </c>
-      <c r="F59">
+      <c r="G59">
         <v>904244.9992349767</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>900432.2157621604</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>940544.2187585958</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>963456.430004466</v>
       </c>
-      <c r="J59">
+      <c r="K59">
         <v>959582.6030741407</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
+        <v>2035</v>
+      </c>
+      <c r="B60">
         <v>876768.1438986205</v>
       </c>
-      <c r="B60">
+      <c r="C60">
         <v>858842.7655436336</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>896150.5488958587</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>904852.8997292037</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>945625.4270717086</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <v>918724.9399245981</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>914886.9713913655</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>956191.202593943</v>
       </c>
-      <c r="I60">
+      <c r="J60">
         <v>977783.1708585034</v>
       </c>
-      <c r="J60">
+      <c r="K60">
         <v>973917.8930433175</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
+        <v>2036</v>
+      </c>
+      <c r="B61">
         <v>891868.8648309549</v>
       </c>
-      <c r="B61">
+      <c r="C61">
         <v>874991.165194961</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>910848.5461117659</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <v>919635.7767475878</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>959826.0093858289</v>
       </c>
-      <c r="F61">
+      <c r="G61">
         <v>932029.7970113447</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <v>928197.6575121328</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>970409.3006317827</v>
       </c>
-      <c r="I61">
+      <c r="J61">
         <v>990654.983208015</v>
       </c>
-      <c r="J61">
+      <c r="K61">
         <v>986804.3272103323</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
+        <v>2037</v>
+      </c>
+      <c r="B62">
         <v>905542.4163424436</v>
       </c>
-      <c r="B62">
+      <c r="C62">
         <v>889894.8181320555</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>924166.7900362826</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>933171.6149773363</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>972438.3565946319</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>944069.2755104064</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>940212.1469872807</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>983089.8340038862</v>
       </c>
-      <c r="I62">
+      <c r="J62">
         <v>1002073.19104454</v>
       </c>
-      <c r="J62">
+      <c r="K62">
         <v>998221.4588875723</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
+        <v>2038</v>
+      </c>
+      <c r="B63">
         <v>917897.5717441108</v>
       </c>
-      <c r="B63">
+      <c r="C63">
         <v>902984.3301377172</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>935802.8846641905</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <v>945071.0340344566</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <v>983361.6153669322</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>954459.5242443979</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>950615.8961155267</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>994086.31422687</v>
       </c>
-      <c r="I63">
+      <c r="J63">
         <v>1011882.481024619</v>
       </c>
-      <c r="J63">
+      <c r="K63">
         <v>1008046.355070624</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
+        <v>2039</v>
+      </c>
+      <c r="B64">
         <v>928010.2021182209</v>
       </c>
-      <c r="B64">
+      <c r="C64">
         <v>913594.7696743059</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>945225.1479398037</v>
       </c>
-      <c r="D64">
+      <c r="E64">
         <v>954579.7886349461</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>992508.6079345419</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>962954.0436809177</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>959108.9726797935</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>1003217.559899761</v>
       </c>
-      <c r="I64">
+      <c r="J64">
         <v>1020044.699550697</v>
       </c>
-      <c r="J64">
+      <c r="K64">
         <v>1016214.48512161</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
+        <v>2040</v>
+      </c>
+      <c r="B65">
         <v>937078.0134360138</v>
       </c>
-      <c r="B65">
+      <c r="C65">
         <v>922844.3380808802</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>953367.5670067391</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>962697.4592198342</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>1000394.044241938</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>970207.0079770877</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>966355.8676013964</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>1011040.358451933</v>
       </c>
-      <c r="I65">
+      <c r="J65">
         <v>1026977.658424906</v>
       </c>
-      <c r="J65">
+      <c r="K65">
         <v>1023148.571682237</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
+        <v>2041</v>
+      </c>
+      <c r="B66">
         <v>944978.5718764915</v>
       </c>
-      <c r="B66">
+      <c r="C66">
         <v>931090.4403974414</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>960522.5750183482</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>969777.5446052094</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>1007227.401027987</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>976584.6784870722</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>972730.7198160002</v>
       </c>
-      <c r="H66">
+      <c r="I66">
         <v>1017798.292638899</v>
       </c>
-      <c r="I66">
+      <c r="J66">
         <v>1032948.678464522</v>
       </c>
-      <c r="J66">
+      <c r="K66">
         <v>1029120.259505558</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
+        <v>2042</v>
+      </c>
+      <c r="B67">
         <v>951740.3046753434</v>
       </c>
-      <c r="B67">
+      <c r="C67">
         <v>938577.2085124686</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>966991.2868483961</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>976167.4917924494</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>1013191.556985788</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>982287.2273309258</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>978429.6020251815</v>
       </c>
-      <c r="H67">
+      <c r="I67">
         <v>1023696.029347324</v>
       </c>
-      <c r="I67">
+      <c r="J67">
         <v>1038121.869789542</v>
       </c>
-      <c r="J67">
+      <c r="K67">
         <v>1034291.850002057</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
+        <v>2043</v>
+      </c>
+      <c r="B68">
         <v>957506.8740447799</v>
       </c>
-      <c r="B68">
+      <c r="C68">
         <v>945127.2000551061</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>972635.5512389415</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>981780.5032600061</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>1018288.391291727</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>987197.964607124</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>983351.8582499002</v>
       </c>
-      <c r="H68">
+      <c r="I68">
         <v>1028754.826127243</v>
       </c>
-      <c r="I68">
+      <c r="J68">
         <v>1042525.544731795</v>
       </c>
-      <c r="J68">
+      <c r="K68">
         <v>1038699.393609994</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
+        <v>2044</v>
+      </c>
+      <c r="B69">
         <v>962834.5798553249</v>
       </c>
-      <c r="B69">
+      <c r="C69">
         <v>950968.2834305452</v>
       </c>
-      <c r="C69">
+      <c r="D69">
         <v>977572.5380401083</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>986711.75423443</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>1022634.184455611</v>
       </c>
-      <c r="F69">
+      <c r="G69">
         <v>991482.3068631541</v>
       </c>
-      <c r="G69">
+      <c r="H69">
         <v>987626.0581177705</v>
       </c>
-      <c r="H69">
+      <c r="I69">
         <v>1033078.03974286</v>
       </c>
-      <c r="I69">
+      <c r="J69">
         <v>1046278.879766039</v>
       </c>
-      <c r="J69">
+      <c r="K69">
         <v>1042447.360895124</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
+        <v>2045</v>
+      </c>
+      <c r="B70">
         <v>967196.5364457704</v>
       </c>
-      <c r="B70">
+      <c r="C70">
         <v>956407.6082196048</v>
       </c>
-      <c r="C70">
+      <c r="D70">
         <v>981926.0453351386</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>991059.5649079154</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>1026333.969172865</v>
       </c>
-      <c r="F70">
+      <c r="G70">
         <v>995209.739544729</v>
       </c>
-      <c r="G70">
+      <c r="H70">
         <v>991342.454661588</v>
       </c>
-      <c r="H70">
+      <c r="I70">
         <v>1036758.669322066</v>
       </c>
-      <c r="I70">
+      <c r="J70">
         <v>1049452.786672076</v>
       </c>
-      <c r="J70">
+      <c r="K70">
         <v>1045615.799678256</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
+        <v>2046</v>
+      </c>
+      <c r="B71">
         <v>970767.8044499594</v>
       </c>
-      <c r="B71">
+      <c r="C71">
         <v>960860.9507003872</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>985490.3956413293</v>
       </c>
-      <c r="D71">
+      <c r="E71">
         <v>994619.2512148585</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>1029363.096700649</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>998261.5033111623</v>
       </c>
-      <c r="G71">
+      <c r="H71">
         <v>994385.1828026441</v>
       </c>
-      <c r="H71">
+      <c r="I71">
         <v>1039772.11394925</v>
       </c>
-      <c r="I71">
+      <c r="J71">
         <v>1052051.361863455</v>
       </c>
-      <c r="J71">
+      <c r="K71">
         <v>1048209.897949251</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
+        <v>2047</v>
+      </c>
+      <c r="B72">
         <v>973691.7113924723</v>
       </c>
-      <c r="B72">
+      <c r="C72">
         <v>964507.0391433925</v>
       </c>
-      <c r="C72">
+      <c r="D72">
         <v>988408.6388517505</v>
       </c>
-      <c r="D72">
+      <c r="E72">
         <v>997533.6758656634</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>1031843.136562641</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>1000760.07615787</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>996876.3579049825</v>
       </c>
-      <c r="H72">
+      <c r="I72">
         <v>1042239.313738224</v>
       </c>
-      <c r="I72">
+      <c r="J72">
         <v>1054178.895286822</v>
       </c>
-      <c r="J72">
+      <c r="K72">
         <v>1050333.765980221</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
+        <v>2048</v>
+      </c>
+      <c r="B73">
         <v>976085.6039254458</v>
       </c>
-      <c r="B73">
+      <c r="C73">
         <v>967492.203880123</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>990797.8943130835</v>
       </c>
-      <c r="D73">
+      <c r="E73">
         <v>999919.8049548061</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>1033873.621466513</v>
       </c>
-      <c r="F73">
+      <c r="G73">
         <v>1002805.734586276</v>
       </c>
-      <c r="G73">
+      <c r="H73">
         <v>998915.9595725692</v>
       </c>
-      <c r="H73">
+      <c r="I73">
         <v>1044259.286079444</v>
       </c>
-      <c r="I73">
+      <c r="J73">
         <v>1055920.772328734</v>
       </c>
-      <c r="J73">
+      <c r="K73">
         <v>1052072.642052656</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
+        <v>2049</v>
+      </c>
+      <c r="B74">
         <v>978045.5573617549</v>
       </c>
-      <c r="B74">
+      <c r="C74">
         <v>969936.2500530883</v>
       </c>
-      <c r="C74">
+      <c r="D74">
         <v>992754.0512362362</v>
       </c>
-      <c r="D74">
+      <c r="E74">
         <v>1001873.402220901</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>1035536.041900974</v>
       </c>
-      <c r="F74">
+      <c r="G74">
         <v>1004480.578051905</v>
       </c>
-      <c r="G74">
+      <c r="H74">
         <v>1000585.844181851</v>
       </c>
-      <c r="H74">
+      <c r="I74">
         <v>1045913.099555568</v>
       </c>
-      <c r="I74">
+      <c r="J74">
         <v>1057346.900631029</v>
       </c>
-      <c r="J74">
+      <c r="K74">
         <v>1053496.313368949</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
+        <v>2050</v>
+      </c>
+      <c r="B75">
         <v>979650.2315146622</v>
       </c>
-      <c r="B75">
+      <c r="C75">
         <v>971937.2658168374</v>
       </c>
-      <c r="C75">
+      <c r="D75">
         <v>994355.6170670678</v>
       </c>
-      <c r="D75">
+      <c r="E75">
         <v>1003472.872381782</v>
       </c>
-      <c r="E75">
+      <c r="F75">
         <v>1036897.116635212</v>
       </c>
-      <c r="F75">
+      <c r="G75">
         <v>1005851.823903807</v>
       </c>
-      <c r="G75">
+      <c r="H75">
         <v>1001953.030065563</v>
       </c>
-      <c r="H75">
+      <c r="I75">
         <v>1047267.127508325</v>
       </c>
-      <c r="I75">
+      <c r="J75">
         <v>1058514.515729952</v>
       </c>
-      <c r="J75">
+      <c r="K75">
         <v>1054661.916857874</v>
       </c>
     </row>
@@ -5213,56 +5667,61 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>2023 Rceattle</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean L@A</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean W@A</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean A@AE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean A@AC</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean L@A W@A</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean L@A W@A A@AE</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>2025 Rceattle New Data Clean L@A W@A A@AC</t>
         </is>
@@ -5270,2369 +5729,2591 @@
     </row>
     <row r="2">
       <c r="A2">
+        <v>1977</v>
+      </c>
+      <c r="B2">
         <v>561923.5906346415</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>561960.6585428691</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>766173.0230304888</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>760629.3122990479</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>681643.611268725</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>792270.0872658272</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>789981.0644502919</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>678029.668701601</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>701916.7299246681</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>699771.8222530062</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
+        <v>1978</v>
+      </c>
+      <c r="B3">
         <v>620526.1004852419</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>617905.0333456716</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>770044.2461150923</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>762902.9757833814</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>685567.5531919083</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>793120.9318651621</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>790839.9819149839</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>680468.1813300729</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>702205.8829975673</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>700233.1970856884</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
+        <v>1979</v>
+      </c>
+      <c r="B4">
         <v>696002.8680737212</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>688601.3460891246</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>774556.034100285</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>766016.3151393451</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>690131.3773367979</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>794117.6471406514</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>792995.100541655</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>683686.3585346502</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>702252.7535179198</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>700951.2142135487</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
+        <v>1980</v>
+      </c>
+      <c r="B5">
         <v>643847.20981868</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>640799.3938950825</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>788102.251674366</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>779587.7622680233</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>698549.4909186731</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>807049.1679912538</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>803618.2331094729</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>692127.0709302608</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>710707.253231336</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>708297.1800649411</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
+        <v>1981</v>
+      </c>
+      <c r="B6">
         <v>540059.9039221653</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>543788.947710557</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>797744.7661480475</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>793185.6386228956</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>705969.9740335639</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>814492.2836837011</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>810201.2302387072</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>702816.2704764669</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>720254.8405632512</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>716218.5252080044</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
+        <v>1982</v>
+      </c>
+      <c r="B7">
         <v>514936.7750239923</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>524143.0987062187</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>803997.5894316459</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>810219.8675427468</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>710492.9624484114</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>816457.4637569713</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>817981.0762512421</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>716379.0808278025</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>730746.5470988005</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>731475.8807596328</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
+        <v>1983</v>
+      </c>
+      <c r="B8">
         <v>599540.7372996985</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>605071.22767136</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>806919.6520932118</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>828774.2707265893</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>711678.5300759072</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>814331.3552380853</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>813679.0550833651</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>730578.3228268104</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>735720.0081205536</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>734352.7047301127</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
+        <v>1984</v>
+      </c>
+      <c r="B9">
         <v>785411.22593608</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>785605.2858448214</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>818131.0030351487</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>846551.3614004275</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>722867.3270745638</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>817605.7520214285</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>820021.7669704068</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>747274.0766543894</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>740563.5655595175</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>740852.0520168897</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
+        <v>1985</v>
+      </c>
+      <c r="B10">
         <v>1260214.359066644</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>1262341.537531293</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>869533.5233763509</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>885021.5187065529</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>765577.301616089</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>897217.3567723101</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>894346.9633949387</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>778665.4432360913</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>796403.6198074564</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>792661.8061597114</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
+        <v>1986</v>
+      </c>
+      <c r="B11">
         <v>1106850.776433271</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>1099960.334730157</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>917168.2131022401</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>911995.2956770303</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>807899.31472286</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>893216.010009618</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>886911.4163958058</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>803346.5931050171</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>791183.1953936046</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>787917.6804689857</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
+        <v>1987</v>
+      </c>
+      <c r="B12">
         <v>1055377.576325869</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>1057830.520055088</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>985788.1908803172</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>971669.9164608979</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>865303.1804240661</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>965290.4435730698</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>969525.5734478108</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>852909.2587863802</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>841440.6899594511</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>844883.4946388074</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
+        <v>1988</v>
+      </c>
+      <c r="B13">
         <v>1106064.560374558</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>1118950.802753006</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>1056263.62488602</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>1040668.777126369</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>927304.9884646139</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>1020684.37291691</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>1014612.430949728</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>913526.0814137519</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>886472.0874996006</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>881664.423568156</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
+        <v>1989</v>
+      </c>
+      <c r="B14">
         <v>1040065.584001866</v>
       </c>
-      <c r="B14">
+      <c r="C14">
         <v>1031386.702961154</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>925115.5714808611</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>924022.3110907099</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>815810.1047695224</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>912764.9994947168</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>903702.8384092971</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>815017.4693803196</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>805446.562354184</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>799374.0362236155</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
+        <v>1990</v>
+      </c>
+      <c r="B15">
         <v>827559.4051862862</v>
       </c>
-      <c r="B15">
+      <c r="C15">
         <v>816071.9194701194</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>835465.9071772583</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>847655.3342829627</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>740334.5865077795</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>841654.2905293123</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>837256.2821747691</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>751594.0987355176</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>757886.1662868896</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>752684.5476756908</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
+        <v>1991</v>
+      </c>
+      <c r="B16">
         <v>997424.6920651441</v>
       </c>
-      <c r="B16">
+      <c r="C16">
         <v>996373.2493916542</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>912006.5243848326</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>942399.3310389725</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>805501.4977770491</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>920528.4647039227</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>915539.001329805</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>832825.9873179883</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>840014.3077919789</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>836287.6993163816</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
+        <v>1992</v>
+      </c>
+      <c r="B17">
         <v>961738.6176977737</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>939290.2883543206</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>913102.9586888021</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>952629.0990143124</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>803217.3914376685</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>899322.5417005122</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>890554.5343692324</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>839089.7590278975</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>824404.2056111573</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>818319.6355295469</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
+        <v>1993</v>
+      </c>
+      <c r="B18">
         <v>727633.3452602997</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>723811.0658767476</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>767720.2110049432</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>793110.9888532776</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>679643.2309651504</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>787024.4144185254</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>786448.8014289533</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>704123.904737439</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>722079.7095885773</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>721838.0419334044</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
+        <v>1994</v>
+      </c>
+      <c r="B19">
         <v>732954.2138904615</v>
       </c>
-      <c r="B19">
+      <c r="C19">
         <v>730468.347347995</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>753038.6296270355</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>775070.4748630805</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>670967.8225331504</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>769828.6370156278</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>771116.9312311891</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>692308.5243736538</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>707044.4514928568</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>708311.9005935716</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
+        <v>1995</v>
+      </c>
+      <c r="B20">
         <v>809796.1812723188</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>811932.8828583201</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>818392.2475926311</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>843159.5668612189</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>737285.0650847021</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>849863.6949900705</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>836106.6974734742</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>759587.5952173326</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>782349.1125758801</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>770986.9227132081</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
+        <v>1996</v>
+      </c>
+      <c r="B21">
         <v>750515.1978848138</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>747177.4990212391</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>787194.505234795</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>804317.6995519499</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>722202.4833249882</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>799111.4676600005</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>801985.2782215232</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>736739.3891149675</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>738340.7206665809</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>740448.077349105</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
+        <v>1997</v>
+      </c>
+      <c r="B22">
         <v>890368.2511621655</v>
       </c>
-      <c r="B22">
+      <c r="C22">
         <v>888650.8345938203</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>883471.3226251489</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>874607.5326161797</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>817252.3488171932</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>913887.6025402569</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>896284.8790125641</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>805622.0486014561</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>819349.2186457807</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>806013.7856682248</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
+        <v>1998</v>
+      </c>
+      <c r="B23">
         <v>1221272.287707215</v>
       </c>
-      <c r="B23">
+      <c r="C23">
         <v>1220510.833868332</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>1149954.329702107</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>1073982.749540753</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>1033529.134973044</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>1120882.776009266</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>1123005.612978752</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>964092.9919689926</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>955047.972198106</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>956018.0779382843</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
+        <v>1999</v>
+      </c>
+      <c r="B24">
         <v>1057955.766130074</v>
       </c>
-      <c r="B24">
+      <c r="C24">
         <v>1064029.599516423</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>1102732.659081487</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>1074185.851662026</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>986255.6155454299</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>1141592.716613676</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>1127601.461950746</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>963029.7680714683</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>991033.1876373584</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>977904.9651783159</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
+        <v>2000</v>
+      </c>
+      <c r="B25">
         <v>2162765.865755301</v>
       </c>
-      <c r="B25">
+      <c r="C25">
         <v>2097570.883804205</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>1822942.842775583</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>1833022.594139485</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>1557320.336322657</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>1600153.686064799</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>1600024.006586145</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>1573188.112232541</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>1391666.143064165</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>1390202.921885924</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
+        <v>2001</v>
+      </c>
+      <c r="B26">
         <v>843484.3435993973</v>
       </c>
-      <c r="B26">
+      <c r="C26">
         <v>842085.6110870413</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>919676.8118238322</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>929548.3542706938</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>802885.1611013472</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>960419.686193775</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>960611.9959481186</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>813073.2860925888</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>847599.8329670093</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>849700.5786280051</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
+        <v>2002</v>
+      </c>
+      <c r="B27">
         <v>921908.0250308808</v>
       </c>
-      <c r="B27">
+      <c r="C27">
         <v>902025.8464086915</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>910171.1609550553</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>891414.0931799787</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>792627.616039867</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>908336.5581219624</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>908159.4123901847</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>777197.4535626476</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>779362.541423823</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>779168.1746666988</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
+        <v>2003</v>
+      </c>
+      <c r="B28">
         <v>840087.2753160645</v>
       </c>
-      <c r="B28">
+      <c r="C28">
         <v>841107.9367481634</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>851910.0341783423</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>835149.0414327766</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>742566.9047295516</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>888117.905433716</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>878044.5887681674</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>728652.913923631</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>757681.4765218371</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>750211.8282668341</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
+        <v>2004</v>
+      </c>
+      <c r="B29">
         <v>924113.3100813554</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>883900.7177104757</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>877974.9625166809</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>883411.4048343698</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>764635.2513559358</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>854719.5240610155</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>857868.8312107577</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>769681.2049074256</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>750308.8347313332</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>752981.5540735114</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
+        <v>2005</v>
+      </c>
+      <c r="B30">
         <v>943795.2277700031</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>897777.3487054852</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>876058.267342825</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>900320.6089750333</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>762656.9720453562</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>867662.4056403576</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>857691.9020772905</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>784022.2002069285</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>780409.8293057502</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>771418.2290568642</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
+        <v>2006</v>
+      </c>
+      <c r="B31">
         <v>914611.1515397528</v>
       </c>
-      <c r="B31">
+      <c r="C31">
         <v>864858.3265795326</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>835539.3591457964</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>884679.7687972876</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>730611.5702827087</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>835278.3599022321</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>841143.696786917</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>773206.5257107619</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>770182.7923848811</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>776005.437184789</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
+        <v>2007</v>
+      </c>
+      <c r="B32">
         <v>619399.3787195022</v>
       </c>
-      <c r="B32">
+      <c r="C32">
         <v>590489.6510387339</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>625377.9634679946</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>675431.6829679803</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>550765.3246489601</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>640259.3401067323</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>638113.4156971587</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>594519.1720090244</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>603027.3464100875</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>601124.3080072493</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
+        <v>2008</v>
+      </c>
+      <c r="B33">
         <v>644171.7275632756</v>
       </c>
-      <c r="B33">
+      <c r="C33">
         <v>600919.0417754283</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>613098.8734707613</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>658535.2924434659</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>539117.368640599</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>633631.566385998</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>631695.2395223547</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>578623.2788080079</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>592896.0076016118</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>592052.5731316567</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
+        <v>2009</v>
+      </c>
+      <c r="B34">
         <v>469452.533549617</v>
       </c>
-      <c r="B34">
+      <c r="C34">
         <v>447397.7149075911</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>492646.9037233643</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>509985.467525759</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>435954.2888043239</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>533254.0960311708</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>529522.1223784345</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>451552.5496676348</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>485151.2405741951</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>482999.5794095679</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
+        <v>2010</v>
+      </c>
+      <c r="B35">
         <v>460841.3530126021</v>
       </c>
-      <c r="B35">
+      <c r="C35">
         <v>437265.2968404989</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>484248.7870451087</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>476553.5392442295</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>429841.372517664</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>514242.2831999339</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>513505.8354182811</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>423658.4001687376</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>449197.1868375277</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>449061.1859352351</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
+        <v>2011</v>
+      </c>
+      <c r="B36">
         <v>614411.5592907257</v>
       </c>
-      <c r="B36">
+      <c r="C36">
         <v>572460.4075658174</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>582298.4617497765</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>555684.9722224884</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>514267.7776450799</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>612057.7502889388</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>607540.7226069537</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>492059.4246359341</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>519974.3298349709</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>516506.9614595235</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
+        <v>2012</v>
+      </c>
+      <c r="B37">
         <v>695655.593159543</v>
       </c>
-      <c r="B37">
+      <c r="C37">
         <v>652066.0921679436</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>656132.1775205741</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>648024.5320761258</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>574083.9862042085</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>648451.8478476132</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>649617.5172032006</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>568877.7638058958</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>567301.8918126307</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>567721.1122591466</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
+        <v>2013</v>
+      </c>
+      <c r="B38">
         <v>742670.0950666618</v>
       </c>
-      <c r="B38">
+      <c r="C38">
         <v>727087.0941490248</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>713953.9313034834</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>721531.1126351382</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>626835.5802820614</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>730431.2597408859</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>726872.9889092104</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>635376.8184260166</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>651868.9818937167</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>648019.9333832494</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
+        <v>2014</v>
+      </c>
+      <c r="B39">
         <v>545972.8202091842</v>
       </c>
-      <c r="B39">
+      <c r="C39">
         <v>583187.0595648569</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>612379.8475240294</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>608008.4561199724</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>553892.0324650056</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>633185.6653916533</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>633471.1442689997</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>550567.4273111586</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>567219.5066210459</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>567668.5474353894</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
+        <v>2015</v>
+      </c>
+      <c r="B40">
         <v>525481.2159379956</v>
       </c>
-      <c r="B40">
+      <c r="C40">
         <v>603406.926389319</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>622084.5220817773</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>610248.1491112586</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>569242.1795992949</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>658400.1629020597</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>649588.9012866777</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>557877.7298475323</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>588204.1395732759</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>581010.1415673428</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
+        <v>2016</v>
+      </c>
+      <c r="B41">
         <v>599380.7240177552</v>
       </c>
-      <c r="B41">
+      <c r="C41">
         <v>755834.98923788</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>750800.2021532436</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>742677.4384215784</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>685079.4658860408</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>750251.3178260189</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>748136.1490698991</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>676947.9264967263</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>679469.8066221754</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>676808.0408606656</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
+        <v>2017</v>
+      </c>
+      <c r="B42">
         <v>658405.429190198</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>880788.3775130452</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>844118.909526949</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>877390.6378620641</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>771427.9913985695</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>848089.0950155349</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>838463.3207741057</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>801414.8150083758</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>800399.5743194459</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>790710.3227773898</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
+        <v>2018</v>
+      </c>
+      <c r="B43">
         <v>757543.2788952539</v>
       </c>
-      <c r="B43">
+      <c r="C43">
         <v>886275.2177379505</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>863625.8897316613</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>929204.4699961104</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>779440.4572307202</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>848354.7521613783</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>846952.6613433647</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>839663.6037897756</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>815153.6209311748</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>814216.4217619833</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
+        <v>2019</v>
+      </c>
+      <c r="B44">
         <v>607371.4033129427</v>
       </c>
-      <c r="B44">
+      <c r="C44">
         <v>659894.0674735022</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>690898.5861037765</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>732747.7506756919</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>624405.1042972073</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>726442.0812285928</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>722917.2563931383</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>663263.7666468789</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>689716.3625860517</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>687258.8753613359</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
+        <v>2020</v>
+      </c>
+      <c r="B45">
         <v>662290.7321375252</v>
       </c>
-      <c r="B45">
+      <c r="C45">
         <v>590465.9981243273</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>644401.6439953907</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>665749.2932153469</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>579419.0788069696</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>679427.473976257</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>675048.1952028353</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>599681.5781598345</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>628392.08401567</v>
       </c>
-      <c r="J45">
+      <c r="K45">
         <v>625027.7204674558</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
+        <v>2021</v>
+      </c>
+      <c r="B46">
         <v>682870.253485114</v>
       </c>
-      <c r="B46">
+      <c r="C46">
         <v>577209.8859458219</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>635738.2728699222</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>642389.3330772658</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>571558.7684272034</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>685597.3639808764</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>682024.0894633392</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>578688.5948402593</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>620295.6402874604</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>617502.9479939488</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
+        <v>2022</v>
+      </c>
+      <c r="B47">
         <v>682812.401837012</v>
       </c>
-      <c r="B47">
+      <c r="C47">
         <v>619906.7574358068</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>690176.864984879</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>688937.3184151435</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>617332.2351346025</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>731181.4093575744</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>727690.3752967871</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>617359.2940850477</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>652566.7229714891</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>649330.3348929016</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
+        <v>2023</v>
+      </c>
+      <c r="B48">
         <v>682628.6758057827</v>
       </c>
-      <c r="B48">
+      <c r="C48">
         <v>622884.9962652557</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>714070.6034561738</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>717743.6555850119</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>636421.1254027762</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>744091.0837970693</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>745112.8339425968</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>640574.8946063978</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>666449.2384629973</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>667107.8515300057</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
+        <v>2024</v>
+      </c>
+      <c r="B49">
         <v>802343.9063816267</v>
       </c>
-      <c r="B49">
+      <c r="C49">
         <v>667848.6427872791</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>752876.7683792991</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>760487.2635565726</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>669914.6482584235</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>779498.6080186814</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>776855.0069926161</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>677327.1684587302</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <v>699377.1991295036</v>
       </c>
-      <c r="J49">
+      <c r="K49">
         <v>697102.4857624809</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
+        <v>2025</v>
+      </c>
+      <c r="B50">
         <v>802343.9063816267</v>
       </c>
-      <c r="B50">
+      <c r="C50">
         <v>797528.6728770635</v>
       </c>
-      <c r="C50">
+      <c r="D50">
         <v>814287.9090062374</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>821692.5037897824</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>722235.156059145</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>822788.5366788681</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>819603.9254347135</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>729393.6218078918</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>736598.6483209771</v>
       </c>
-      <c r="J50">
+      <c r="K50">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
+        <v>2026</v>
+      </c>
+      <c r="B51">
         <v>802343.9063816267</v>
       </c>
-      <c r="B51">
+      <c r="C51">
         <v>797528.6728770635</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>814287.9090062374</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>821692.5037897824</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>722235.156059145</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>822788.5366788681</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>819603.9254347135</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>729393.6218078918</v>
       </c>
-      <c r="I51">
+      <c r="J51">
         <v>736598.6483209771</v>
       </c>
-      <c r="J51">
+      <c r="K51">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
+        <v>2027</v>
+      </c>
+      <c r="B52">
         <v>802343.9063816267</v>
       </c>
-      <c r="B52">
+      <c r="C52">
         <v>797528.6728770635</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>814287.9090062374</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <v>821692.5037897824</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>722235.156059145</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>822788.5366788681</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>819603.9254347135</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>729393.6218078918</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>736598.6483209771</v>
       </c>
-      <c r="J52">
+      <c r="K52">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
+        <v>2028</v>
+      </c>
+      <c r="B53">
         <v>802343.9063816267</v>
       </c>
-      <c r="B53">
+      <c r="C53">
         <v>797528.6728770635</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>814287.9090062374</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>821692.5037897824</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>722235.156059145</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>822788.5366788681</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <v>819603.9254347135</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>729393.6218078918</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>736598.6483209771</v>
       </c>
-      <c r="J53">
+      <c r="K53">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
+        <v>2029</v>
+      </c>
+      <c r="B54">
         <v>802343.9063816267</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <v>797528.6728770635</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>814287.9090062374</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <v>821692.5037897824</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>722235.156059145</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>822788.5366788681</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>819603.9254347135</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>729393.6218078918</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>736598.6483209771</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
+        <v>2030</v>
+      </c>
+      <c r="B55">
         <v>802343.9063816267</v>
       </c>
-      <c r="B55">
+      <c r="C55">
         <v>797528.6728770635</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>814287.9090062374</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <v>821692.5037897824</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>722235.156059145</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>822788.5366788681</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>819603.9254347135</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>729393.6218078918</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>736598.6483209771</v>
       </c>
-      <c r="J55">
+      <c r="K55">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
+        <v>2031</v>
+      </c>
+      <c r="B56">
         <v>802343.9063816267</v>
       </c>
-      <c r="B56">
+      <c r="C56">
         <v>797528.6728770635</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <v>814287.9090062374</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>821692.5037897824</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>722235.156059145</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>822788.5366788681</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>819603.9254347135</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>729393.6218078918</v>
       </c>
-      <c r="I56">
+      <c r="J56">
         <v>736598.6483209771</v>
       </c>
-      <c r="J56">
+      <c r="K56">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
+        <v>2032</v>
+      </c>
+      <c r="B57">
         <v>802343.9063816267</v>
       </c>
-      <c r="B57">
+      <c r="C57">
         <v>797528.6728770635</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>814287.9090062374</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>821692.5037897824</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>722235.156059145</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>822788.5366788681</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <v>819603.9254347135</v>
       </c>
-      <c r="H57">
+      <c r="I57">
         <v>729393.6218078918</v>
       </c>
-      <c r="I57">
+      <c r="J57">
         <v>736598.6483209771</v>
       </c>
-      <c r="J57">
+      <c r="K57">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
+        <v>2033</v>
+      </c>
+      <c r="B58">
         <v>802343.9063816267</v>
       </c>
-      <c r="B58">
+      <c r="C58">
         <v>797528.6728770635</v>
       </c>
-      <c r="C58">
+      <c r="D58">
         <v>814287.9090062374</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>821692.5037897824</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>722235.156059145</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <v>822788.5366788681</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <v>819603.9254347135</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>729393.6218078918</v>
       </c>
-      <c r="I58">
+      <c r="J58">
         <v>736598.6483209771</v>
       </c>
-      <c r="J58">
+      <c r="K58">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
+        <v>2034</v>
+      </c>
+      <c r="B59">
         <v>802343.9063816267</v>
       </c>
-      <c r="B59">
+      <c r="C59">
         <v>797528.6728770635</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <v>814287.9090062374</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>821692.5037897824</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>722235.156059145</v>
       </c>
-      <c r="F59">
+      <c r="G59">
         <v>822788.5366788681</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>819603.9254347135</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>729393.6218078918</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>736598.6483209771</v>
       </c>
-      <c r="J59">
+      <c r="K59">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
+        <v>2035</v>
+      </c>
+      <c r="B60">
         <v>802343.9063816267</v>
       </c>
-      <c r="B60">
+      <c r="C60">
         <v>797528.6728770635</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>814287.9090062374</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>821692.5037897824</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>722235.156059145</v>
       </c>
-      <c r="F60">
+      <c r="G60">
         <v>822788.5366788681</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>819603.9254347135</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>729393.6218078918</v>
       </c>
-      <c r="I60">
+      <c r="J60">
         <v>736598.6483209771</v>
       </c>
-      <c r="J60">
+      <c r="K60">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
+        <v>2036</v>
+      </c>
+      <c r="B61">
         <v>802343.9063816267</v>
       </c>
-      <c r="B61">
+      <c r="C61">
         <v>797528.6728770635</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>814287.9090062374</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <v>821692.5037897824</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>722235.156059145</v>
       </c>
-      <c r="F61">
+      <c r="G61">
         <v>822788.5366788681</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <v>819603.9254347135</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>729393.6218078918</v>
       </c>
-      <c r="I61">
+      <c r="J61">
         <v>736598.6483209771</v>
       </c>
-      <c r="J61">
+      <c r="K61">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
+        <v>2037</v>
+      </c>
+      <c r="B62">
         <v>802343.9063816267</v>
       </c>
-      <c r="B62">
+      <c r="C62">
         <v>797528.6728770635</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>814287.9090062374</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>821692.5037897824</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>722235.156059145</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>822788.5366788681</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>819603.9254347135</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>729393.6218078918</v>
       </c>
-      <c r="I62">
+      <c r="J62">
         <v>736598.6483209771</v>
       </c>
-      <c r="J62">
+      <c r="K62">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
+        <v>2038</v>
+      </c>
+      <c r="B63">
         <v>802343.9063816267</v>
       </c>
-      <c r="B63">
+      <c r="C63">
         <v>797528.6728770635</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>814287.9090062374</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <v>821692.5037897824</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <v>722235.156059145</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>822788.5366788681</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>819603.9254347135</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>729393.6218078918</v>
       </c>
-      <c r="I63">
+      <c r="J63">
         <v>736598.6483209771</v>
       </c>
-      <c r="J63">
+      <c r="K63">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
+        <v>2039</v>
+      </c>
+      <c r="B64">
         <v>802343.9063816267</v>
       </c>
-      <c r="B64">
+      <c r="C64">
         <v>797528.6728770635</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>814287.9090062374</v>
       </c>
-      <c r="D64">
+      <c r="E64">
         <v>821692.5037897824</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>722235.156059145</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>822788.5366788681</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>819603.9254347135</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>729393.6218078918</v>
       </c>
-      <c r="I64">
+      <c r="J64">
         <v>736598.6483209771</v>
       </c>
-      <c r="J64">
+      <c r="K64">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
+        <v>2040</v>
+      </c>
+      <c r="B65">
         <v>802343.9063816267</v>
       </c>
-      <c r="B65">
+      <c r="C65">
         <v>797528.6728770635</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>814287.9090062374</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>821692.5037897824</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>722235.156059145</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>822788.5366788681</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>819603.9254347135</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>729393.6218078918</v>
       </c>
-      <c r="I65">
+      <c r="J65">
         <v>736598.6483209771</v>
       </c>
-      <c r="J65">
+      <c r="K65">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
+        <v>2041</v>
+      </c>
+      <c r="B66">
         <v>802343.9063816267</v>
       </c>
-      <c r="B66">
+      <c r="C66">
         <v>797528.6728770635</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>814287.9090062374</v>
       </c>
-      <c r="D66">
+      <c r="E66">
         <v>821692.5037897824</v>
       </c>
-      <c r="E66">
+      <c r="F66">
         <v>722235.156059145</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>822788.5366788681</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>819603.9254347135</v>
       </c>
-      <c r="H66">
+      <c r="I66">
         <v>729393.6218078918</v>
       </c>
-      <c r="I66">
+      <c r="J66">
         <v>736598.6483209771</v>
       </c>
-      <c r="J66">
+      <c r="K66">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
+        <v>2042</v>
+      </c>
+      <c r="B67">
         <v>802343.9063816267</v>
       </c>
-      <c r="B67">
+      <c r="C67">
         <v>797528.6728770635</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>814287.9090062374</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>821692.5037897824</v>
       </c>
-      <c r="E67">
+      <c r="F67">
         <v>722235.156059145</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>822788.5366788681</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>819603.9254347135</v>
       </c>
-      <c r="H67">
+      <c r="I67">
         <v>729393.6218078918</v>
       </c>
-      <c r="I67">
+      <c r="J67">
         <v>736598.6483209771</v>
       </c>
-      <c r="J67">
+      <c r="K67">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
+        <v>2043</v>
+      </c>
+      <c r="B68">
         <v>802343.9063816267</v>
       </c>
-      <c r="B68">
+      <c r="C68">
         <v>797528.6728770635</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>814287.9090062374</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>821692.5037897824</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>722235.156059145</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>822788.5366788681</v>
       </c>
-      <c r="G68">
+      <c r="H68">
         <v>819603.9254347135</v>
       </c>
-      <c r="H68">
+      <c r="I68">
         <v>729393.6218078918</v>
       </c>
-      <c r="I68">
+      <c r="J68">
         <v>736598.6483209771</v>
       </c>
-      <c r="J68">
+      <c r="K68">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
+        <v>2044</v>
+      </c>
+      <c r="B69">
         <v>802343.9063816267</v>
       </c>
-      <c r="B69">
+      <c r="C69">
         <v>797528.6728770635</v>
       </c>
-      <c r="C69">
+      <c r="D69">
         <v>814287.9090062374</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>821692.5037897824</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>722235.156059145</v>
       </c>
-      <c r="F69">
+      <c r="G69">
         <v>822788.5366788681</v>
       </c>
-      <c r="G69">
+      <c r="H69">
         <v>819603.9254347135</v>
       </c>
-      <c r="H69">
+      <c r="I69">
         <v>729393.6218078918</v>
       </c>
-      <c r="I69">
+      <c r="J69">
         <v>736598.6483209771</v>
       </c>
-      <c r="J69">
+      <c r="K69">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
+        <v>2045</v>
+      </c>
+      <c r="B70">
         <v>802343.9063816267</v>
       </c>
-      <c r="B70">
+      <c r="C70">
         <v>797528.6728770635</v>
       </c>
-      <c r="C70">
+      <c r="D70">
         <v>814287.9090062374</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>821692.5037897824</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>722235.156059145</v>
       </c>
-      <c r="F70">
+      <c r="G70">
         <v>822788.5366788681</v>
       </c>
-      <c r="G70">
+      <c r="H70">
         <v>819603.9254347135</v>
       </c>
-      <c r="H70">
+      <c r="I70">
         <v>729393.6218078918</v>
       </c>
-      <c r="I70">
+      <c r="J70">
         <v>736598.6483209771</v>
       </c>
-      <c r="J70">
+      <c r="K70">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
+        <v>2046</v>
+      </c>
+      <c r="B71">
         <v>802343.9063816267</v>
       </c>
-      <c r="B71">
+      <c r="C71">
         <v>797528.6728770635</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>814287.9090062374</v>
       </c>
-      <c r="D71">
+      <c r="E71">
         <v>821692.5037897824</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>722235.156059145</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>822788.5366788681</v>
       </c>
-      <c r="G71">
+      <c r="H71">
         <v>819603.9254347135</v>
       </c>
-      <c r="H71">
+      <c r="I71">
         <v>729393.6218078918</v>
       </c>
-      <c r="I71">
+      <c r="J71">
         <v>736598.6483209771</v>
       </c>
-      <c r="J71">
+      <c r="K71">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
+        <v>2047</v>
+      </c>
+      <c r="B72">
         <v>802343.9063816267</v>
       </c>
-      <c r="B72">
+      <c r="C72">
         <v>797528.6728770635</v>
       </c>
-      <c r="C72">
+      <c r="D72">
         <v>814287.9090062374</v>
       </c>
-      <c r="D72">
+      <c r="E72">
         <v>821692.5037897824</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>722235.156059145</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>822788.5366788681</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>819603.9254347135</v>
       </c>
-      <c r="H72">
+      <c r="I72">
         <v>729393.6218078918</v>
       </c>
-      <c r="I72">
+      <c r="J72">
         <v>736598.6483209771</v>
       </c>
-      <c r="J72">
+      <c r="K72">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
+        <v>2048</v>
+      </c>
+      <c r="B73">
         <v>802343.9063816267</v>
       </c>
-      <c r="B73">
+      <c r="C73">
         <v>797528.6728770635</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>814287.9090062374</v>
       </c>
-      <c r="D73">
+      <c r="E73">
         <v>821692.5037897824</v>
       </c>
-      <c r="E73">
+      <c r="F73">
         <v>722235.156059145</v>
       </c>
-      <c r="F73">
+      <c r="G73">
         <v>822788.5366788681</v>
       </c>
-      <c r="G73">
+      <c r="H73">
         <v>819603.9254347135</v>
       </c>
-      <c r="H73">
+      <c r="I73">
         <v>729393.6218078918</v>
       </c>
-      <c r="I73">
+      <c r="J73">
         <v>736598.6483209771</v>
       </c>
-      <c r="J73">
+      <c r="K73">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
+        <v>2049</v>
+      </c>
+      <c r="B74">
         <v>802343.9063816267</v>
       </c>
-      <c r="B74">
+      <c r="C74">
         <v>797528.6728770635</v>
       </c>
-      <c r="C74">
+      <c r="D74">
         <v>814287.9090062374</v>
       </c>
-      <c r="D74">
+      <c r="E74">
         <v>821692.5037897824</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>722235.156059145</v>
       </c>
-      <c r="F74">
+      <c r="G74">
         <v>822788.5366788681</v>
       </c>
-      <c r="G74">
+      <c r="H74">
         <v>819603.9254347135</v>
       </c>
-      <c r="H74">
+      <c r="I74">
         <v>729393.6218078918</v>
       </c>
-      <c r="I74">
+      <c r="J74">
         <v>736598.6483209771</v>
       </c>
-      <c r="J74">
+      <c r="K74">
         <v>733924.7028967908</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
+        <v>2050</v>
+      </c>
+      <c r="B75">
         <v>802343.9063816267</v>
       </c>
-      <c r="B75">
+      <c r="C75">
         <v>797528.6728770635</v>
       </c>
-      <c r="C75">
+      <c r="D75">
         <v>814287.9090062374</v>
       </c>
-      <c r="D75">
+      <c r="E75">
         <v>821692.5037897824</v>
       </c>
-      <c r="E75">
+      <c r="F75">
         <v>722235.156059145</v>
       </c>
-      <c r="F75">
+      <c r="G75">
         <v>822788.5366788681</v>
       </c>
-      <c r="G75">
+      <c r="H75">
         <v>819603.9254347135</v>
       </c>
-      <c r="H75">
+      <c r="I75">
         <v>729393.6218078918</v>
       </c>
-      <c r="I75">
+      <c r="J75">
         <v>736598.6483209771</v>
       </c>
-      <c r="J75">
+      <c r="K75">
         <v>733924.7028967908</v>
       </c>
     </row>

--- a/Results/Model bridging outputs.xlsx
+++ b/Results/Model bridging outputs.xlsx
@@ -418,34 +418,34 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>1270992.078794064</v>
+        <v>145106.0158417163</v>
       </c>
       <c r="C2">
-        <v>1281684.591266106</v>
+        <v>1465180.184588539</v>
       </c>
       <c r="D2">
-        <v>1504086.90315226</v>
+        <v>1698601.686236291</v>
       </c>
       <c r="E2">
-        <v>1525787.029938394</v>
+        <v>1711668.413840666</v>
       </c>
       <c r="F2">
-        <v>1453981.372054342</v>
+        <v>1639993.361607599</v>
       </c>
       <c r="G2">
-        <v>1580986.477865727</v>
+        <v>1721414.854598895</v>
       </c>
       <c r="H2">
-        <v>1576220.135698695</v>
+        <v>1715173.318381905</v>
       </c>
       <c r="I2">
-        <v>1476818.106513873</v>
+        <v>1654225.350479335</v>
       </c>
       <c r="J2">
-        <v>1545163.474964341</v>
+        <v>1674319.505160615</v>
       </c>
       <c r="K2">
-        <v>1540897.742383468</v>
+        <v>1668477.498949887</v>
       </c>
     </row>
     <row r="3">
@@ -453,34 +453,34 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>1260760.248169834</v>
+        <v>157837.6419671343</v>
       </c>
       <c r="C3">
-        <v>1270856.494622041</v>
+        <v>1440685.841810436</v>
       </c>
       <c r="D3">
-        <v>1499000.244437364</v>
+        <v>1684624.248244215</v>
       </c>
       <c r="E3">
-        <v>1519083.290344778</v>
+        <v>1696644.651394552</v>
       </c>
       <c r="F3">
-        <v>1446900.441687675</v>
+        <v>1628018.56221921</v>
       </c>
       <c r="G3">
-        <v>1574842.808077489</v>
+        <v>1708914.465386841</v>
       </c>
       <c r="H3">
-        <v>1570073.600760674</v>
+        <v>1702735.692309923</v>
       </c>
       <c r="I3">
-        <v>1468757.612826034</v>
+        <v>1641584.722335044</v>
       </c>
       <c r="J3">
-        <v>1536740.259360753</v>
+        <v>1662576.907956722</v>
       </c>
       <c r="K3">
-        <v>1532458.665515638</v>
+        <v>1656759.05572978</v>
       </c>
     </row>
     <row r="4">
@@ -488,34 +488,34 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>1257163.680528443</v>
+        <v>323419.1167143278</v>
       </c>
       <c r="C4">
-        <v>1266179.952299369</v>
+        <v>1417751.289674118</v>
       </c>
       <c r="D4">
-        <v>1497665.074791715</v>
+        <v>1671488.009089528</v>
       </c>
       <c r="E4">
-        <v>1515478.809337291</v>
+        <v>1681987.93579166</v>
       </c>
       <c r="F4">
-        <v>1443813.035543105</v>
+        <v>1616449.797151168</v>
       </c>
       <c r="G4">
-        <v>1571885.272473956</v>
+        <v>1697533.147714145</v>
       </c>
       <c r="H4">
-        <v>1567172.192944205</v>
+        <v>1691497.487923996</v>
       </c>
       <c r="I4">
-        <v>1463961.179357795</v>
+        <v>1628846.657461733</v>
       </c>
       <c r="J4">
-        <v>1531210.460152539</v>
+        <v>1651300.675310734</v>
       </c>
       <c r="K4">
-        <v>1526918.273645719</v>
+        <v>1645541.507870584</v>
       </c>
     </row>
     <row r="5">
@@ -523,34 +523,34 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>1255661.26115658</v>
+        <v>474926.6396901449</v>
       </c>
       <c r="C5">
-        <v>1263497.063998782</v>
+        <v>1394406.19068686</v>
       </c>
       <c r="D5">
-        <v>1499911.297089376</v>
+        <v>1659830.980665132</v>
       </c>
       <c r="E5">
-        <v>1515017.776184112</v>
+        <v>1668489.93004976</v>
       </c>
       <c r="F5">
-        <v>1444357.089753479</v>
+        <v>1605425.285981657</v>
       </c>
       <c r="G5">
-        <v>1572081.075847748</v>
+        <v>1687813.071827203</v>
       </c>
       <c r="H5">
-        <v>1567340.383950214</v>
+        <v>1681858.370547315</v>
       </c>
       <c r="I5">
-        <v>1462183.862802921</v>
+        <v>1616229.308611218</v>
       </c>
       <c r="J5">
-        <v>1528302.22445761</v>
+        <v>1640559.956151791</v>
       </c>
       <c r="K5">
-        <v>1523998.573920624</v>
+        <v>1634885.012763716</v>
       </c>
     </row>
     <row r="6">
@@ -558,34 +558,34 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>1250168.427621922</v>
+        <v>584344.3529959823</v>
       </c>
       <c r="C6">
-        <v>1257076.682510897</v>
+        <v>1367067.68586609</v>
       </c>
       <c r="D6">
-        <v>1504261.676172229</v>
+        <v>1649031.607391026</v>
       </c>
       <c r="E6">
-        <v>1516594.295199407</v>
+        <v>1655833.47468207</v>
       </c>
       <c r="F6">
-        <v>1447128.55899397</v>
+        <v>1594412.445558787</v>
       </c>
       <c r="G6">
-        <v>1573978.662225274</v>
+        <v>1678913.246075341</v>
       </c>
       <c r="H6">
-        <v>1569122.758190677</v>
+        <v>1672963.323591381</v>
       </c>
       <c r="I6">
-        <v>1462243.80123103</v>
+        <v>1603359.440661674</v>
       </c>
       <c r="J6">
-        <v>1526872.450549466</v>
+        <v>1629797.795420894</v>
       </c>
       <c r="K6">
-        <v>1522512.618115389</v>
+        <v>1624183.313552348</v>
       </c>
     </row>
     <row r="7">
@@ -593,34 +593,34 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>1241625.29840498</v>
+        <v>694515.2962053384</v>
       </c>
       <c r="C7">
-        <v>1248083.10288029</v>
+        <v>1338228.801977386</v>
       </c>
       <c r="D7">
-        <v>1511028.133159342</v>
+        <v>1640150.905087227</v>
       </c>
       <c r="E7">
-        <v>1521160.56866604</v>
+        <v>1645650.301191262</v>
       </c>
       <c r="F7">
-        <v>1452517.858541909</v>
+        <v>1584720.232887474</v>
       </c>
       <c r="G7">
-        <v>1577838.930772227</v>
+        <v>1671623.467540026</v>
       </c>
       <c r="H7">
-        <v>1573102.740773611</v>
+        <v>1665913.626705025</v>
       </c>
       <c r="I7">
-        <v>1464946.93085072</v>
+        <v>1591891.092511969</v>
       </c>
       <c r="J7">
-        <v>1527751.569689834</v>
+        <v>1620455.702945806</v>
       </c>
       <c r="K7">
-        <v>1523346.810423736</v>
+        <v>1614925.263327695</v>
       </c>
     </row>
     <row r="8">
@@ -628,34 +628,34 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>1237395.659387482</v>
+        <v>758913.437106378</v>
       </c>
       <c r="C8">
-        <v>1243600.953673358</v>
+        <v>1315837.736314926</v>
       </c>
       <c r="D8">
-        <v>1522049.185877231</v>
+        <v>1635620.636447534</v>
       </c>
       <c r="E8">
-        <v>1531298.833539293</v>
+        <v>1641057.820583299</v>
       </c>
       <c r="F8">
-        <v>1462428.904404929</v>
+        <v>1579060.974063966</v>
       </c>
       <c r="G8">
-        <v>1585441.677104134</v>
+        <v>1668141.109849646</v>
       </c>
       <c r="H8">
-        <v>1580844.056861436</v>
+        <v>1662688.680070647</v>
       </c>
       <c r="I8">
-        <v>1472824.879504027</v>
+        <v>1585094.904794646</v>
       </c>
       <c r="J8">
-        <v>1533344.870246066</v>
+        <v>1615471.93104802</v>
       </c>
       <c r="K8">
-        <v>1528941.400116005</v>
+        <v>1610076.596566272</v>
       </c>
     </row>
     <row r="9">
@@ -663,34 +663,34 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>1241289.964758538</v>
+        <v>787750.4774905376</v>
       </c>
       <c r="C9">
-        <v>1247181.534279157</v>
+        <v>1303132.831286454</v>
       </c>
       <c r="D9">
-        <v>1532514.985721695</v>
+        <v>1631060.206651893</v>
       </c>
       <c r="E9">
-        <v>1542180.039205052</v>
+        <v>1637637.980251724</v>
       </c>
       <c r="F9">
-        <v>1471718.565718016</v>
+        <v>1572940.992087275</v>
       </c>
       <c r="G9">
-        <v>1591794.264877846</v>
+        <v>1663778.217950993</v>
       </c>
       <c r="H9">
-        <v>1587545.079188583</v>
+        <v>1658783.590493298</v>
       </c>
       <c r="I9">
-        <v>1481135.340921927</v>
+        <v>1578828.332083624</v>
       </c>
       <c r="J9">
-        <v>1538626.910851453</v>
+        <v>1610255.31486103</v>
       </c>
       <c r="K9">
-        <v>1534299.301309814</v>
+        <v>1605067.905848469</v>
       </c>
     </row>
     <row r="10">
@@ -698,34 +698,34 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>1279454.009924183</v>
+        <v>846262.2701509026</v>
       </c>
       <c r="C10">
-        <v>1285125.336908981</v>
+        <v>1325200.982582958</v>
       </c>
       <c r="D10">
-        <v>1549216.123652715</v>
+        <v>1633484.802487422</v>
       </c>
       <c r="E10">
-        <v>1559704.514751705</v>
+        <v>1641517.171709022</v>
       </c>
       <c r="F10">
-        <v>1485649.808703877</v>
+        <v>1572069.229293733</v>
       </c>
       <c r="G10">
-        <v>1605447.196180705</v>
+        <v>1667204.886594884</v>
       </c>
       <c r="H10">
-        <v>1601401.702553765</v>
+        <v>1662522.369709452</v>
       </c>
       <c r="I10">
-        <v>1495142.129025163</v>
+        <v>1578770.34618756</v>
       </c>
       <c r="J10">
-        <v>1549182.201119072</v>
+        <v>1610676.960176403</v>
       </c>
       <c r="K10">
-        <v>1544943.344326942</v>
+        <v>1605706.091019599</v>
       </c>
     </row>
     <row r="11">
@@ -733,34 +733,34 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>1332261.800735511</v>
+        <v>862882.5652850283</v>
       </c>
       <c r="C11">
-        <v>1337276.710874633</v>
+        <v>1364046.851216902</v>
       </c>
       <c r="D11">
-        <v>1571917.880527588</v>
+        <v>1642811.783493792</v>
       </c>
       <c r="E11">
-        <v>1582603.934494323</v>
+        <v>1651601.51231945</v>
       </c>
       <c r="F11">
-        <v>1504057.627150749</v>
+        <v>1576565.535294225</v>
       </c>
       <c r="G11">
-        <v>1623081.922686318</v>
+        <v>1675270.438582697</v>
       </c>
       <c r="H11">
-        <v>1618992.178215082</v>
+        <v>1670650.584141412</v>
       </c>
       <c r="I11">
-        <v>1514067.165166952</v>
+        <v>1584424.209485997</v>
       </c>
       <c r="J11">
-        <v>1564174.30107424</v>
+        <v>1616099.77036338</v>
       </c>
       <c r="K11">
-        <v>1559973.87559151</v>
+        <v>1611289.675017556</v>
       </c>
     </row>
     <row r="12">
@@ -768,34 +768,34 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>1394409.416988673</v>
+        <v>857972.5110116518</v>
       </c>
       <c r="C12">
-        <v>1398990.355990305</v>
+        <v>1414729.470439267</v>
       </c>
       <c r="D12">
-        <v>1600813.091117056</v>
+        <v>1659295.733378759</v>
       </c>
       <c r="E12">
-        <v>1610817.000448748</v>
+        <v>1667873.767850629</v>
       </c>
       <c r="F12">
-        <v>1526664.399962401</v>
+        <v>1586316.61530288</v>
       </c>
       <c r="G12">
-        <v>1646138.981756186</v>
+        <v>1689432.334376394</v>
       </c>
       <c r="H12">
-        <v>1642364.58342729</v>
+        <v>1685224.528085309</v>
       </c>
       <c r="I12">
-        <v>1536884.602582023</v>
+        <v>1594931.486781233</v>
       </c>
       <c r="J12">
-        <v>1582431.408493605</v>
+        <v>1625473.050327491</v>
       </c>
       <c r="K12">
-        <v>1578317.423225933</v>
+        <v>1620862.860790923</v>
       </c>
     </row>
     <row r="13">
@@ -803,34 +803,34 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>1460896.40191376</v>
+        <v>900138.0328584678</v>
       </c>
       <c r="C13">
-        <v>1465654.616489346</v>
+        <v>1472306.293581433</v>
       </c>
       <c r="D13">
-        <v>1633157.224682642</v>
+        <v>1680248.941929729</v>
       </c>
       <c r="E13">
-        <v>1641599.322117365</v>
+        <v>1687606.365898212</v>
       </c>
       <c r="F13">
-        <v>1551022.505731651</v>
+        <v>1598973.542482885</v>
       </c>
       <c r="G13">
-        <v>1671207.009515726</v>
+        <v>1706327.207512636</v>
       </c>
       <c r="H13">
-        <v>1667384.464868827</v>
+        <v>1702172.501028933</v>
       </c>
       <c r="I13">
-        <v>1560610.907264992</v>
+        <v>1607396.954120256</v>
       </c>
       <c r="J13">
-        <v>1600701.010251107</v>
+        <v>1635613.180596734</v>
       </c>
       <c r="K13">
-        <v>1596678.153895752</v>
+        <v>1631199.551447137</v>
       </c>
     </row>
     <row r="14">
@@ -838,34 +838,34 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>1527585.868418448</v>
+        <v>901718.5500303713</v>
       </c>
       <c r="C14">
-        <v>1531826.006929347</v>
+        <v>1531854.257598625</v>
       </c>
       <c r="D14">
-        <v>1663407.331125254</v>
+        <v>1700394.648843777</v>
       </c>
       <c r="E14">
-        <v>1670325.194054578</v>
+        <v>1706507.313264061</v>
       </c>
       <c r="F14">
-        <v>1579381.554661069</v>
+        <v>1616882.826255464</v>
       </c>
       <c r="G14">
-        <v>1694526.426524248</v>
+        <v>1722367.162747485</v>
       </c>
       <c r="H14">
-        <v>1690333.717850256</v>
+        <v>1717933.802891483</v>
       </c>
       <c r="I14">
-        <v>1587659.84232718</v>
+        <v>1624334.001609217</v>
       </c>
       <c r="J14">
-        <v>1621641.128553812</v>
+        <v>1649245.010712236</v>
       </c>
       <c r="K14">
-        <v>1617597.046606912</v>
+        <v>1644907.389095649</v>
       </c>
     </row>
     <row r="15">
@@ -873,34 +873,34 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>1584612.966891939</v>
+        <v>888390.6768410789</v>
       </c>
       <c r="C15">
-        <v>1587878.413829526</v>
+        <v>1583203.00571448</v>
       </c>
       <c r="D15">
-        <v>1690584.084220447</v>
+        <v>1718795.849432898</v>
       </c>
       <c r="E15">
-        <v>1696664.878336456</v>
+        <v>1724308.927174511</v>
       </c>
       <c r="F15">
-        <v>1610178.112844399</v>
+        <v>1638568.264238768</v>
       </c>
       <c r="G15">
-        <v>1715952.311971258</v>
+        <v>1737456.862871043</v>
       </c>
       <c r="H15">
-        <v>1711382.946418257</v>
+        <v>1732716.850301795</v>
       </c>
       <c r="I15">
-        <v>1617107.522503872</v>
+        <v>1644926.562525286</v>
       </c>
       <c r="J15">
-        <v>1645071.533115859</v>
+        <v>1666259.492352965</v>
       </c>
       <c r="K15">
-        <v>1640838.066585913</v>
+        <v>1661817.376438166</v>
       </c>
     </row>
     <row r="16">
@@ -908,34 +908,34 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>1635172.561065602</v>
+        <v>981569.5142356444</v>
       </c>
       <c r="C16">
-        <v>1637605.663476845</v>
+        <v>1629401.732022753</v>
       </c>
       <c r="D16">
-        <v>1711361.676988079</v>
+        <v>1732167.392494359</v>
       </c>
       <c r="E16">
-        <v>1717990.977736311</v>
+        <v>1738379.32349054</v>
       </c>
       <c r="F16">
-        <v>1633114.415591432</v>
+        <v>1653808.383699486</v>
       </c>
       <c r="G16">
-        <v>1732141.369235866</v>
+        <v>1748258.042383964</v>
       </c>
       <c r="H16">
-        <v>1727112.672678341</v>
+        <v>1743112.385196255</v>
       </c>
       <c r="I16">
-        <v>1639285.495502072</v>
+        <v>1659592.152758425</v>
       </c>
       <c r="J16">
-        <v>1661990.720728719</v>
+        <v>1677706.245656658</v>
       </c>
       <c r="K16">
-        <v>1657434.090097579</v>
+        <v>1673009.870165143</v>
       </c>
     </row>
     <row r="17">
@@ -943,34 +943,34 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>1669868.105105132</v>
+        <v>1034554.87736253</v>
       </c>
       <c r="C17">
-        <v>1670352.700684899</v>
+        <v>1659770.622450668</v>
       </c>
       <c r="D17">
-        <v>1720174.452767116</v>
+        <v>1735038.844794908</v>
       </c>
       <c r="E17">
-        <v>1728678.520302491</v>
+        <v>1743209.676154886</v>
       </c>
       <c r="F17">
-        <v>1643615.308469975</v>
+        <v>1658058.415845598</v>
       </c>
       <c r="G17">
-        <v>1736345.026421823</v>
+        <v>1748052.680716928</v>
       </c>
       <c r="H17">
-        <v>1730627.714186476</v>
+        <v>1742263.461214943</v>
       </c>
       <c r="I17">
-        <v>1650034.028927599</v>
+        <v>1664205.918991295</v>
       </c>
       <c r="J17">
-        <v>1668150.304258755</v>
+        <v>1679348.973491937</v>
       </c>
       <c r="K17">
-        <v>1663150.867575289</v>
+        <v>1674263.470778618</v>
       </c>
     </row>
     <row r="18">
@@ -978,34 +978,34 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>1683696.649711254</v>
+        <v>1049622.368220862</v>
       </c>
       <c r="C18">
-        <v>1682572.699718705</v>
+        <v>1670642.779906454</v>
       </c>
       <c r="D18">
-        <v>1715852.048868727</v>
+        <v>1725996.250543904</v>
       </c>
       <c r="E18">
-        <v>1726453.892183398</v>
+        <v>1736367.854317985</v>
       </c>
       <c r="F18">
-        <v>1645709.668253065</v>
+        <v>1655248.923249433</v>
       </c>
       <c r="G18">
-        <v>1729431.736092618</v>
+        <v>1737610.424744841</v>
       </c>
       <c r="H18">
-        <v>1723324.725879754</v>
+        <v>1731460.572325485</v>
       </c>
       <c r="I18">
-        <v>1653361.77708305</v>
+        <v>1662706.643301004</v>
       </c>
       <c r="J18">
-        <v>1667831.119733718</v>
+        <v>1675424.436233628</v>
       </c>
       <c r="K18">
-        <v>1662388.63861153</v>
+        <v>1669935.201539659</v>
       </c>
     </row>
     <row r="19">
@@ -1013,34 +1013,34 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>1689876.9430268</v>
+        <v>1076577.637160623</v>
       </c>
       <c r="C19">
-        <v>1687325.065500527</v>
+        <v>1674581.552374087</v>
       </c>
       <c r="D19">
-        <v>1708606.323510506</v>
+        <v>1715074.587633359</v>
       </c>
       <c r="E19">
-        <v>1721479.290652189</v>
+        <v>1727824.33954751</v>
       </c>
       <c r="F19">
-        <v>1645324.609606515</v>
+        <v>1651119.07532574</v>
       </c>
       <c r="G19">
-        <v>1720736.531874092</v>
+        <v>1726142.577674203</v>
       </c>
       <c r="H19">
-        <v>1714509.022361486</v>
+        <v>1719889.367337825</v>
       </c>
       <c r="I19">
-        <v>1654974.131609446</v>
+        <v>1660641.972263002</v>
       </c>
       <c r="J19">
-        <v>1666989.077539861</v>
+        <v>1671793.105709735</v>
       </c>
       <c r="K19">
-        <v>1661252.556716889</v>
+        <v>1666035.882189087</v>
       </c>
     </row>
     <row r="20">
@@ -1048,34 +1048,34 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>1686742.305265364</v>
+        <v>1082459.166607877</v>
       </c>
       <c r="C20">
-        <v>1683229.627046005</v>
+        <v>1670022.372067965</v>
       </c>
       <c r="D20">
-        <v>1695893.014214189</v>
+        <v>1699587.995495737</v>
       </c>
       <c r="E20">
-        <v>1711152.332085483</v>
+        <v>1714802.55420787</v>
       </c>
       <c r="F20">
-        <v>1636186.522494178</v>
+        <v>1639206.493166559</v>
       </c>
       <c r="G20">
-        <v>1708368.464874085</v>
+        <v>1711646.264907808</v>
       </c>
       <c r="H20">
-        <v>1701469.156449874</v>
+        <v>1704732.894297128</v>
       </c>
       <c r="I20">
-        <v>1648168.821542741</v>
+        <v>1651126.441944544</v>
       </c>
       <c r="J20">
-        <v>1659105.607028386</v>
+        <v>1661816.811380261</v>
       </c>
       <c r="K20">
-        <v>1653065.688606462</v>
+        <v>1655772.643490151</v>
       </c>
     </row>
     <row r="21">
@@ -1083,34 +1083,34 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>1680825.31298585</v>
+        <v>1062218.14905496</v>
       </c>
       <c r="C21">
-        <v>1676463.646040059</v>
+        <v>1663168.960975413</v>
       </c>
       <c r="D21">
-        <v>1685017.7215131</v>
+        <v>1686638.409333516</v>
       </c>
       <c r="E21">
-        <v>1702318.631006128</v>
+        <v>1703987.030085445</v>
       </c>
       <c r="F21">
-        <v>1628915.81537478</v>
+        <v>1629930.628762358</v>
       </c>
       <c r="G21">
-        <v>1698080.83334685</v>
+        <v>1699751.57738629</v>
       </c>
       <c r="H21">
-        <v>1691090.081492912</v>
+        <v>1692751.653960118</v>
       </c>
       <c r="I21">
-        <v>1643313.912584278</v>
+        <v>1644330.994389793</v>
       </c>
       <c r="J21">
-        <v>1654099.202598095</v>
+        <v>1655281.602803021</v>
       </c>
       <c r="K21">
-        <v>1647796.712088366</v>
+        <v>1648984.11469092</v>
       </c>
     </row>
     <row r="22">
@@ -1118,34 +1118,34 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>1672755.73121383</v>
+        <v>1061638.596907688</v>
       </c>
       <c r="C22">
-        <v>1667777.844718358</v>
+        <v>1653759.749012548</v>
       </c>
       <c r="D22">
-        <v>1673319.852322756</v>
+        <v>1673109.397128717</v>
       </c>
       <c r="E22">
-        <v>1690915.168500509</v>
+        <v>1690855.686284589</v>
       </c>
       <c r="F22">
-        <v>1617295.310623834</v>
+        <v>1616788.461600249</v>
       </c>
       <c r="G22">
-        <v>1688249.616328885</v>
+        <v>1688501.420178984</v>
       </c>
       <c r="H22">
-        <v>1680372.712463464</v>
+        <v>1680619.638777001</v>
       </c>
       <c r="I22">
-        <v>1633289.392660324</v>
+        <v>1632854.354608852</v>
       </c>
       <c r="J22">
-        <v>1644522.130944718</v>
+        <v>1644539.347889946</v>
       </c>
       <c r="K22">
-        <v>1637839.618514184</v>
+        <v>1637867.940167695</v>
       </c>
     </row>
     <row r="23">
@@ -1153,34 +1153,34 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>1689755.183095852</v>
+        <v>1061495.322254472</v>
       </c>
       <c r="C23">
-        <v>1684395.407988582</v>
+        <v>1669851.568079243</v>
       </c>
       <c r="D23">
-        <v>1684165.237357176</v>
+        <v>1682775.832619995</v>
       </c>
       <c r="E23">
-        <v>1697516.479002975</v>
+        <v>1696286.524111832</v>
       </c>
       <c r="F23">
-        <v>1618714.862720867</v>
+        <v>1617244.855341446</v>
       </c>
       <c r="G23">
-        <v>1698596.87537249</v>
+        <v>1697878.638680056</v>
       </c>
       <c r="H23">
-        <v>1690463.885655329</v>
+        <v>1689747.536611099</v>
       </c>
       <c r="I23">
-        <v>1634019.057938113</v>
+        <v>1632661.688731041</v>
       </c>
       <c r="J23">
-        <v>1645705.819997711</v>
+        <v>1644949.134945553</v>
       </c>
       <c r="K23">
-        <v>1638616.856239522</v>
+        <v>1637874.258902723</v>
       </c>
     </row>
     <row r="24">
@@ -1188,34 +1188,34 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>1713839.015574609</v>
+        <v>1042000.179848632</v>
       </c>
       <c r="C24">
-        <v>1708630.511913224</v>
+        <v>1693144.464658708</v>
       </c>
       <c r="D24">
-        <v>1706518.683792678</v>
+        <v>1704344.702297491</v>
       </c>
       <c r="E24">
-        <v>1715090.750733286</v>
+        <v>1713128.786399259</v>
       </c>
       <c r="F24">
-        <v>1633528.484898746</v>
+        <v>1631491.692850027</v>
       </c>
       <c r="G24">
-        <v>1722606.847634887</v>
+        <v>1721256.537212083</v>
       </c>
       <c r="H24">
-        <v>1713666.923403589</v>
+        <v>1712324.375782277</v>
       </c>
       <c r="I24">
-        <v>1645690.461405743</v>
+        <v>1643787.840842468</v>
       </c>
       <c r="J24">
-        <v>1658041.91966047</v>
+        <v>1656787.729599869</v>
       </c>
       <c r="K24">
-        <v>1650425.109251128</v>
+        <v>1649187.194436061</v>
       </c>
     </row>
     <row r="25">
@@ -1223,34 +1223,34 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>1796577.248254717</v>
+        <v>1144255.721064174</v>
       </c>
       <c r="C25">
-        <v>1788191.286696026</v>
+        <v>1773394.367615534</v>
       </c>
       <c r="D25">
-        <v>1770208.184428651</v>
+        <v>1767909.829127076</v>
       </c>
       <c r="E25">
-        <v>1775016.68484178</v>
+        <v>1772633.349692995</v>
       </c>
       <c r="F25">
-        <v>1665413.943775549</v>
+        <v>1663171.253477757</v>
       </c>
       <c r="G25">
-        <v>1775242.084214867</v>
+        <v>1773564.036117549</v>
       </c>
       <c r="H25">
-        <v>1765976.407948329</v>
+        <v>1764327.794577956</v>
       </c>
       <c r="I25">
-        <v>1673321.283160484</v>
+        <v>1671136.375961363</v>
       </c>
       <c r="J25">
-        <v>1683046.605390835</v>
+        <v>1681467.763413059</v>
       </c>
       <c r="K25">
-        <v>1674860.377223497</v>
+        <v>1673302.484020212</v>
       </c>
     </row>
     <row r="26">
@@ -1258,34 +1258,34 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>1840428.741117157</v>
+        <v>1164699.742726016</v>
       </c>
       <c r="C26">
-        <v>1830204.173689626</v>
+        <v>1815739.873388669</v>
       </c>
       <c r="D26">
-        <v>1806863.371380031</v>
+        <v>1804515.118804875</v>
       </c>
       <c r="E26">
-        <v>1808534.845349399</v>
+        <v>1805975.763316583</v>
       </c>
       <c r="F26">
-        <v>1702965.177343606</v>
+        <v>1700767.685145462</v>
       </c>
       <c r="G26">
-        <v>1807054.240619774</v>
+        <v>1805216.164091291</v>
       </c>
       <c r="H26">
-        <v>1797719.770650114</v>
+        <v>1795924.744615931</v>
       </c>
       <c r="I26">
-        <v>1706684.929745869</v>
+        <v>1704402.466233294</v>
       </c>
       <c r="J26">
-        <v>1711276.442209971</v>
+        <v>1709498.020209083</v>
       </c>
       <c r="K26">
-        <v>1702686.406981682</v>
+        <v>1700934.737368176</v>
       </c>
     </row>
     <row r="27">
@@ -1293,34 +1293,34 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>1882412.330821825</v>
+        <v>1267793.505790097</v>
       </c>
       <c r="C27">
-        <v>1869715.534904175</v>
+        <v>1855743.001330038</v>
       </c>
       <c r="D27">
-        <v>1841629.81916084</v>
+        <v>1839392.65560437</v>
       </c>
       <c r="E27">
-        <v>1839594.82758464</v>
+        <v>1837023.033985099</v>
       </c>
       <c r="F27">
-        <v>1746512.206965116</v>
+        <v>1744490.81164298</v>
       </c>
       <c r="G27">
-        <v>1836774.232787203</v>
+        <v>1834903.852818661</v>
       </c>
       <c r="H27">
-        <v>1827613.484414445</v>
+        <v>1825796.291715075</v>
       </c>
       <c r="I27">
-        <v>1746442.284330202</v>
+        <v>1744186.949615436</v>
       </c>
       <c r="J27">
-        <v>1745432.713801882</v>
+        <v>1743556.898730916</v>
       </c>
       <c r="K27">
-        <v>1736718.811109076</v>
+        <v>1734874.414058962</v>
       </c>
     </row>
     <row r="28">
@@ -1328,34 +1328,34 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>1907552.439357017</v>
+        <v>1301406.202671396</v>
       </c>
       <c r="C28">
-        <v>1893340.308934402</v>
+        <v>1879882.495785351</v>
       </c>
       <c r="D28">
-        <v>1862649.101368084</v>
+        <v>1860585.841026967</v>
       </c>
       <c r="E28">
-        <v>1856920.179539763</v>
+        <v>1854449.197930841</v>
       </c>
       <c r="F28">
-        <v>1780122.576354178</v>
+        <v>1778324.361619263</v>
       </c>
       <c r="G28">
-        <v>1855885.016716788</v>
+        <v>1854059.38431473</v>
       </c>
       <c r="H28">
-        <v>1846555.536550738</v>
+        <v>1844790.634151419</v>
       </c>
       <c r="I28">
-        <v>1776386.450068044</v>
+        <v>1774239.834921261</v>
       </c>
       <c r="J28">
-        <v>1771162.650219527</v>
+        <v>1769272.389867575</v>
       </c>
       <c r="K28">
-        <v>1762442.761140957</v>
+        <v>1760587.41805527</v>
       </c>
     </row>
     <row r="29">
@@ -1363,34 +1363,34 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>1914529.21530383</v>
+        <v>1450423.038763444</v>
       </c>
       <c r="C29">
-        <v>1897255.979948272</v>
+        <v>1884211.248950023</v>
       </c>
       <c r="D29">
-        <v>1864763.599534484</v>
+        <v>1862895.555443952</v>
       </c>
       <c r="E29">
-        <v>1856243.995714896</v>
+        <v>1853916.895184098</v>
       </c>
       <c r="F29">
-        <v>1792384.763499172</v>
+        <v>1790810.399180993</v>
       </c>
       <c r="G29">
-        <v>1855379.344028385</v>
+        <v>1853638.849353031</v>
       </c>
       <c r="H29">
-        <v>1846389.476976266</v>
+        <v>1844713.531949551</v>
       </c>
       <c r="I29">
-        <v>1785064.54916834</v>
+        <v>1783068.925906775</v>
       </c>
       <c r="J29">
-        <v>1777009.60352657</v>
+        <v>1775164.229922712</v>
       </c>
       <c r="K29">
-        <v>1768417.328544835</v>
+        <v>1766608.458318428</v>
       </c>
     </row>
     <row r="30">
@@ -1398,34 +1398,34 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>1930183.090111142</v>
+        <v>1521710.779742735</v>
       </c>
       <c r="C30">
-        <v>1908859.329166343</v>
+        <v>1896055.957726542</v>
       </c>
       <c r="D30">
-        <v>1873920.781377375</v>
+        <v>1872246.602601638</v>
       </c>
       <c r="E30">
-        <v>1864397.729750885</v>
+        <v>1862227.866787384</v>
       </c>
       <c r="F30">
-        <v>1808452.650868334</v>
+        <v>1807081.306851369</v>
       </c>
       <c r="G30">
-        <v>1862894.062118214</v>
+        <v>1861250.70474362</v>
       </c>
       <c r="H30">
-        <v>1853781.621696417</v>
+        <v>1852206.263755197</v>
       </c>
       <c r="I30">
-        <v>1798657.19051268</v>
+        <v>1796822.500275422</v>
       </c>
       <c r="J30">
-        <v>1788765.080867093</v>
+        <v>1786994.772498532</v>
       </c>
       <c r="K30">
-        <v>1780291.068708601</v>
+        <v>1778558.425972192</v>
       </c>
     </row>
     <row r="31">
@@ -1433,34 +1433,34 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>1932244.218389702</v>
+        <v>1638199.982845559</v>
       </c>
       <c r="C31">
-        <v>1905865.251304342</v>
+        <v>1893326.325043587</v>
       </c>
       <c r="D31">
-        <v>1869612.269094626</v>
+        <v>1868119.144034192</v>
       </c>
       <c r="E31">
-        <v>1861635.855833285</v>
+        <v>1859606.912612437</v>
       </c>
       <c r="F31">
-        <v>1809218.287064321</v>
+        <v>1808024.45145259</v>
       </c>
       <c r="G31">
-        <v>1857582.266539839</v>
+        <v>1856042.205120087</v>
       </c>
       <c r="H31">
-        <v>1848958.705588775</v>
+        <v>1847488.868304218</v>
       </c>
       <c r="I31">
-        <v>1798715.746137056</v>
+        <v>1797030.595193729</v>
       </c>
       <c r="J31">
-        <v>1787624.269963574</v>
+        <v>1785940.484227858</v>
       </c>
       <c r="K31">
-        <v>1779380.016047775</v>
+        <v>1777734.428226911</v>
       </c>
     </row>
     <row r="32">
@@ -1468,34 +1468,34 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>1905435.015971922</v>
+        <v>1666184.113756764</v>
       </c>
       <c r="C32">
-        <v>1874452.587898443</v>
+        <v>1862429.758413686</v>
       </c>
       <c r="D32">
-        <v>1840511.260670429</v>
+        <v>1839163.319143118</v>
       </c>
       <c r="E32">
-        <v>1835924.191206905</v>
+        <v>1834063.70587406</v>
       </c>
       <c r="F32">
-        <v>1790042.303175352</v>
+        <v>1788993.815766329</v>
       </c>
       <c r="G32">
-        <v>1828885.437383896</v>
+        <v>1827452.379526015</v>
       </c>
       <c r="H32">
-        <v>1820677.204366626</v>
+        <v>1819310.37168365</v>
       </c>
       <c r="I32">
-        <v>1780881.292240382</v>
+        <v>1779334.303869006</v>
       </c>
       <c r="J32">
-        <v>1769372.255181461</v>
+        <v>1767784.257352815</v>
       </c>
       <c r="K32">
-        <v>1761493.122117134</v>
+        <v>1759942.420520955</v>
       </c>
     </row>
     <row r="33">
@@ -1503,34 +1503,34 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>1869900.081442137</v>
+        <v>1714412.704342731</v>
       </c>
       <c r="C33">
-        <v>1833848.988781691</v>
+        <v>1822301.320511949</v>
       </c>
       <c r="D33">
-        <v>1802829.313133263</v>
+        <v>1801603.971666237</v>
       </c>
       <c r="E33">
-        <v>1802961.671086474</v>
+        <v>1801258.325597063</v>
       </c>
       <c r="F33">
-        <v>1760805.058020875</v>
+        <v>1759869.390765881</v>
       </c>
       <c r="G33">
-        <v>1792810.142771489</v>
+        <v>1791481.992123283</v>
       </c>
       <c r="H33">
-        <v>1785007.928291604</v>
+        <v>1783739.964701444</v>
       </c>
       <c r="I33">
-        <v>1755003.492783483</v>
+        <v>1753587.768273915</v>
       </c>
       <c r="J33">
-        <v>1743970.529143021</v>
+        <v>1742491.159947062</v>
       </c>
       <c r="K33">
-        <v>1736529.938454762</v>
+        <v>1735085.74627906</v>
       </c>
     </row>
     <row r="34">
@@ -1538,34 +1538,34 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>1812152.837832744</v>
+        <v>1692349.21678885</v>
       </c>
       <c r="C34">
-        <v>1772011.430039798</v>
+        <v>1761246.936553194</v>
       </c>
       <c r="D34">
-        <v>1746285.714253421</v>
+        <v>1745169.525941786</v>
       </c>
       <c r="E34">
-        <v>1750623.991041695</v>
+        <v>1749127.253777762</v>
       </c>
       <c r="F34">
-        <v>1714294.366510733</v>
+        <v>1713444.451489426</v>
       </c>
       <c r="G34">
-        <v>1739938.208122981</v>
+        <v>1738726.494478504</v>
       </c>
       <c r="H34">
-        <v>1732439.630011292</v>
+        <v>1731276.663562242</v>
       </c>
       <c r="I34">
-        <v>1712899.93650527</v>
+        <v>1711625.994800782</v>
       </c>
       <c r="J34">
-        <v>1703675.077030068</v>
+        <v>1702328.385556076</v>
       </c>
       <c r="K34">
-        <v>1696690.279267278</v>
+        <v>1695374.480997774</v>
       </c>
     </row>
     <row r="35">
@@ -1573,34 +1573,34 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>1746820.065129069</v>
+        <v>1668947.986803269</v>
       </c>
       <c r="C35">
-        <v>1703275.031899427</v>
+        <v>1693445.164448718</v>
       </c>
       <c r="D35">
-        <v>1684842.912232699</v>
+        <v>1683815.986489004</v>
       </c>
       <c r="E35">
-        <v>1691774.324864715</v>
+        <v>1690506.395117234</v>
       </c>
       <c r="F35">
-        <v>1660382.358677209</v>
+        <v>1659589.67968068</v>
       </c>
       <c r="G35">
-        <v>1682950.951644951</v>
+        <v>1681857.735164848</v>
       </c>
       <c r="H35">
-        <v>1675851.067304496</v>
+        <v>1674790.931832397</v>
       </c>
       <c r="I35">
-        <v>1663187.035705631</v>
+        <v>1662066.964728114</v>
       </c>
       <c r="J35">
-        <v>1657102.198810226</v>
+        <v>1655913.701720715</v>
       </c>
       <c r="K35">
-        <v>1650578.360792035</v>
+        <v>1649414.119219723</v>
       </c>
     </row>
     <row r="36">
@@ -1608,34 +1608,34 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>1682684.196537743</v>
+        <v>1617212.672778848</v>
       </c>
       <c r="C36">
-        <v>1635522.781699583</v>
+        <v>1626470.936505792</v>
       </c>
       <c r="D36">
-        <v>1623190.474159648</v>
+        <v>1622239.418693332</v>
       </c>
       <c r="E36">
-        <v>1630430.748180967</v>
+        <v>1629380.658370008</v>
       </c>
       <c r="F36">
-        <v>1599183.777281201</v>
+        <v>1598426.169864062</v>
       </c>
       <c r="G36">
-        <v>1626322.781715876</v>
+        <v>1625337.097381479</v>
       </c>
       <c r="H36">
-        <v>1619437.384098002</v>
+        <v>1618470.162722607</v>
       </c>
       <c r="I36">
-        <v>1604741.106116495</v>
+        <v>1603781.162616617</v>
       </c>
       <c r="J36">
-        <v>1602875.557881142</v>
+        <v>1601860.95095938</v>
       </c>
       <c r="K36">
-        <v>1596760.576835921</v>
+        <v>1595762.403322328</v>
       </c>
     </row>
     <row r="37">
@@ -1643,34 +1643,34 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>1616567.954201521</v>
+        <v>1594906.500456267</v>
       </c>
       <c r="C37">
-        <v>1565671.119195798</v>
+        <v>1557324.166979956</v>
       </c>
       <c r="D37">
-        <v>1558841.175411629</v>
+        <v>1557957.338431749</v>
       </c>
       <c r="E37">
-        <v>1565383.897371504</v>
+        <v>1564527.27790542</v>
       </c>
       <c r="F37">
-        <v>1529418.934270248</v>
+        <v>1528681.82222751</v>
       </c>
       <c r="G37">
-        <v>1565251.749419146</v>
+        <v>1564361.403319348</v>
       </c>
       <c r="H37">
-        <v>1558756.128732306</v>
+        <v>1557871.117547043</v>
       </c>
       <c r="I37">
-        <v>1535852.631763204</v>
+        <v>1535047.390170644</v>
       </c>
       <c r="J37">
-        <v>1538382.584547921</v>
+        <v>1537543.476046781</v>
       </c>
       <c r="K37">
-        <v>1532634.70804703</v>
+        <v>1531803.864370184</v>
       </c>
     </row>
     <row r="38">
@@ -1678,34 +1678,34 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>1569036.083339877</v>
+        <v>1558251.931941019</v>
       </c>
       <c r="C38">
-        <v>1515925.272778413</v>
+        <v>1508074.120261069</v>
       </c>
       <c r="D38">
-        <v>1512944.403129734</v>
+        <v>1512107.510441453</v>
       </c>
       <c r="E38">
-        <v>1518703.067347227</v>
+        <v>1517984.135720926</v>
       </c>
       <c r="F38">
-        <v>1474520.541182145</v>
+        <v>1473791.515264769</v>
       </c>
       <c r="G38">
-        <v>1522837.74170199</v>
+        <v>1522019.277914398</v>
       </c>
       <c r="H38">
-        <v>1516596.790178872</v>
+        <v>1515773.977924564</v>
       </c>
       <c r="I38">
-        <v>1480757.297599907</v>
+        <v>1480080.841982332</v>
       </c>
       <c r="J38">
-        <v>1487468.551576475</v>
+        <v>1486784.755649604</v>
       </c>
       <c r="K38">
-        <v>1482028.71713274</v>
+        <v>1481345.805602336</v>
       </c>
     </row>
     <row r="39">
@@ -1713,34 +1713,34 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>1518153.766470484</v>
+        <v>1549763.276705549</v>
       </c>
       <c r="C39">
-        <v>1466492.881840924</v>
+        <v>1459097.803891775</v>
       </c>
       <c r="D39">
-        <v>1467917.227391018</v>
+        <v>1467100.969971821</v>
       </c>
       <c r="E39">
-        <v>1472237.3444704</v>
+        <v>1471641.914395955</v>
       </c>
       <c r="F39">
-        <v>1424274.824231292</v>
+        <v>1423544.280011271</v>
       </c>
       <c r="G39">
-        <v>1481108.420469707</v>
+        <v>1480346.141556424</v>
       </c>
       <c r="H39">
-        <v>1475242.699715263</v>
+        <v>1474465.843225085</v>
       </c>
       <c r="I39">
-        <v>1429656.214283217</v>
+        <v>1429080.905522269</v>
       </c>
       <c r="J39">
-        <v>1440152.617852858</v>
+        <v>1439597.843974123</v>
       </c>
       <c r="K39">
-        <v>1434983.722906676</v>
+        <v>1434423.524257608</v>
       </c>
     </row>
     <row r="40">
@@ -1748,34 +1748,34 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>1452980.941618328</v>
+        <v>1484815.797158656</v>
       </c>
       <c r="C40">
-        <v>1407408.586749829</v>
+        <v>1400316.500860603</v>
       </c>
       <c r="D40">
-        <v>1412640.279900028</v>
+        <v>1411827.343556745</v>
       </c>
       <c r="E40">
-        <v>1414695.019955705</v>
+        <v>1414205.222784233</v>
       </c>
       <c r="F40">
-        <v>1365434.537082157</v>
+        <v>1364691.630113311</v>
       </c>
       <c r="G40">
-        <v>1429775.463988561</v>
+        <v>1429051.325666196</v>
       </c>
       <c r="H40">
-        <v>1423808.295964359</v>
+        <v>1423061.233583114</v>
       </c>
       <c r="I40">
-        <v>1369091.890876026</v>
+        <v>1368596.220118366</v>
       </c>
       <c r="J40">
-        <v>1383265.527262751</v>
+        <v>1382815.202401049</v>
       </c>
       <c r="K40">
-        <v>1378217.413092992</v>
+        <v>1377756.800849423</v>
       </c>
     </row>
     <row r="41">
@@ -1783,34 +1783,34 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>1411014.202769245</v>
+        <v>1446565.893450296</v>
       </c>
       <c r="C41">
-        <v>1379023.49982292</v>
+        <v>1371886.238168016</v>
       </c>
       <c r="D41">
-        <v>1386717.260794467</v>
+        <v>1385885.505924863</v>
       </c>
       <c r="E41">
-        <v>1386410.39387775</v>
+        <v>1385975.350988338</v>
       </c>
       <c r="F41">
-        <v>1333414.90010482</v>
+        <v>1332644.639166508</v>
       </c>
       <c r="G41">
-        <v>1406142.6494514</v>
+        <v>1405428.382973445</v>
       </c>
       <c r="H41">
-        <v>1400229.469534991</v>
+        <v>1399486.238609134</v>
       </c>
       <c r="I41">
-        <v>1334939.868835353</v>
+        <v>1334497.286533998</v>
       </c>
       <c r="J41">
-        <v>1352403.452657085</v>
+        <v>1352029.028340924</v>
       </c>
       <c r="K41">
-        <v>1347366.240499512</v>
+        <v>1346977.676518231</v>
       </c>
     </row>
     <row r="42">
@@ -1818,34 +1818,34 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>1375168.034000436</v>
+        <v>1385353.312730714</v>
       </c>
       <c r="C42">
-        <v>1365307.357326655</v>
+        <v>1357472.983805289</v>
       </c>
       <c r="D42">
-        <v>1372672.791599431</v>
+        <v>1371796.196977366</v>
       </c>
       <c r="E42">
-        <v>1372018.549129233</v>
+        <v>1371571.719692845</v>
       </c>
       <c r="F42">
-        <v>1311517.802862228</v>
+        <v>1310702.787855237</v>
       </c>
       <c r="G42">
-        <v>1393742.189392856</v>
+        <v>1392996.530420437</v>
       </c>
       <c r="H42">
-        <v>1387420.001649989</v>
+        <v>1386645.581849119</v>
       </c>
       <c r="I42">
-        <v>1311268.573685091</v>
+        <v>1310835.639244736</v>
       </c>
       <c r="J42">
-        <v>1331230.34338734</v>
+        <v>1330883.843006425</v>
       </c>
       <c r="K42">
-        <v>1325957.732793714</v>
+        <v>1325596.352092253</v>
       </c>
     </row>
     <row r="43">
@@ -1853,34 +1853,34 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>1343703.290737016</v>
+        <v>1309030.296095053</v>
       </c>
       <c r="C43">
-        <v>1356984.198496754</v>
+        <v>1347680.279899954</v>
       </c>
       <c r="D43">
-        <v>1362710.838988438</v>
+        <v>1361739.294091955</v>
       </c>
       <c r="E43">
-        <v>1364456.843128681</v>
+        <v>1363893.33719136</v>
       </c>
       <c r="F43">
-        <v>1294891.956593087</v>
+        <v>1294003.627078932</v>
       </c>
       <c r="G43">
-        <v>1383506.883291569</v>
+        <v>1382680.916008412</v>
       </c>
       <c r="H43">
-        <v>1377043.532055517</v>
+        <v>1376191.733500135</v>
       </c>
       <c r="I43">
-        <v>1294373.935741077</v>
+        <v>1293881.978078351</v>
       </c>
       <c r="J43">
-        <v>1315313.753356518</v>
+        <v>1314927.948805145</v>
       </c>
       <c r="K43">
-        <v>1309701.638912784</v>
+        <v>1309303.33022592</v>
       </c>
     </row>
     <row r="44">
@@ -1888,34 +1888,34 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>1320974.401836435</v>
+        <v>1223277.570196132</v>
       </c>
       <c r="C44">
-        <v>1354614.405499577</v>
+        <v>1343573.121111946</v>
       </c>
       <c r="D44">
-        <v>1360779.717944511</v>
+        <v>1359658.870416486</v>
       </c>
       <c r="E44">
-        <v>1366153.850097126</v>
+        <v>1365459.1350494</v>
       </c>
       <c r="F44">
-        <v>1295522.886404081</v>
+        <v>1294516.389661367</v>
       </c>
       <c r="G44">
-        <v>1382964.026198161</v>
+        <v>1382025.812477985</v>
       </c>
       <c r="H44">
-        <v>1376276.425141697</v>
+        <v>1375314.597278312</v>
       </c>
       <c r="I44">
-        <v>1296975.311432145</v>
+        <v>1296360.997351887</v>
       </c>
       <c r="J44">
-        <v>1318072.007029374</v>
+        <v>1317587.689019776</v>
       </c>
       <c r="K44">
-        <v>1312092.760539993</v>
+        <v>1311600.408494593</v>
       </c>
     </row>
     <row r="45">
@@ -1923,34 +1923,34 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>1300486.723581266</v>
+        <v>1127285.083034448</v>
       </c>
       <c r="C45">
-        <v>1345157.636044825</v>
+        <v>1332227.706161365</v>
       </c>
       <c r="D45">
-        <v>1353055.282065594</v>
+        <v>1351746.676922245</v>
       </c>
       <c r="E45">
-        <v>1362039.317736077</v>
+        <v>1361190.872696075</v>
       </c>
       <c r="F45">
-        <v>1293745.035117925</v>
+        <v>1292575.623508892</v>
       </c>
       <c r="G45">
-        <v>1376543.382396521</v>
+        <v>1375463.75282684</v>
       </c>
       <c r="H45">
-        <v>1369658.923845417</v>
+        <v>1368556.240635976</v>
       </c>
       <c r="I45">
-        <v>1298487.211083913</v>
+        <v>1297707.56387414</v>
       </c>
       <c r="J45">
-        <v>1319564.09977372</v>
+        <v>1318944.07012995</v>
       </c>
       <c r="K45">
-        <v>1313279.193563012</v>
+        <v>1312656.077646488</v>
       </c>
     </row>
     <row r="46">
@@ -1958,34 +1958,34 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>1283800.329738885</v>
+        <v>1022284.041124313</v>
       </c>
       <c r="C46">
-        <v>1330983.566537772</v>
+        <v>1315787.570762281</v>
       </c>
       <c r="D46">
-        <v>1343841.983908598</v>
+        <v>1342264.085008649</v>
       </c>
       <c r="E46">
-        <v>1355468.961435849</v>
+        <v>1354458.776686877</v>
       </c>
       <c r="F46">
-        <v>1293492.429261113</v>
+        <v>1292096.046282331</v>
       </c>
       <c r="G46">
-        <v>1371033.237045661</v>
+        <v>1369773.750681289</v>
       </c>
       <c r="H46">
-        <v>1363989.724436381</v>
+        <v>1362705.064209456</v>
       </c>
       <c r="I46">
-        <v>1301728.67574062</v>
+        <v>1300762.220228779</v>
       </c>
       <c r="J46">
-        <v>1324098.736010588</v>
+        <v>1323330.785243157</v>
       </c>
       <c r="K46">
-        <v>1317566.226764019</v>
+        <v>1316799.225043362</v>
       </c>
     </row>
     <row r="47">
@@ -1993,34 +1993,34 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>1283070.791689515</v>
+        <v>931090.4020805151</v>
       </c>
       <c r="C47">
-        <v>1327647.918195144</v>
+        <v>1309592.702670798</v>
       </c>
       <c r="D47">
-        <v>1347275.574238896</v>
+        <v>1345344.381664383</v>
       </c>
       <c r="E47">
-        <v>1360461.464273582</v>
+        <v>1359234.893582665</v>
       </c>
       <c r="F47">
-        <v>1302969.981186865</v>
+        <v>1301285.934388459</v>
       </c>
       <c r="G47">
-        <v>1378460.163933877</v>
+        <v>1376966.341543581</v>
       </c>
       <c r="H47">
-        <v>1371284.522047541</v>
+        <v>1369762.573546461</v>
       </c>
       <c r="I47">
-        <v>1314278.979719842</v>
+        <v>1313102.803234897</v>
       </c>
       <c r="J47">
-        <v>1338965.942013435</v>
+        <v>1338037.280782574</v>
       </c>
       <c r="K47">
-        <v>1332233.989027495</v>
+        <v>1331309.440402498</v>
       </c>
     </row>
     <row r="48">
@@ -2028,34 +2028,34 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>1282813.952124937</v>
+        <v>832424.7046348429</v>
       </c>
       <c r="C48">
-        <v>1320591.404550668</v>
+        <v>1299197.933856061</v>
       </c>
       <c r="D48">
-        <v>1349519.556194983</v>
+        <v>1347145.858844391</v>
       </c>
       <c r="E48">
-        <v>1363611.383971118</v>
+        <v>1362098.781357259</v>
       </c>
       <c r="F48">
-        <v>1308691.862023163</v>
+        <v>1306649.472589762</v>
       </c>
       <c r="G48">
-        <v>1384631.196330645</v>
+        <v>1382852.384964225</v>
       </c>
       <c r="H48">
-        <v>1377559.781046343</v>
+        <v>1375748.288484669</v>
       </c>
       <c r="I48">
-        <v>1322199.615810691</v>
+        <v>1320778.045366169</v>
       </c>
       <c r="J48">
-        <v>1350014.145260967</v>
+        <v>1348905.789449659</v>
       </c>
       <c r="K48">
-        <v>1343188.703742903</v>
+        <v>1342086.041716942</v>
       </c>
     </row>
     <row r="49">
@@ -2063,34 +2063,34 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>1293552.717777698</v>
+        <v>780681.2375642662</v>
       </c>
       <c r="C49">
-        <v>1317504.07039234</v>
+        <v>1292004.833873406</v>
       </c>
       <c r="D49">
-        <v>1356964.716590226</v>
+        <v>1354065.139626582</v>
       </c>
       <c r="E49">
-        <v>1371637.206598587</v>
+        <v>1369746.847672019</v>
       </c>
       <c r="F49">
-        <v>1316652.720313843</v>
+        <v>1314179.683462337</v>
       </c>
       <c r="G49">
-        <v>1395446.723088165</v>
+        <v>1393329.429799086</v>
       </c>
       <c r="H49">
-        <v>1388503.799361708</v>
+        <v>1386351.980709385</v>
       </c>
       <c r="I49">
-        <v>1331592.16287047</v>
+        <v>1329871.041025613</v>
       </c>
       <c r="J49">
-        <v>1362719.787270075</v>
+        <v>1361400.940663816</v>
       </c>
       <c r="K49">
-        <v>1355932.50219855</v>
+        <v>1354619.839384799</v>
       </c>
     </row>
     <row r="50">
@@ -2098,34 +2098,34 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>1318147.47092542</v>
+        <v>749234.7951164721</v>
       </c>
       <c r="C50">
-        <v>1312868.618159466</v>
+        <v>1284167.844213579</v>
       </c>
       <c r="D50">
-        <v>1360110.807073697</v>
+        <v>1356667.560280222</v>
       </c>
       <c r="E50">
-        <v>1374881.216731442</v>
+        <v>1372559.266320993</v>
       </c>
       <c r="F50">
-        <v>1317060.888952621</v>
+        <v>1314106.544940957</v>
       </c>
       <c r="G50">
-        <v>1400690.828012738</v>
+        <v>1398217.936728868</v>
       </c>
       <c r="H50">
-        <v>1393829.367355183</v>
+        <v>1391322.557960575</v>
       </c>
       <c r="I50">
-        <v>1332592.560874612</v>
+        <v>1330516.934528827</v>
       </c>
       <c r="J50">
-        <v>1366678.020078369</v>
+        <v>1365114.659933831</v>
       </c>
       <c r="K50">
-        <v>1359973.489125087</v>
+        <v>1358417.04237055</v>
       </c>
     </row>
     <row r="51">
@@ -2133,34 +2133,34 @@
         <v>2026</v>
       </c>
       <c r="B51">
-        <v>1345402.446141205</v>
+        <v>746446.7189821673</v>
       </c>
       <c r="C51">
-        <v>1332460.394947425</v>
+        <v>1301111.800076389</v>
       </c>
       <c r="D51">
-        <v>1385626.227713827</v>
+        <v>1381631.883699633</v>
       </c>
       <c r="E51">
-        <v>1400533.848824689</v>
+        <v>1397742.889292462</v>
       </c>
       <c r="F51">
-        <v>1339504.033585215</v>
+        <v>1336045.768264763</v>
       </c>
       <c r="G51">
-        <v>1427313.192779641</v>
+        <v>1424476.588603541</v>
       </c>
       <c r="H51">
-        <v>1420574.703299911</v>
+        <v>1417706.746425501</v>
       </c>
       <c r="I51">
-        <v>1355473.933341263</v>
+        <v>1352999.263755214</v>
       </c>
       <c r="J51">
-        <v>1391664.906841211</v>
+        <v>1389828.107844467</v>
       </c>
       <c r="K51">
-        <v>1385092.226454242</v>
+        <v>1383263.742715453</v>
       </c>
     </row>
     <row r="52">
@@ -2168,34 +2168,34 @@
         <v>2027</v>
       </c>
       <c r="B52">
-        <v>1373400.85586205</v>
+        <v>752994.5356302193</v>
       </c>
       <c r="C52">
-        <v>1354691.877058831</v>
+        <v>1321323.602399649</v>
       </c>
       <c r="D52">
-        <v>1412050.312478997</v>
+        <v>1407515.928455469</v>
       </c>
       <c r="E52">
-        <v>1427052.557096075</v>
+        <v>1423779.590614066</v>
       </c>
       <c r="F52">
-        <v>1363598.100626414</v>
+        <v>1359638.067888428</v>
       </c>
       <c r="G52">
-        <v>1453975.042676097</v>
+        <v>1450779.875612739</v>
       </c>
       <c r="H52">
-        <v>1447306.220151088</v>
+        <v>1444083.633984068</v>
       </c>
       <c r="I52">
-        <v>1379857.570055158</v>
+        <v>1376959.288213015</v>
       </c>
       <c r="J52">
-        <v>1417185.061603407</v>
+        <v>1415058.355604127</v>
       </c>
       <c r="K52">
-        <v>1410725.352469865</v>
+        <v>1408609.341044844</v>
       </c>
     </row>
     <row r="53">
@@ -2203,34 +2203,34 @@
         <v>2028</v>
       </c>
       <c r="B53">
-        <v>1402285.007272857</v>
+        <v>777869.1919079394</v>
       </c>
       <c r="C53">
-        <v>1379488.760394823</v>
+        <v>1344641.006184798</v>
       </c>
       <c r="D53">
-        <v>1439221.583013566</v>
+        <v>1434172.602516608</v>
       </c>
       <c r="E53">
-        <v>1454282.187383472</v>
+        <v>1450526.491501399</v>
       </c>
       <c r="F53">
-        <v>1389004.377143802</v>
+        <v>1384563.017082828</v>
       </c>
       <c r="G53">
-        <v>1480666.474743379</v>
+        <v>1477126.066772032</v>
       </c>
       <c r="H53">
-        <v>1474049.346956566</v>
+        <v>1470486.764957729</v>
       </c>
       <c r="I53">
-        <v>1405442.977227173</v>
+        <v>1402112.973093761</v>
       </c>
       <c r="J53">
-        <v>1443012.130843956</v>
+        <v>1440589.22291698</v>
       </c>
       <c r="K53">
-        <v>1436653.590106123</v>
+        <v>1434244.634432981</v>
       </c>
     </row>
     <row r="54">
@@ -2238,34 +2238,34 @@
         <v>2029</v>
       </c>
       <c r="B54">
-        <v>1430398.92426906</v>
+        <v>806481.855871847</v>
       </c>
       <c r="C54">
-        <v>1405078.606018007</v>
+        <v>1369228.299056347</v>
       </c>
       <c r="D54">
-        <v>1465913.377767833</v>
+        <v>1460382.423890098</v>
       </c>
       <c r="E54">
-        <v>1480951.356449856</v>
+        <v>1476728.933466701</v>
       </c>
       <c r="F54">
-        <v>1414697.414265834</v>
+        <v>1409805.671408514</v>
       </c>
       <c r="G54">
-        <v>1506396.996589872</v>
+        <v>1502531.265732845</v>
       </c>
       <c r="H54">
-        <v>1499810.116618858</v>
+        <v>1495928.109666928</v>
       </c>
       <c r="I54">
-        <v>1431216.462209982</v>
+        <v>1427462.879177955</v>
       </c>
       <c r="J54">
-        <v>1468325.81125503</v>
+        <v>1465611.615298769</v>
       </c>
       <c r="K54">
-        <v>1462048.848675905</v>
+        <v>1459352.433413012</v>
       </c>
     </row>
     <row r="55">
@@ -2273,34 +2273,34 @@
         <v>2030</v>
       </c>
       <c r="B55">
-        <v>1457719.382269657</v>
+        <v>843821.7767833391</v>
       </c>
       <c r="C55">
-        <v>1431009.287986596</v>
+        <v>1394517.866902331</v>
       </c>
       <c r="D55">
-        <v>1491880.898506762</v>
+        <v>1485905.363779446</v>
       </c>
       <c r="E55">
-        <v>1506855.862804561</v>
+        <v>1502189.35803503</v>
       </c>
       <c r="F55">
-        <v>1440050.355111224</v>
+        <v>1434745.57313762</v>
       </c>
       <c r="G55">
-        <v>1530987.588284003</v>
+        <v>1526819.687568379</v>
       </c>
       <c r="H55">
-        <v>1524428.732287201</v>
+        <v>1520250.862062269</v>
       </c>
       <c r="I55">
-        <v>1456591.447051275</v>
+        <v>1452432.716022603</v>
       </c>
       <c r="J55">
-        <v>1492688.642562954</v>
+        <v>1489695.126901611</v>
       </c>
       <c r="K55">
-        <v>1486479.067868928</v>
+        <v>1483507.511522908</v>
       </c>
     </row>
     <row r="56">
@@ -2308,34 +2308,34 @@
         <v>2031</v>
       </c>
       <c r="B56">
-        <v>1484166.390925437</v>
+        <v>882507.9919110867</v>
       </c>
       <c r="C56">
-        <v>1456861.840451044</v>
+        <v>1419992.171606449</v>
       </c>
       <c r="D56">
-        <v>1516893.400927806</v>
+        <v>1510512.916452179</v>
       </c>
       <c r="E56">
-        <v>1531796.119153213</v>
+        <v>1526713.080480675</v>
       </c>
       <c r="F56">
-        <v>1464499.563517853</v>
+        <v>1458821.953957669</v>
       </c>
       <c r="G56">
-        <v>1554405.298103259</v>
+        <v>1549959.87524624</v>
       </c>
       <c r="H56">
-        <v>1547850.153949961</v>
+        <v>1543401.38453214</v>
       </c>
       <c r="I56">
-        <v>1481035.10591112</v>
+        <v>1476496.958185941</v>
       </c>
       <c r="J56">
-        <v>1515773.054756401</v>
+        <v>1512517.068982627</v>
       </c>
       <c r="K56">
-        <v>1509609.585639154</v>
+        <v>1506379.943286193</v>
       </c>
     </row>
     <row r="57">
@@ -2343,34 +2343,34 @@
         <v>2032</v>
       </c>
       <c r="B57">
-        <v>1508914.861257694</v>
+        <v>926556.6712040878</v>
       </c>
       <c r="C57">
-        <v>1481674.517374607</v>
+        <v>1444641.199409629</v>
       </c>
       <c r="D57">
-        <v>1540379.877481796</v>
+        <v>1533633.796145508</v>
       </c>
       <c r="E57">
-        <v>1555323.133111032</v>
+        <v>1549855.091054088</v>
       </c>
       <c r="F57">
-        <v>1487454.775785225</v>
+        <v>1481444.678800993</v>
       </c>
       <c r="G57">
-        <v>1576073.919895494</v>
+        <v>1571376.682337395</v>
       </c>
       <c r="H57">
-        <v>1569536.078658976</v>
+        <v>1564841.96872911</v>
       </c>
       <c r="I57">
-        <v>1504015.868482961</v>
+        <v>1499128.946543589</v>
       </c>
       <c r="J57">
-        <v>1537151.60840371</v>
+        <v>1533653.936937336</v>
       </c>
       <c r="K57">
-        <v>1531028.284531349</v>
+        <v>1527561.247405791</v>
       </c>
     </row>
     <row r="58">
@@ -2378,34 +2378,34 @@
         <v>2033</v>
       </c>
       <c r="B58">
-        <v>1531590.178908889</v>
+        <v>965124.630204309</v>
       </c>
       <c r="C58">
-        <v>1504982.948768344</v>
+        <v>1467936.775688799</v>
       </c>
       <c r="D58">
-        <v>1562020.272407891</v>
+        <v>1554947.064395873</v>
       </c>
       <c r="E58">
-        <v>1577068.391799484</v>
+        <v>1571248.82048199</v>
       </c>
       <c r="F58">
-        <v>1508578.577620224</v>
+        <v>1502275.133045773</v>
       </c>
       <c r="G58">
-        <v>1596001.233779117</v>
+        <v>1591077.455710436</v>
       </c>
       <c r="H58">
-        <v>1589454.334525829</v>
+        <v>1584539.993985147</v>
       </c>
       <c r="I58">
-        <v>1525174.555866813</v>
+        <v>1519971.862326424</v>
       </c>
       <c r="J58">
-        <v>1556670.22005186</v>
+        <v>1552953.101299497</v>
       </c>
       <c r="K58">
-        <v>1550568.353123055</v>
+        <v>1546886.062002195</v>
       </c>
     </row>
     <row r="59">
@@ -2413,34 +2413,34 @@
         <v>2034</v>
       </c>
       <c r="B59">
-        <v>1551304.352683701</v>
+        <v>1005060.439898556</v>
       </c>
       <c r="C59">
-        <v>1525813.015892987</v>
+        <v>1488879.019232878</v>
       </c>
       <c r="D59">
-        <v>1581185.835036974</v>
+        <v>1573821.337841727</v>
       </c>
       <c r="E59">
-        <v>1596306.358465077</v>
+        <v>1590172.689197221</v>
       </c>
       <c r="F59">
-        <v>1527529.974597477</v>
+        <v>1520969.664291174</v>
       </c>
       <c r="G59">
-        <v>1613497.618552247</v>
+        <v>1608372.547959969</v>
       </c>
       <c r="H59">
-        <v>1606953.984045807</v>
+        <v>1601843.951040787</v>
       </c>
       <c r="I59">
-        <v>1544131.947801822</v>
+        <v>1538648.033583679</v>
       </c>
       <c r="J59">
-        <v>1573982.25134761</v>
+        <v>1570069.803201832</v>
       </c>
       <c r="K59">
-        <v>1567902.245406768</v>
+        <v>1564028.425438246</v>
       </c>
     </row>
     <row r="60">
@@ -2448,34 +2448,34 @@
         <v>2035</v>
       </c>
       <c r="B60">
-        <v>1569049.919588532</v>
+        <v>1038120.790530423</v>
       </c>
       <c r="C60">
-        <v>1544902.972877049</v>
+        <v>1508148.761012914</v>
       </c>
       <c r="D60">
-        <v>1598464.627621733</v>
+        <v>1590843.372008997</v>
       </c>
       <c r="E60">
-        <v>1613640.590718476</v>
+        <v>1607226.046785137</v>
       </c>
       <c r="F60">
-        <v>1544512.422136717</v>
+        <v>1537729.347289069</v>
       </c>
       <c r="G60">
-        <v>1629223.69380236</v>
+        <v>1623920.355244854</v>
       </c>
       <c r="H60">
-        <v>1622646.638444453</v>
+        <v>1617363.617266716</v>
       </c>
       <c r="I60">
-        <v>1561107.481255099</v>
+        <v>1555374.824312924</v>
       </c>
       <c r="J60">
-        <v>1589386.290426479</v>
+        <v>1585300.720585088</v>
       </c>
       <c r="K60">
-        <v>1583308.430593964</v>
+        <v>1579265.070423896</v>
       </c>
     </row>
     <row r="61">
@@ -2483,34 +2483,34 @@
         <v>2036</v>
       </c>
       <c r="B61">
-        <v>1585206.769125601</v>
+        <v>1071853.443040141</v>
       </c>
       <c r="C61">
-        <v>1562637.272034851</v>
+        <v>1526095.903051286</v>
       </c>
       <c r="D61">
-        <v>1614299.013100121</v>
+        <v>1606452.594028806</v>
       </c>
       <c r="E61">
-        <v>1629545.194532172</v>
+        <v>1622878.791818325</v>
       </c>
       <c r="F61">
-        <v>1559702.101361805</v>
+        <v>1552727.185017407</v>
       </c>
       <c r="G61">
-        <v>1643448.84143742</v>
+        <v>1637988.049001582</v>
       </c>
       <c r="H61">
-        <v>1636871.584581652</v>
+        <v>1631436.028445759</v>
       </c>
       <c r="I61">
-        <v>1576297.491308474</v>
+        <v>1570345.994326814</v>
       </c>
       <c r="J61">
-        <v>1603045.169254379</v>
+        <v>1598807.106424265</v>
       </c>
       <c r="K61">
-        <v>1596977.303648572</v>
+        <v>1592784.646128319</v>
       </c>
     </row>
     <row r="62">
@@ -2518,34 +2518,34 @@
         <v>2037</v>
       </c>
       <c r="B62">
-        <v>1599658.051104954</v>
+        <v>1101169.260002287</v>
       </c>
       <c r="C62">
-        <v>1578715.491355019</v>
+        <v>1542397.116273443</v>
       </c>
       <c r="D62">
-        <v>1628455.859716931</v>
+        <v>1620412.714561672</v>
       </c>
       <c r="E62">
-        <v>1643909.714838742</v>
+        <v>1637019.988651476</v>
       </c>
       <c r="F62">
-        <v>1573037.081441526</v>
+        <v>1565897.671274456</v>
       </c>
       <c r="G62">
-        <v>1656166.562836091</v>
+        <v>1650567.201914138</v>
       </c>
       <c r="H62">
-        <v>1649559.619152973</v>
+        <v>1643990.188278795</v>
       </c>
       <c r="I62">
-        <v>1589688.761773818</v>
+        <v>1583546.59252125</v>
       </c>
       <c r="J62">
-        <v>1615038.318603355</v>
+        <v>1610666.828277837</v>
       </c>
       <c r="K62">
-        <v>1608965.827441992</v>
+        <v>1604642.757077635</v>
       </c>
     </row>
     <row r="63">
@@ -2553,34 +2553,34 @@
         <v>2038</v>
       </c>
       <c r="B63">
-        <v>1612582.06900956</v>
+        <v>1128702.221755372</v>
       </c>
       <c r="C63">
-        <v>1592671.953094701</v>
+        <v>1556584.336366675</v>
       </c>
       <c r="D63">
-        <v>1640707.91791781</v>
+        <v>1632492.3652788</v>
       </c>
       <c r="E63">
-        <v>1656418.251521022</v>
+        <v>1649330.669118993</v>
       </c>
       <c r="F63">
-        <v>1584486.665295081</v>
+        <v>1577206.611574163</v>
       </c>
       <c r="G63">
-        <v>1667053.841215442</v>
+        <v>1661333.551018193</v>
       </c>
       <c r="H63">
-        <v>1660456.931041155</v>
+        <v>1654770.512930072</v>
       </c>
       <c r="I63">
-        <v>1601203.251839947</v>
+        <v>1594896.135957627</v>
       </c>
       <c r="J63">
-        <v>1625265.87286171</v>
+        <v>1620779.471739693</v>
       </c>
       <c r="K63">
-        <v>1619206.375600104</v>
+        <v>1614770.863498497</v>
       </c>
     </row>
     <row r="64">
@@ -2588,34 +2588,34 @@
         <v>2039</v>
       </c>
       <c r="B64">
-        <v>1623105.932015176</v>
+        <v>1152798.632209769</v>
       </c>
       <c r="C64">
-        <v>1603915.355469722</v>
+        <v>1568103.819645216</v>
       </c>
       <c r="D64">
-        <v>1650577.836013457</v>
+        <v>1642213.753611796</v>
       </c>
       <c r="E64">
-        <v>1666369.442723598</v>
+        <v>1659115.641955345</v>
       </c>
       <c r="F64">
-        <v>1594013.735541515</v>
+        <v>1586614.695488425</v>
       </c>
       <c r="G64">
-        <v>1675909.193709417</v>
+        <v>1670085.640698417</v>
       </c>
       <c r="H64">
-        <v>1669308.202112075</v>
+        <v>1663521.775761566</v>
       </c>
       <c r="I64">
-        <v>1610708.508548449</v>
+        <v>1604262.41580286</v>
       </c>
       <c r="J64">
-        <v>1633729.808963435</v>
+        <v>1629146.703199418</v>
       </c>
       <c r="K64">
-        <v>1627674.263441846</v>
+        <v>1623144.179368589</v>
       </c>
     </row>
     <row r="65">
@@ -2623,34 +2623,34 @@
         <v>2040</v>
       </c>
       <c r="B65">
-        <v>1632471.811536468</v>
+        <v>1174771.030180785</v>
       </c>
       <c r="C65">
-        <v>1613626.017956271</v>
+        <v>1578085.871663003</v>
       </c>
       <c r="D65">
-        <v>1659045.264133574</v>
+        <v>1650553.376640484</v>
       </c>
       <c r="E65">
-        <v>1674808.252204879</v>
+        <v>1667410.716884217</v>
       </c>
       <c r="F65">
-        <v>1602172.956059813</v>
+        <v>1594673.744630279</v>
       </c>
       <c r="G65">
-        <v>1683423.639097008</v>
+        <v>1677511.433344547</v>
       </c>
       <c r="H65">
-        <v>1676814.612244872</v>
+        <v>1670942.290657522</v>
       </c>
       <c r="I65">
-        <v>1618800.718059263</v>
+        <v>1612236.289374004</v>
       </c>
       <c r="J65">
-        <v>1640879.804012458</v>
+        <v>1636214.63624068</v>
       </c>
       <c r="K65">
-        <v>1634823.939516905</v>
+        <v>1630213.635009529</v>
       </c>
     </row>
     <row r="66">
@@ -2658,34 +2658,34 @@
         <v>2041</v>
       </c>
       <c r="B66">
-        <v>1640587.051066677</v>
+        <v>1194543.474463087</v>
       </c>
       <c r="C66">
-        <v>1622206.75273764</v>
+        <v>1586916.184974906</v>
       </c>
       <c r="D66">
-        <v>1666435.463740338</v>
+        <v>1657834.356420348</v>
       </c>
       <c r="E66">
-        <v>1682120.749356627</v>
+        <v>1674599.391731599</v>
       </c>
       <c r="F66">
-        <v>1609202.888985764</v>
+        <v>1601619.763040059</v>
       </c>
       <c r="G66">
-        <v>1689990.444110586</v>
+        <v>1684001.894403559</v>
       </c>
       <c r="H66">
-        <v>1683377.164049496</v>
+        <v>1677431.02886645</v>
       </c>
       <c r="I66">
-        <v>1625752.12240824</v>
+        <v>1619087.22720778</v>
       </c>
       <c r="J66">
-        <v>1647006.606786146</v>
+        <v>1642271.492416045</v>
       </c>
       <c r="K66">
-        <v>1640950.360157589</v>
+        <v>1636271.720175587</v>
       </c>
     </row>
     <row r="67">
@@ -2693,34 +2693,34 @@
         <v>2042</v>
       </c>
       <c r="B67">
-        <v>1647502.656848007</v>
+        <v>1212152.136171662</v>
       </c>
       <c r="C67">
-        <v>1629935.711848536</v>
+        <v>1594852.436191127</v>
       </c>
       <c r="D67">
-        <v>1673074.196822292</v>
+        <v>1664377.928281069</v>
       </c>
       <c r="E67">
-        <v>1688678.793657158</v>
+        <v>1681047.708410697</v>
       </c>
       <c r="F67">
-        <v>1615307.936915629</v>
+        <v>1607654.179330963</v>
       </c>
       <c r="G67">
-        <v>1695829.548788959</v>
+        <v>1689774.400450215</v>
       </c>
       <c r="H67">
-        <v>1689211.55318297</v>
+        <v>1683201.112196263</v>
       </c>
       <c r="I67">
-        <v>1631788.580695271</v>
+        <v>1625037.654648</v>
       </c>
       <c r="J67">
-        <v>1652291.408251481</v>
+        <v>1647496.337392867</v>
       </c>
       <c r="K67">
-        <v>1646232.797818531</v>
+        <v>1641495.609104194</v>
       </c>
     </row>
     <row r="68">
@@ -2728,34 +2728,34 @@
         <v>2043</v>
       </c>
       <c r="B68">
-        <v>1653379.218273162</v>
+        <v>1227696.118226856</v>
       </c>
       <c r="C68">
-        <v>1636659.818499878</v>
+        <v>1601776.198231654</v>
       </c>
       <c r="D68">
-        <v>1678840.517618298</v>
+        <v>1670063.505548972</v>
       </c>
       <c r="E68">
-        <v>1694412.644092173</v>
+        <v>1686686.345479551</v>
       </c>
       <c r="F68">
-        <v>1620505.259463834</v>
+        <v>1612793.042514989</v>
       </c>
       <c r="G68">
-        <v>1700838.141110142</v>
+        <v>1694726.650616325</v>
       </c>
       <c r="H68">
-        <v>1694230.941575968</v>
+        <v>1688166.103488994</v>
       </c>
       <c r="I68">
-        <v>1636946.403682351</v>
+        <v>1630122.889281203</v>
       </c>
       <c r="J68">
-        <v>1656774.673979582</v>
+        <v>1651929.082127056</v>
       </c>
       <c r="K68">
-        <v>1650719.402641219</v>
+        <v>1645932.840389838</v>
       </c>
     </row>
     <row r="69">
@@ -2763,34 +2763,34 @@
         <v>2044</v>
       </c>
       <c r="B69">
-        <v>1658786.438258412</v>
+        <v>1243507.708857208</v>
       </c>
       <c r="C69">
-        <v>1642626.044159678</v>
+        <v>1607909.621384173</v>
       </c>
       <c r="D69">
-        <v>1683864.970188591</v>
+        <v>1675020.523582955</v>
       </c>
       <c r="E69">
-        <v>1699430.569127376</v>
+        <v>1691622.212845563</v>
       </c>
       <c r="F69">
-        <v>1624922.616278231</v>
+        <v>1617162.462878498</v>
       </c>
       <c r="G69">
-        <v>1705192.601928136</v>
+        <v>1699033.488063553</v>
       </c>
       <c r="H69">
-        <v>1698574.682319202</v>
+        <v>1692464.199301753</v>
       </c>
       <c r="I69">
-        <v>1641340.181397992</v>
+        <v>1634455.783748878</v>
       </c>
       <c r="J69">
-        <v>1660584.719506729</v>
+        <v>1655696.529903945</v>
       </c>
       <c r="K69">
-        <v>1654523.675913993</v>
+        <v>1649695.624245166</v>
       </c>
     </row>
     <row r="70">
@@ -2798,34 +2798,34 @@
         <v>2045</v>
       </c>
       <c r="B70">
-        <v>1663204.427540736</v>
+        <v>1256416.707983745</v>
       </c>
       <c r="C70">
-        <v>1648155.726597074</v>
+        <v>1613706.384351025</v>
       </c>
       <c r="D70">
-        <v>1688281.142921372</v>
+        <v>1679384.66440401</v>
       </c>
       <c r="E70">
-        <v>1703840.484834897</v>
+        <v>1695965.410401384</v>
       </c>
       <c r="F70">
-        <v>1628673.334450709</v>
+        <v>1620875.432009999</v>
       </c>
       <c r="G70">
-        <v>1708970.172496852</v>
+        <v>1702773.478003036</v>
       </c>
       <c r="H70">
-        <v>1702340.800628921</v>
+        <v>1696194.420439694</v>
       </c>
       <c r="I70">
-        <v>1645071.038082518</v>
+        <v>1638137.170698769</v>
       </c>
       <c r="J70">
-        <v>1663798.948483688</v>
+        <v>1658875.983068819</v>
       </c>
       <c r="K70">
-        <v>1657732.147912338</v>
+        <v>1652870.239957512</v>
       </c>
     </row>
     <row r="71">
@@ -2833,34 +2833,34 @@
         <v>2046</v>
       </c>
       <c r="B71">
-        <v>1666815.181115526</v>
+        <v>1266960.026278763</v>
       </c>
       <c r="C71">
-        <v>1652672.743036455</v>
+        <v>1618441.179824959</v>
       </c>
       <c r="D71">
-        <v>1691889.652815183</v>
+        <v>1682950.622885155</v>
       </c>
       <c r="E71">
-        <v>1707443.935819636</v>
+        <v>1699514.325657411</v>
       </c>
       <c r="F71">
-        <v>1631738.354177758</v>
+        <v>1623909.575039271</v>
       </c>
       <c r="G71">
-        <v>1712057.267835197</v>
+        <v>1705829.844626161</v>
       </c>
       <c r="H71">
-        <v>1705418.567106208</v>
+        <v>1699242.833237847</v>
       </c>
       <c r="I71">
-        <v>1648119.877152602</v>
+        <v>1641145.567572495</v>
       </c>
       <c r="J71">
-        <v>1666425.938158198</v>
+        <v>1661474.544319566</v>
       </c>
       <c r="K71">
-        <v>1660354.457113287</v>
+        <v>1655464.871875841</v>
       </c>
     </row>
     <row r="72">
@@ -2868,34 +2868,34 @@
         <v>2047</v>
       </c>
       <c r="B72">
-        <v>1669766.913069358</v>
+        <v>1275574.071436738</v>
       </c>
       <c r="C72">
-        <v>1656363.701759709</v>
+        <v>1622309.815172194</v>
       </c>
       <c r="D72">
-        <v>1694839.014761047</v>
+        <v>1685865.18100878</v>
       </c>
       <c r="E72">
-        <v>1710389.200917635</v>
+        <v>1702415.003023657</v>
       </c>
       <c r="F72">
-        <v>1634243.686845085</v>
+        <v>1626389.648865437</v>
       </c>
       <c r="G72">
-        <v>1714580.738419822</v>
+        <v>1708328.184643916</v>
       </c>
       <c r="H72">
-        <v>1707934.433306772</v>
+        <v>1701734.692356965</v>
       </c>
       <c r="I72">
-        <v>1650612.018983929</v>
+        <v>1643604.640553864</v>
       </c>
       <c r="J72">
-        <v>1668573.494929403</v>
+        <v>1663598.856592528</v>
       </c>
       <c r="K72">
-        <v>1662498.205050596</v>
+        <v>1657585.989097076</v>
       </c>
     </row>
     <row r="73">
@@ -2903,34 +2903,34 @@
         <v>2048</v>
       </c>
       <c r="B73">
-        <v>1672180.413556404</v>
+        <v>1282613.904652007</v>
       </c>
       <c r="C73">
-        <v>1659380.486048513</v>
+        <v>1625471.627805203</v>
       </c>
       <c r="D73">
-        <v>1697250.199224613</v>
+        <v>1688247.894703216</v>
       </c>
       <c r="E73">
-        <v>1712797.062902596</v>
+        <v>1704786.403596247</v>
       </c>
       <c r="F73">
-        <v>1636291.995287633</v>
+        <v>1628417.29181834</v>
       </c>
       <c r="G73">
-        <v>1716643.941987599</v>
+        <v>1710370.83275901</v>
       </c>
       <c r="H73">
-        <v>1709991.4344972</v>
+        <v>1703772.056306767</v>
       </c>
       <c r="I73">
-        <v>1652649.567685329</v>
+        <v>1645615.144663647</v>
       </c>
       <c r="J73">
-        <v>1670329.482186053</v>
+        <v>1665335.834516261</v>
       </c>
       <c r="K73">
-        <v>1664251.090256252</v>
+        <v>1659320.366646398</v>
       </c>
     </row>
     <row r="74">
@@ -2938,34 +2938,34 @@
         <v>2049</v>
       </c>
       <c r="B74">
-        <v>1674154.184484412</v>
+        <v>1288368.647501792</v>
       </c>
       <c r="C74">
-        <v>1661846.814143227</v>
+        <v>1628056.384317704</v>
       </c>
       <c r="D74">
-        <v>1699221.80925446</v>
+        <v>1690196.211885541</v>
       </c>
       <c r="E74">
-        <v>1714765.97508153</v>
+        <v>1706725.49465592</v>
       </c>
       <c r="F74">
-        <v>1637966.975757514</v>
+        <v>1630075.363175519</v>
       </c>
       <c r="G74">
-        <v>1718331.149303975</v>
+        <v>1712041.224587239</v>
       </c>
       <c r="H74">
-        <v>1711673.580342996</v>
+        <v>1705438.137291261</v>
       </c>
       <c r="I74">
-        <v>1654315.767013132</v>
+        <v>1647259.222817699</v>
       </c>
       <c r="J74">
-        <v>1671765.553788616</v>
+        <v>1666756.357851724</v>
       </c>
       <c r="K74">
-        <v>1665684.633641874</v>
+        <v>1660738.771906974</v>
       </c>
     </row>
     <row r="75">
@@ -2973,34 +2973,34 @@
         <v>2050</v>
       </c>
       <c r="B75">
-        <v>1675768.595659149</v>
+        <v>1293073.900755944</v>
       </c>
       <c r="C75">
-        <v>1663863.531711849</v>
+        <v>1630169.843893816</v>
       </c>
       <c r="D75">
-        <v>1700834.264705527</v>
+        <v>1691789.608778643</v>
       </c>
       <c r="E75">
-        <v>1716376.237479083</v>
+        <v>1708311.363403432</v>
       </c>
       <c r="F75">
-        <v>1639336.90139912</v>
+        <v>1631431.45210655</v>
       </c>
       <c r="G75">
-        <v>1719711.107814241</v>
+        <v>1713407.425530539</v>
       </c>
       <c r="H75">
-        <v>1713049.406574043</v>
+        <v>1706800.819712149</v>
       </c>
       <c r="I75">
-        <v>1655678.523128049</v>
+        <v>1648603.882491703</v>
       </c>
       <c r="J75">
-        <v>1672940.175812812</v>
+        <v>1667918.260783868</v>
       </c>
       <c r="K75">
-        <v>1666857.193860475</v>
+        <v>1661898.948409447</v>
       </c>
     </row>
   </sheetData>
@@ -3075,34 +3075,34 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>746657.9289938222</v>
+        <v>62364.59472978051</v>
       </c>
       <c r="C2">
-        <v>753086.043682688</v>
+        <v>865655.540296633</v>
       </c>
       <c r="D2">
-        <v>880427.1949234953</v>
+        <v>997697.1846835625</v>
       </c>
       <c r="E2">
-        <v>893648.584689917</v>
+        <v>1005647.989079899</v>
       </c>
       <c r="F2">
-        <v>921122.040536306</v>
+        <v>1040103.932523131</v>
       </c>
       <c r="G2">
-        <v>925849.7824650558</v>
+        <v>1010494.309239701</v>
       </c>
       <c r="H2">
-        <v>923055.4278914541</v>
+        <v>1006811.882464956</v>
       </c>
       <c r="I2">
-        <v>935760.8743012613</v>
+        <v>1049219.277503587</v>
       </c>
       <c r="J2">
-        <v>979156.4147357706</v>
+        <v>1061754.083075394</v>
       </c>
       <c r="K2">
-        <v>976455.7365017</v>
+        <v>1058045.513188309</v>
       </c>
     </row>
     <row r="3">
@@ -3110,34 +3110,34 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>738622.5683549435</v>
+        <v>53928.80035483077</v>
       </c>
       <c r="C3">
-        <v>745066.2494082984</v>
+        <v>857628.3215057408</v>
       </c>
       <c r="D3">
-        <v>872406.2252106979</v>
+        <v>989670.3702532416</v>
       </c>
       <c r="E3">
-        <v>885913.0115364321</v>
+        <v>997906.930210989</v>
       </c>
       <c r="F3">
-        <v>913005.3676746022</v>
+        <v>1031984.260192824</v>
       </c>
       <c r="G3">
-        <v>917814.8105874883</v>
+        <v>1002455.130947718</v>
       </c>
       <c r="H3">
-        <v>915028.0678680805</v>
+        <v>998780.3702523578</v>
       </c>
       <c r="I3">
-        <v>927877.093843863</v>
+        <v>1041332.767979849</v>
       </c>
       <c r="J3">
-        <v>971259.8936263336</v>
+        <v>1053855.544843016</v>
       </c>
       <c r="K3">
-        <v>968567.9899867006</v>
+        <v>1050155.774366223</v>
       </c>
     </row>
     <row r="4">
@@ -3145,34 +3145,34 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>732061.3445646089</v>
+        <v>48040.04732387535</v>
       </c>
       <c r="C4">
-        <v>738485.9784267005</v>
+        <v>851001.8721239197</v>
       </c>
       <c r="D4">
-        <v>865847.3070930016</v>
+        <v>983081.3300005861</v>
       </c>
       <c r="E4">
-        <v>879328.4807740821</v>
+        <v>991293.8797798306</v>
       </c>
       <c r="F4">
-        <v>906394.9262168586</v>
+        <v>1025352.968913222</v>
       </c>
       <c r="G4">
-        <v>911254.5575682146</v>
+        <v>995873.3109972097</v>
       </c>
       <c r="H4">
-        <v>908470.1627575159</v>
+        <v>992201.1202456681</v>
       </c>
       <c r="I4">
-        <v>921173.0970326567</v>
+        <v>1034609.10940068</v>
       </c>
       <c r="J4">
-        <v>964558.4522363336</v>
+        <v>1047139.849206934</v>
       </c>
       <c r="K4">
-        <v>961867.7193650826</v>
+        <v>1043441.417255782</v>
       </c>
     </row>
     <row r="5">
@@ -3180,34 +3180,34 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>726768.8276789418</v>
+        <v>45032.88761419791</v>
       </c>
       <c r="C5">
-        <v>733152.8256860431</v>
+        <v>845443.7193313029</v>
       </c>
       <c r="D5">
-        <v>860632.0365531354</v>
+        <v>977720.9599896488</v>
       </c>
       <c r="E5">
-        <v>873893.5697923281</v>
+        <v>985721.6090575742</v>
       </c>
       <c r="F5">
-        <v>901169.7293237122</v>
+        <v>1020007.988874465</v>
       </c>
       <c r="G5">
-        <v>906033.4044548087</v>
+        <v>990548.3380385573</v>
       </c>
       <c r="H5">
-        <v>903248.0633332147</v>
+        <v>986876.2244799833</v>
       </c>
       <c r="I5">
-        <v>915656.7543588041</v>
+        <v>1028979.545275669</v>
       </c>
       <c r="J5">
-        <v>959046.1270495108</v>
+        <v>1041545.486289122</v>
       </c>
       <c r="K5">
-        <v>956350.7769083314</v>
+        <v>1037843.37736619</v>
       </c>
     </row>
     <row r="6">
@@ -3215,34 +3215,34 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>721672.4305438112</v>
+        <v>46376.24274970806</v>
       </c>
       <c r="C6">
-        <v>727984.1133796213</v>
+        <v>839283.5128620933</v>
       </c>
       <c r="D6">
-        <v>855986.3500443978</v>
+        <v>972434.408234637</v>
       </c>
       <c r="E6">
-        <v>868899.8393110561</v>
+        <v>980122.4007135754</v>
       </c>
       <c r="F6">
-        <v>896540.1549162312</v>
+        <v>1014788.689351918</v>
       </c>
       <c r="G6">
-        <v>901328.9390040431</v>
+        <v>985385.3868012875</v>
       </c>
       <c r="H6">
-        <v>898541.8127050032</v>
+        <v>981716.0151720101</v>
       </c>
       <c r="I6">
-        <v>910610.9163017687</v>
+        <v>1023377.100246118</v>
       </c>
       <c r="J6">
-        <v>953971.1785384859</v>
+        <v>1036067.233206018</v>
       </c>
       <c r="K6">
-        <v>951267.9821786986</v>
+        <v>1032361.935068457</v>
       </c>
     </row>
     <row r="7">
@@ -3250,34 +3250,34 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>717098.6195316534</v>
+        <v>59856.2218425116</v>
       </c>
       <c r="C7">
-        <v>723234.8757594115</v>
+        <v>830921.953174757</v>
       </c>
       <c r="D7">
-        <v>853083.4256886439</v>
+        <v>967192.0415035929</v>
       </c>
       <c r="E7">
-        <v>865335.5341562541</v>
+        <v>974356.1945834922</v>
       </c>
       <c r="F7">
-        <v>893711.6855581172</v>
+        <v>1009657.474027963</v>
       </c>
       <c r="G7">
-        <v>898176.9265413862</v>
+        <v>980559.7377490122</v>
       </c>
       <c r="H7">
-        <v>895387.5531635807</v>
+        <v>976904.8789683713</v>
       </c>
       <c r="I7">
-        <v>907061.8178904504</v>
+        <v>1017661.647761022</v>
       </c>
       <c r="J7">
-        <v>950263.2852482195</v>
+        <v>1030789.753764995</v>
       </c>
       <c r="K7">
-        <v>947546.9188742433</v>
+        <v>1027089.794725437</v>
       </c>
     </row>
     <row r="8">
@@ -3285,34 +3285,34 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>715055.6677221631</v>
+        <v>98902.7448268165</v>
       </c>
       <c r="C8">
-        <v>720776.5472627047</v>
+        <v>819266.8757526898</v>
       </c>
       <c r="D8">
-        <v>854876.5845776905</v>
+        <v>963012.0477615085</v>
       </c>
       <c r="E8">
-        <v>865790.9627602149</v>
+        <v>969215.4750290774</v>
       </c>
       <c r="F8">
-        <v>895758.9654893496</v>
+        <v>1005577.554653054</v>
       </c>
       <c r="G8">
-        <v>899287.8979255273</v>
+        <v>977398.4201645411</v>
       </c>
       <c r="H8">
-        <v>896496.3715197409</v>
+        <v>973785.0433381593</v>
       </c>
       <c r="I8">
-        <v>907714.7170556847</v>
+        <v>1012573.88084143</v>
       </c>
       <c r="J8">
-        <v>950445.593573668</v>
+        <v>1026813.91739509</v>
       </c>
       <c r="K8">
-        <v>947707.0123017202</v>
+        <v>1023141.859804066</v>
       </c>
     </row>
     <row r="9">
@@ -3320,34 +3320,34 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>713230.1649453456</v>
+        <v>171689.6937203202</v>
       </c>
       <c r="C9">
-        <v>718236.4925062817</v>
+        <v>802120.092491049</v>
       </c>
       <c r="D9">
-        <v>857494.2057219436</v>
+        <v>956079.8549978016</v>
       </c>
       <c r="E9">
-        <v>866600.9944608533</v>
+        <v>961081.4040292013</v>
       </c>
       <c r="F9">
-        <v>898822.3362919375</v>
+        <v>998615.1099068883</v>
       </c>
       <c r="G9">
-        <v>900687.261400378</v>
+        <v>971975.1167031126</v>
       </c>
       <c r="H9">
-        <v>897904.1826659126</v>
+        <v>968441.034519781</v>
       </c>
       <c r="I9">
-        <v>908869.6981524618</v>
+        <v>1004339.168299589</v>
       </c>
       <c r="J9">
-        <v>950708.6749262068</v>
+        <v>1020284.845560009</v>
       </c>
       <c r="K9">
-        <v>947953.4661483726</v>
+        <v>1016678.713544777</v>
       </c>
     </row>
     <row r="10">
@@ -3355,34 +3355,34 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>716786.9854581881</v>
+        <v>295468.6301374491</v>
       </c>
       <c r="C10">
-        <v>720862.9995046461</v>
+        <v>788246.1486251096</v>
       </c>
       <c r="D10">
-        <v>864082.3334892569</v>
+        <v>951657.4862917752</v>
       </c>
       <c r="E10">
-        <v>871026.5196093222</v>
+        <v>955202.1356742182</v>
       </c>
       <c r="F10">
-        <v>906009.7913080932</v>
+        <v>994102.4259766105</v>
       </c>
       <c r="G10">
-        <v>905673.33442985</v>
+        <v>969105.8485571954</v>
       </c>
       <c r="H10">
-        <v>902901.1912467331</v>
+        <v>965666.7789874076</v>
       </c>
       <c r="I10">
-        <v>913769.975275757</v>
+        <v>998288.8360820455</v>
       </c>
       <c r="J10">
-        <v>954379.7819494492</v>
+        <v>1016048.875473248</v>
       </c>
       <c r="K10">
-        <v>951612.2117756627</v>
+        <v>1012528.119048164</v>
       </c>
     </row>
     <row r="11">
@@ -3390,34 +3390,34 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>721936.8645922822</v>
+        <v>427587.1942200888</v>
       </c>
       <c r="C11">
-        <v>725172.8780867716</v>
+        <v>776835.0159865303</v>
       </c>
       <c r="D11">
-        <v>873283.4350144934</v>
+        <v>949738.3948858763</v>
       </c>
       <c r="E11">
-        <v>878164.5481164407</v>
+        <v>951911.5940225949</v>
       </c>
       <c r="F11">
-        <v>915770.5605098114</v>
+        <v>992003.2413053158</v>
       </c>
       <c r="G11">
-        <v>913029.0734057876</v>
+        <v>968537.3984065831</v>
       </c>
       <c r="H11">
-        <v>910238.4361120302</v>
+        <v>965167.7939451168</v>
       </c>
       <c r="I11">
-        <v>921339.582571059</v>
+        <v>994737.8704312864</v>
       </c>
       <c r="J11">
-        <v>960492.9069859476</v>
+        <v>1014145.110606706</v>
       </c>
       <c r="K11">
-        <v>957690.1886684014</v>
+        <v>1010690.954922231</v>
       </c>
     </row>
     <row r="12">
@@ -3425,34 +3425,34 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>723519.2722836859</v>
+        <v>504412.0619475911</v>
       </c>
       <c r="C12">
-        <v>726328.7065902967</v>
+        <v>764484.8950335261</v>
       </c>
       <c r="D12">
-        <v>883452.0988255871</v>
+        <v>949218.8780781785</v>
       </c>
       <c r="E12">
-        <v>886831.2373095299</v>
+        <v>950512.1696747337</v>
       </c>
       <c r="F12">
-        <v>926331.2755220244</v>
+        <v>991192.0525853696</v>
       </c>
       <c r="G12">
-        <v>921155.0106616819</v>
+        <v>969051.2488852923</v>
       </c>
       <c r="H12">
-        <v>918341.6429068905</v>
+        <v>965744.6053021704</v>
       </c>
       <c r="I12">
-        <v>930283.7014803016</v>
+        <v>992978.0031999032</v>
       </c>
       <c r="J12">
-        <v>967789.504741026</v>
+        <v>1013731.842604799</v>
       </c>
       <c r="K12">
-        <v>964933.3395790654</v>
+        <v>1010324.189349946</v>
       </c>
     </row>
     <row r="13">
@@ -3460,34 +3460,34 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>719531.1712496694</v>
+        <v>532317.0676271967</v>
       </c>
       <c r="C13">
-        <v>722360.1325398337</v>
+        <v>749558.0818680342</v>
       </c>
       <c r="D13">
-        <v>890880.2174026235</v>
+        <v>946621.6669878917</v>
       </c>
       <c r="E13">
-        <v>893857.0289238796</v>
+        <v>948035.4681903331</v>
       </c>
       <c r="F13">
-        <v>933919.3383739959</v>
+        <v>988188.4318686051</v>
       </c>
       <c r="G13">
-        <v>926279.7973564179</v>
+        <v>967034.8493679895</v>
       </c>
       <c r="H13">
-        <v>923563.32241565</v>
+        <v>963902.5899839427</v>
       </c>
       <c r="I13">
-        <v>937372.2715040034</v>
+        <v>990038.5719794149</v>
       </c>
       <c r="J13">
-        <v>972886.0627412385</v>
+        <v>1011609.12457496</v>
       </c>
       <c r="K13">
-        <v>970062.8724881364</v>
+        <v>1008326.766368992</v>
       </c>
     </row>
     <row r="14">
@@ -3495,34 +3495,34 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>720759.3166541178</v>
+        <v>535523.9745800007</v>
       </c>
       <c r="C14">
-        <v>723746.4099877994</v>
+        <v>742122.7747917962</v>
       </c>
       <c r="D14">
-        <v>898710.3088710679</v>
+        <v>945259.8020179485</v>
       </c>
       <c r="E14">
-        <v>902346.9650639748</v>
+        <v>947749.3849271039</v>
       </c>
       <c r="F14">
-        <v>941738.7890018367</v>
+        <v>986386.3901414339</v>
       </c>
       <c r="G14">
-        <v>931533.4966062529</v>
+        <v>965732.0535457419</v>
       </c>
       <c r="H14">
-        <v>929037.0431427539</v>
+        <v>962887.5396435957</v>
       </c>
       <c r="I14">
-        <v>945818.0554728383</v>
+        <v>989312.6240878514</v>
       </c>
       <c r="J14">
-        <v>978778.6683769674</v>
+        <v>1010901.288047376</v>
       </c>
       <c r="K14">
-        <v>976080.436137807</v>
+        <v>1007826.556126863</v>
       </c>
     </row>
     <row r="15">
@@ -3530,34 +3530,34 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>739542.7431561797</v>
+        <v>529585.9808362434</v>
       </c>
       <c r="C15">
-        <v>742527.438457645</v>
+        <v>753325.3349341111</v>
       </c>
       <c r="D15">
-        <v>909935.8869089242</v>
+        <v>948172.964230031</v>
       </c>
       <c r="E15">
-        <v>914825.2458866544</v>
+        <v>952236.0660373707</v>
       </c>
       <c r="F15">
-        <v>952888.6233325165</v>
+        <v>988932.0750970759</v>
       </c>
       <c r="G15">
-        <v>940045.5444613057</v>
+        <v>968298.6735732426</v>
       </c>
       <c r="H15">
-        <v>937787.035039376</v>
+        <v>965752.2466725591</v>
       </c>
       <c r="I15">
-        <v>958280.3650582533</v>
+        <v>993517.1127150449</v>
       </c>
       <c r="J15">
-        <v>988180.0258917564</v>
+        <v>1014357.034954526</v>
       </c>
       <c r="K15">
-        <v>985600.6882838598</v>
+        <v>1011475.638390607</v>
       </c>
     </row>
     <row r="16">
@@ -3565,34 +3565,34 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>775237.3096139878</v>
+        <v>527647.5101245645</v>
       </c>
       <c r="C16">
-        <v>778025.5573487421</v>
+        <v>781864.6326120119</v>
       </c>
       <c r="D16">
-        <v>919533.4443791978</v>
+        <v>950250.0679108764</v>
       </c>
       <c r="E16">
-        <v>925653.0562454017</v>
+        <v>955795.5305684928</v>
       </c>
       <c r="F16">
-        <v>962369.8896471321</v>
+        <v>990743.6963833268</v>
       </c>
       <c r="G16">
-        <v>946872.0120688516</v>
+        <v>969725.6233163445</v>
       </c>
       <c r="H16">
-        <v>944744.1329722508</v>
+        <v>967366.9462088295</v>
       </c>
       <c r="I16">
-        <v>969053.9420226545</v>
+        <v>996890.0730138893</v>
       </c>
       <c r="J16">
-        <v>995786.545334033</v>
+        <v>1016619.787090919</v>
       </c>
       <c r="K16">
-        <v>993248.1405862512</v>
+        <v>1013848.047592637</v>
       </c>
     </row>
     <row r="17">
@@ -3600,34 +3600,34 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>816138.7309053635</v>
+        <v>517472.6083306447</v>
       </c>
       <c r="C17">
-        <v>818587.7691195182</v>
+        <v>816707.537649096</v>
       </c>
       <c r="D17">
-        <v>925394.0898839228</v>
+        <v>949331.4902306902</v>
       </c>
       <c r="E17">
-        <v>931848.0415600123</v>
+        <v>955416.9449432476</v>
       </c>
       <c r="F17">
-        <v>968203.5778562513</v>
+        <v>989784.8541360282</v>
       </c>
       <c r="G17">
-        <v>949172.6912073328</v>
+        <v>967150.4884730079</v>
       </c>
       <c r="H17">
-        <v>947033.2562889517</v>
+        <v>964836.8101785122</v>
       </c>
       <c r="I17">
-        <v>975152.6145299673</v>
+        <v>996411.1276660869</v>
       </c>
       <c r="J17">
-        <v>998347.5640547667</v>
+        <v>1014419.790967475</v>
       </c>
       <c r="K17">
-        <v>995808.3178843982</v>
+        <v>1011710.326772313</v>
       </c>
     </row>
     <row r="18">
@@ -3635,34 +3635,34 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>853990.8425901762</v>
+        <v>497770.7899554816</v>
       </c>
       <c r="C18">
-        <v>856151.5381182492</v>
+        <v>850400.6295232131</v>
       </c>
       <c r="D18">
-        <v>932659.9453495117</v>
+        <v>950572.0326163208</v>
       </c>
       <c r="E18">
-        <v>938067.3260266518</v>
+        <v>955766.7546573195</v>
       </c>
       <c r="F18">
-        <v>975801.5055266083</v>
+        <v>991459.6249658209</v>
       </c>
       <c r="G18">
-        <v>951753.0136495441</v>
+        <v>965395.8513562847</v>
       </c>
       <c r="H18">
-        <v>949588.9217543745</v>
+        <v>963111.3624055699</v>
       </c>
       <c r="I18">
-        <v>981458.9241005802</v>
+        <v>996952.935044017</v>
       </c>
       <c r="J18">
-        <v>1000349.778029216</v>
+        <v>1012249.21028524</v>
       </c>
       <c r="K18">
-        <v>997867.2856913693</v>
+        <v>1009651.697319754</v>
       </c>
     </row>
     <row r="19">
@@ -3670,34 +3670,34 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>890483.008659397</v>
+        <v>495078.1575557588</v>
       </c>
       <c r="C19">
-        <v>892514.3182755566</v>
+        <v>884404.3107009208</v>
       </c>
       <c r="D19">
-        <v>945547.0628138266</v>
+        <v>958235.167678104</v>
       </c>
       <c r="E19">
-        <v>948953.1945248032</v>
+        <v>961524.1946302979</v>
       </c>
       <c r="F19">
-        <v>989571.49857372</v>
+        <v>1000200.221478703</v>
       </c>
       <c r="G19">
-        <v>959642.6578260977</v>
+        <v>969515.3074805019</v>
       </c>
       <c r="H19">
-        <v>957335.0283651323</v>
+        <v>967137.7746791008</v>
       </c>
       <c r="I19">
-        <v>992877.3544601599</v>
+        <v>1003433.362878914</v>
       </c>
       <c r="J19">
-        <v>1007119.371732361</v>
+        <v>1015439.992482054</v>
       </c>
       <c r="K19">
-        <v>1004579.287433008</v>
+        <v>1012834.080711171</v>
       </c>
     </row>
     <row r="20">
@@ -3705,34 +3705,34 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>917258.5303135117</v>
+        <v>493719.5311031707</v>
       </c>
       <c r="C20">
-        <v>918874.7834450819</v>
+        <v>909594.4937223108</v>
       </c>
       <c r="D20">
-        <v>952919.2184503657</v>
+        <v>961253.6115737258</v>
       </c>
       <c r="E20">
-        <v>954798.2109383427</v>
+        <v>963073.3650663092</v>
       </c>
       <c r="F20">
-        <v>998002.4613103982</v>
+        <v>1004547.36175078</v>
       </c>
       <c r="G20">
-        <v>962779.3668801375</v>
+        <v>969488.2017154597</v>
       </c>
       <c r="H20">
-        <v>960080.5155242011</v>
+        <v>966761.6656916934</v>
       </c>
       <c r="I20">
-        <v>999408.4669371223</v>
+        <v>1005926.983165509</v>
       </c>
       <c r="J20">
-        <v>1009576.157712967</v>
+        <v>1014950.263637516</v>
       </c>
       <c r="K20">
-        <v>1006718.054002682</v>
+        <v>1012067.392222758</v>
       </c>
     </row>
     <row r="21">
@@ -3740,34 +3740,34 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>938611.7295828732</v>
+        <v>502563.4562568465</v>
       </c>
       <c r="C21">
-        <v>939271.5238762163</v>
+        <v>929644.7882311064</v>
       </c>
       <c r="D21">
-        <v>958696.5891112729</v>
+        <v>963620.3516788782</v>
       </c>
       <c r="E21">
-        <v>960017.4068874704</v>
+        <v>964924.1926380874</v>
       </c>
       <c r="F21">
-        <v>1004629.474779133</v>
+        <v>1008078.603938668</v>
       </c>
       <c r="G21">
-        <v>965858.60760454</v>
+        <v>970060.5535997564</v>
       </c>
       <c r="H21">
-        <v>962689.0407436332</v>
+        <v>966889.3846986499</v>
       </c>
       <c r="I21">
-        <v>1005248.142947738</v>
+        <v>1008698.613555846</v>
       </c>
       <c r="J21">
-        <v>1012756.546241364</v>
+        <v>1015854.940608555</v>
       </c>
       <c r="K21">
-        <v>1009453.525707471</v>
+        <v>1012553.503961239</v>
       </c>
     </row>
     <row r="22">
@@ -3775,34 +3775,34 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>949809.7145887943</v>
+        <v>545460.5108334835</v>
       </c>
       <c r="C22">
-        <v>949269.428825453</v>
+        <v>939124.7684166683</v>
       </c>
       <c r="D22">
-        <v>957678.951569682</v>
+        <v>959740.1688308574</v>
       </c>
       <c r="E22">
-        <v>960080.9659515843</v>
+        <v>962155.7372967275</v>
       </c>
       <c r="F22">
-        <v>1003912.510804804</v>
+        <v>1005040.440491843</v>
       </c>
       <c r="G22">
-        <v>963256.1439920485</v>
+        <v>965317.9642447287</v>
       </c>
       <c r="H22">
-        <v>959666.9589431008</v>
+        <v>961741.8469444904</v>
       </c>
       <c r="I22">
-        <v>1005605.946147276</v>
+        <v>1006744.235774969</v>
       </c>
       <c r="J22">
-        <v>1011524.441495533</v>
+        <v>1012859.475773351</v>
       </c>
       <c r="K22">
-        <v>1007811.880769928</v>
+        <v>1009162.721557413</v>
       </c>
     </row>
     <row r="23">
@@ -3810,34 +3810,34 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>961477.6751479943</v>
+        <v>602278.0151410964</v>
       </c>
       <c r="C23">
-        <v>959581.337715533</v>
+        <v>949300.527208815</v>
       </c>
       <c r="D23">
-        <v>959723.4821674514</v>
+        <v>959867.7366966265</v>
       </c>
       <c r="E23">
-        <v>963958.2765077237</v>
+        <v>964116.6023602356</v>
       </c>
       <c r="F23">
-        <v>1006108.394186599</v>
+        <v>1005761.375395168</v>
       </c>
       <c r="G23">
-        <v>964279.9935714134</v>
+        <v>964852.0400015844</v>
       </c>
       <c r="H23">
-        <v>960316.2729444703</v>
+        <v>960908.7783859418</v>
       </c>
       <c r="I23">
-        <v>1009870.640442038</v>
+        <v>1009520.818396399</v>
       </c>
       <c r="J23">
-        <v>1014672.918438456</v>
+        <v>1014815.597521979</v>
       </c>
       <c r="K23">
-        <v>1010635.283795842</v>
+        <v>1010800.391547468</v>
       </c>
     </row>
     <row r="24">
@@ -3845,34 +3845,34 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>966815.3847426815</v>
+        <v>628692.0744482779</v>
       </c>
       <c r="C24">
-        <v>963718.4154085313</v>
+        <v>953637.2262641839</v>
       </c>
       <c r="D24">
-        <v>959767.8400916076</v>
+        <v>958695.6253805668</v>
       </c>
       <c r="E24">
-        <v>965977.6842969377</v>
+        <v>964934.3803582441</v>
       </c>
       <c r="F24">
-        <v>1006073.096126842</v>
+        <v>1004845.552174288</v>
       </c>
       <c r="G24">
-        <v>964104.455670285</v>
+        <v>963690.1842277858</v>
       </c>
       <c r="H24">
-        <v>959932.6623243416</v>
+        <v>959540.6738430434</v>
       </c>
       <c r="I24">
-        <v>1012218.945640823</v>
+        <v>1010995.564459521</v>
       </c>
       <c r="J24">
-        <v>1016718.285573868</v>
+        <v>1016116.377016395</v>
       </c>
       <c r="K24">
-        <v>1012535.019082959</v>
+        <v>1011956.495545512</v>
       </c>
     </row>
     <row r="25">
@@ -3880,34 +3880,34 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>960580.6402163891</v>
+        <v>622812.3206922412</v>
       </c>
       <c r="C25">
-        <v>956844.0611005109</v>
+        <v>947203.1513244427</v>
       </c>
       <c r="D25">
-        <v>952338.0783882041</v>
+        <v>950519.1508335164</v>
       </c>
       <c r="E25">
-        <v>960415.9567540581</v>
+        <v>958666.9325024548</v>
       </c>
       <c r="F25">
-        <v>998398.042174162</v>
+        <v>996669.0403401345</v>
       </c>
       <c r="G25">
-        <v>957547.5837356054</v>
+        <v>956509.5716751792</v>
       </c>
       <c r="H25">
-        <v>953297.5699902081</v>
+        <v>952278.7207525736</v>
       </c>
       <c r="I25">
-        <v>1006827.350701396</v>
+        <v>1005139.979200989</v>
       </c>
       <c r="J25">
-        <v>1012142.953478625</v>
+        <v>1011116.389066451</v>
       </c>
       <c r="K25">
-        <v>1007941.465092597</v>
+        <v>1006934.949139886</v>
       </c>
     </row>
     <row r="26">
@@ -3915,34 +3915,34 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>945202.8474735353</v>
+        <v>601589.866202827</v>
       </c>
       <c r="C26">
-        <v>941271.5978551146</v>
+        <v>932123.423480863</v>
       </c>
       <c r="D26">
-        <v>937670.1948891898</v>
+        <v>935439.1086114867</v>
       </c>
       <c r="E26">
-        <v>947395.4053212276</v>
+        <v>945274.5422841029</v>
       </c>
       <c r="F26">
-        <v>983942.3089438577</v>
+        <v>981971.3148488526</v>
       </c>
       <c r="G26">
-        <v>944449.8659592719</v>
+        <v>943046.4945919763</v>
       </c>
       <c r="H26">
-        <v>939998.8516686307</v>
+        <v>938609.5458689017</v>
       </c>
       <c r="I26">
-        <v>994268.4273541906</v>
+        <v>992378.7252161419</v>
       </c>
       <c r="J26">
-        <v>1000914.594217355</v>
+        <v>999671.2230771568</v>
       </c>
       <c r="K26">
-        <v>996551.4194022387</v>
+        <v>995324.3550650181</v>
       </c>
     </row>
     <row r="27">
@@ -3950,34 +3950,34 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>936810.2191116547</v>
+        <v>581906.0183509876</v>
       </c>
       <c r="C27">
-        <v>932825.8696302589</v>
+        <v>924084.2356033558</v>
       </c>
       <c r="D27">
-        <v>930315.7159089355</v>
+        <v>927906.9280794279</v>
       </c>
       <c r="E27">
-        <v>940318.2652501719</v>
+        <v>938048.6842282066</v>
       </c>
       <c r="F27">
-        <v>977990.2940930257</v>
+        <v>975951.5127849733</v>
       </c>
       <c r="G27">
-        <v>938684.288648737</v>
+        <v>937094.5384297378</v>
       </c>
       <c r="H27">
-        <v>933938.7756894889</v>
+        <v>932358.3017551741</v>
       </c>
       <c r="I27">
-        <v>988586.2427327833</v>
+        <v>986657.3458763855</v>
       </c>
       <c r="J27">
-        <v>996293.5004044831</v>
+        <v>994962.6070570691</v>
       </c>
       <c r="K27">
-        <v>991645.7007087823</v>
+        <v>990328.1027201031</v>
       </c>
     </row>
     <row r="28">
@@ -3985,34 +3985,34 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>937173.9286718194</v>
+        <v>568386.6829160972</v>
       </c>
       <c r="C28">
-        <v>933128.8385838519</v>
+        <v>924576.439345367</v>
       </c>
       <c r="D28">
-        <v>930235.2810846663</v>
+        <v>927814.9917746568</v>
       </c>
       <c r="E28">
-        <v>938506.8584643059</v>
+        <v>936235.4663459866</v>
       </c>
       <c r="F28">
-        <v>980438.9160702437</v>
+        <v>978451.5661626114</v>
       </c>
       <c r="G28">
-        <v>939523.5333074386</v>
+        <v>937870.0583158112</v>
       </c>
       <c r="H28">
-        <v>934389.9044158217</v>
+        <v>932743.1998435408</v>
       </c>
       <c r="I28">
-        <v>988899.7396416469</v>
+        <v>987030.5248284549</v>
       </c>
       <c r="J28">
-        <v>997008.103583292</v>
+        <v>995664.4781442827</v>
       </c>
       <c r="K28">
-        <v>991986.0258570426</v>
+        <v>990654.1244964702</v>
       </c>
     </row>
     <row r="29">
@@ -4020,34 +4020,34 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>947766.0165447857</v>
+        <v>561248.3520787344</v>
       </c>
       <c r="C29">
-        <v>943562.8495363195</v>
+        <v>934909.6074379485</v>
       </c>
       <c r="D29">
-        <v>937347.6367514939</v>
+        <v>935050.8829458056</v>
       </c>
       <c r="E29">
-        <v>941732.9805566028</v>
+        <v>939546.7495500274</v>
       </c>
       <c r="F29">
-        <v>990614.2371389982</v>
+        <v>988775.7781745183</v>
       </c>
       <c r="G29">
-        <v>945931.474923432</v>
+        <v>944301.917826059</v>
       </c>
       <c r="H29">
-        <v>940434.3565856405</v>
+        <v>938813.7809168238</v>
       </c>
       <c r="I29">
-        <v>994383.8384657078</v>
+        <v>992623.9925974153</v>
       </c>
       <c r="J29">
-        <v>1001825.685454149</v>
+        <v>1000497.395950697</v>
       </c>
       <c r="K29">
-        <v>996401.3261434588</v>
+        <v>995085.4704554228</v>
       </c>
     </row>
     <row r="30">
@@ -4055,34 +4055,34 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>991233.6744566784</v>
+        <v>585976.6117656884</v>
       </c>
       <c r="C30">
-        <v>986255.7176819837</v>
+        <v>977416.6498194176</v>
       </c>
       <c r="D30">
-        <v>973546.3036123004</v>
+        <v>971481.2977208782</v>
       </c>
       <c r="E30">
-        <v>972515.177697744</v>
+        <v>970458.5526428703</v>
       </c>
       <c r="F30">
-        <v>1029899.859646485</v>
+        <v>1028289.012642838</v>
       </c>
       <c r="G30">
-        <v>979049.2137328279</v>
+        <v>977501.7262234444</v>
       </c>
       <c r="H30">
-        <v>973249.3468837927</v>
+        <v>971719.5009842241</v>
       </c>
       <c r="I30">
-        <v>1027607.67282366</v>
+        <v>1025975.683392798</v>
       </c>
       <c r="J30">
-        <v>1032302.007163876</v>
+        <v>1030986.228526399</v>
       </c>
       <c r="K30">
-        <v>1026469.101666278</v>
+        <v>1025169.690671523</v>
       </c>
     </row>
     <row r="31">
@@ -4090,34 +4090,34 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>1046782.607239028</v>
+        <v>644176.8484870861</v>
       </c>
       <c r="C31">
-        <v>1039810.658347879</v>
+        <v>1031391.880784214</v>
       </c>
       <c r="D31">
-        <v>1019154.385343614</v>
+        <v>1017444.712994784</v>
       </c>
       <c r="E31">
-        <v>1014626.002227084</v>
+        <v>1012739.141651741</v>
       </c>
       <c r="F31">
-        <v>1077900.681010836</v>
+        <v>1076611.772422313</v>
       </c>
       <c r="G31">
-        <v>1017840.167855902</v>
+        <v>1016430.77669655</v>
       </c>
       <c r="H31">
-        <v>1011920.391855986</v>
+        <v>1010542.459448284</v>
       </c>
       <c r="I31">
-        <v>1071950.258288261</v>
+        <v>1070461.798504645</v>
       </c>
       <c r="J31">
-        <v>1070081.659355455</v>
+        <v>1068774.230031664</v>
       </c>
       <c r="K31">
-        <v>1064025.811837211</v>
+        <v>1062741.177243816</v>
       </c>
     </row>
     <row r="32">
@@ -4125,34 +4125,34 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>1085838.140905828</v>
+        <v>708294.2400079453</v>
       </c>
       <c r="C32">
-        <v>1076605.028535006</v>
+        <v>1068842.243148586</v>
       </c>
       <c r="D32">
-        <v>1050566.503093033</v>
+        <v>1049210.485141951</v>
       </c>
       <c r="E32">
-        <v>1044013.537308328</v>
+        <v>1042319.214056439</v>
       </c>
       <c r="F32">
-        <v>1110614.096814428</v>
+        <v>1109634.172600245</v>
       </c>
       <c r="G32">
-        <v>1043049.898950226</v>
+        <v>1041794.618193558</v>
       </c>
       <c r="H32">
-        <v>1037339.536417749</v>
+        <v>1036126.955557784</v>
       </c>
       <c r="I32">
-        <v>1102775.783531603</v>
+        <v>1101440.8571185</v>
       </c>
       <c r="J32">
-        <v>1094760.111434238</v>
+        <v>1093487.022148709</v>
       </c>
       <c r="K32">
-        <v>1088888.26496296</v>
+        <v>1087641.954935489</v>
       </c>
     </row>
     <row r="33">
@@ -4160,34 +4160,34 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>1097947.306100805</v>
+        <v>766523.8154953711</v>
       </c>
       <c r="C33">
-        <v>1087095.621188559</v>
+        <v>1079712.287291688</v>
       </c>
       <c r="D33">
-        <v>1061204.650978377</v>
+        <v>1060089.207799867</v>
       </c>
       <c r="E33">
-        <v>1052552.408059777</v>
+        <v>1051055.197605622</v>
       </c>
       <c r="F33">
-        <v>1120767.525607639</v>
+        <v>1119980.928564505</v>
       </c>
       <c r="G33">
-        <v>1051835.418277992</v>
+        <v>1050719.154388998</v>
       </c>
       <c r="H33">
-        <v>1046360.912787148</v>
+        <v>1045291.813632214</v>
       </c>
       <c r="I33">
-        <v>1110943.086623079</v>
+        <v>1109763.084746201</v>
       </c>
       <c r="J33">
-        <v>1101228.330674235</v>
+        <v>1100036.497364235</v>
       </c>
       <c r="K33">
-        <v>1095674.960688148</v>
+        <v>1094510.101571208</v>
       </c>
     </row>
     <row r="34">
@@ -4195,34 +4195,34 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>1089404.598914832</v>
+        <v>818671.7890997716</v>
       </c>
       <c r="C34">
-        <v>1077050.014647993</v>
+        <v>1069928.433413726</v>
       </c>
       <c r="D34">
-        <v>1053123.057729486</v>
+        <v>1052193.764694124</v>
       </c>
       <c r="E34">
-        <v>1042766.703411005</v>
+        <v>1041472.990802442</v>
       </c>
       <c r="F34">
-        <v>1110726.734890636</v>
+        <v>1110067.15195828</v>
       </c>
       <c r="G34">
-        <v>1044315.045286724</v>
+        <v>1043328.252185853</v>
       </c>
       <c r="H34">
-        <v>1038956.657001667</v>
+        <v>1038016.513396166</v>
       </c>
       <c r="I34">
-        <v>1099156.011555317</v>
+        <v>1098125.038734831</v>
       </c>
       <c r="J34">
-        <v>1090165.600936876</v>
+        <v>1089077.948016049</v>
       </c>
       <c r="K34">
-        <v>1084820.05827523</v>
+        <v>1083758.140146245</v>
       </c>
     </row>
     <row r="35">
@@ -4230,34 +4230,34 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>1078543.255922426</v>
+        <v>889794.2085222951</v>
       </c>
       <c r="C35">
-        <v>1063948.318082591</v>
+        <v>1056999.715216641</v>
       </c>
       <c r="D35">
-        <v>1042085.224164404</v>
+        <v>1041306.53251669</v>
       </c>
       <c r="E35">
-        <v>1031142.48701782</v>
+        <v>1030022.5380733</v>
       </c>
       <c r="F35">
-        <v>1096925.806704394</v>
+        <v>1096358.617562149</v>
       </c>
       <c r="G35">
-        <v>1033930.535711095</v>
+        <v>1033055.603620383</v>
       </c>
       <c r="H35">
-        <v>1028689.242103958</v>
+        <v>1027858.565909063</v>
       </c>
       <c r="I35">
-        <v>1084704.440383508</v>
+        <v>1083794.03741188</v>
       </c>
       <c r="J35">
-        <v>1076487.810037551</v>
+        <v>1075496.068938097</v>
       </c>
       <c r="K35">
-        <v>1071305.490748708</v>
+        <v>1070338.077305018</v>
       </c>
     </row>
     <row r="36">
@@ -4265,34 +4265,34 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>1067073.991439415</v>
+        <v>957427.0598818655</v>
       </c>
       <c r="C36">
-        <v>1049156.348207649</v>
+        <v>1042295.564831759</v>
       </c>
       <c r="D36">
-        <v>1028141.460460247</v>
+        <v>1027486.107676623</v>
       </c>
       <c r="E36">
-        <v>1018654.41949252</v>
+        <v>1017666.05691017</v>
       </c>
       <c r="F36">
-        <v>1079699.878469755</v>
+        <v>1079204.845427705</v>
       </c>
       <c r="G36">
-        <v>1020106.823527158</v>
+        <v>1019323.836493934</v>
       </c>
       <c r="H36">
-        <v>1015038.953853823</v>
+        <v>1014298.112478224</v>
       </c>
       <c r="I36">
-        <v>1068948.4295421</v>
+        <v>1068124.600845834</v>
       </c>
       <c r="J36">
-        <v>1060955.70299524</v>
+        <v>1060039.543543125</v>
       </c>
       <c r="K36">
-        <v>1055964.403685358</v>
+        <v>1055071.806148139</v>
       </c>
     </row>
     <row r="37">
@@ -4300,34 +4300,34 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>1044730.372125454</v>
+        <v>985040.5084953579</v>
       </c>
       <c r="C37">
-        <v>1023004.458896125</v>
+        <v>1016270.327865867</v>
       </c>
       <c r="D37">
-        <v>1002978.715391488</v>
+        <v>1002425.993702583</v>
       </c>
       <c r="E37">
-        <v>997042.4169716114</v>
+        <v>996166.1387157247</v>
       </c>
       <c r="F37">
-        <v>1051196.667158829</v>
+        <v>1050756.197371762</v>
       </c>
       <c r="G37">
-        <v>995410.6053805721</v>
+        <v>994707.334623377</v>
       </c>
       <c r="H37">
-        <v>990639.9485758566</v>
+        <v>989976.4000464045</v>
       </c>
       <c r="I37">
-        <v>1044147.280578514</v>
+        <v>1043391.06433339</v>
       </c>
       <c r="J37">
-        <v>1036618.973036928</v>
+        <v>1035768.557606535</v>
       </c>
       <c r="K37">
-        <v>1031955.42125762</v>
+        <v>1031127.518435239</v>
       </c>
     </row>
     <row r="38">
@@ -4335,34 +4335,34 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>1019872.01880103</v>
+        <v>994601.1854814766</v>
       </c>
       <c r="C38">
-        <v>994823.2171077598</v>
+        <v>988373.6428212774</v>
       </c>
       <c r="D38">
-        <v>977357.7432075716</v>
+        <v>976868.594453031</v>
       </c>
       <c r="E38">
-        <v>975417.407699361</v>
+        <v>974647.2933822252</v>
       </c>
       <c r="F38">
-        <v>1022482.518880383</v>
+        <v>1022068.619125999</v>
       </c>
       <c r="G38">
-        <v>971430.3468184826</v>
+        <v>970796.2682825207</v>
       </c>
       <c r="H38">
-        <v>967063.1173724213</v>
+        <v>966462.9272560023</v>
       </c>
       <c r="I38">
-        <v>1019824.488694216</v>
+        <v>1019136.391933398</v>
       </c>
       <c r="J38">
-        <v>1013681.891893768</v>
+        <v>1012909.377559285</v>
       </c>
       <c r="K38">
-        <v>1009458.930062194</v>
+        <v>1008705.571657964</v>
       </c>
     </row>
     <row r="39">
@@ -4370,34 +4370,34 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>982619.3490137039</v>
+        <v>979451.2947193518</v>
       </c>
       <c r="C39">
-        <v>954904.1097498045</v>
+        <v>948898.5686097675</v>
       </c>
       <c r="D39">
-        <v>941469.2466090951</v>
+        <v>941014.9728786424</v>
       </c>
       <c r="E39">
-        <v>943446.649414384</v>
+        <v>942788.4082197148</v>
       </c>
       <c r="F39">
-        <v>983037.6073527311</v>
+        <v>982628.0929058625</v>
       </c>
       <c r="G39">
-        <v>938273.880619225</v>
+        <v>937702.6081290245</v>
       </c>
       <c r="H39">
-        <v>934210.9412345199</v>
+        <v>933664.5518338983</v>
       </c>
       <c r="I39">
-        <v>984773.6654907285</v>
+        <v>984166.8924282754</v>
       </c>
       <c r="J39">
-        <v>981101.7444634596</v>
+        <v>980429.3140500953</v>
       </c>
       <c r="K39">
-        <v>977239.5931970383</v>
+        <v>976581.3330285624</v>
       </c>
     </row>
     <row r="40">
@@ -4405,34 +4405,34 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>924801.9340973758</v>
+        <v>932225.2728095566</v>
       </c>
       <c r="C40">
-        <v>895119.0309619108</v>
+        <v>889701.3005208418</v>
       </c>
       <c r="D40">
-        <v>886701.815331101</v>
+        <v>886265.6036749531</v>
       </c>
       <c r="E40">
-        <v>891511.8301963932</v>
+        <v>890975.1367934758</v>
       </c>
       <c r="F40">
-        <v>924116.2869416031</v>
+        <v>923698.2355577368</v>
       </c>
       <c r="G40">
-        <v>887186.4530881755</v>
+        <v>886673.6993582021</v>
       </c>
       <c r="H40">
-        <v>883288.8682306225</v>
+        <v>882790.1473690972</v>
       </c>
       <c r="I40">
-        <v>929016.0368905495</v>
+        <v>928506.0564573304</v>
       </c>
       <c r="J40">
-        <v>928927.5444924238</v>
+        <v>928375.1427062347</v>
       </c>
       <c r="K40">
-        <v>925330.9779336224</v>
+        <v>924786.6387323244</v>
       </c>
     </row>
     <row r="41">
@@ -4440,34 +4440,34 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>880509.7588115616</v>
+        <v>889741.4189559113</v>
       </c>
       <c r="C41">
-        <v>849376.1132585921</v>
+        <v>844592.4077383694</v>
       </c>
       <c r="D41">
-        <v>846265.5640603658</v>
+        <v>845834.6510405876</v>
       </c>
       <c r="E41">
-        <v>850982.3412514178</v>
+        <v>850568.7680731132</v>
       </c>
       <c r="F41">
-        <v>879725.7315092592</v>
+        <v>879291.390022061</v>
       </c>
       <c r="G41">
-        <v>850538.7274923364</v>
+        <v>850077.5939516654</v>
       </c>
       <c r="H41">
-        <v>846811.1711329161</v>
+        <v>846352.6527484601</v>
       </c>
       <c r="I41">
-        <v>884744.9384103419</v>
+        <v>884337.5897459263</v>
       </c>
       <c r="J41">
-        <v>888619.9290223167</v>
+        <v>888194.7273310514</v>
       </c>
       <c r="K41">
-        <v>885243.072120054</v>
+        <v>884819.0607804359</v>
       </c>
     </row>
     <row r="42">
@@ -4475,34 +4475,34 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>842081.3379766567</v>
+        <v>853970.9260942434</v>
       </c>
       <c r="C42">
-        <v>809547.5305048672</v>
+        <v>805246.7852487757</v>
       </c>
       <c r="D42">
-        <v>810411.4274914009</v>
+        <v>809981.8203008618</v>
       </c>
       <c r="E42">
-        <v>813519.46019139</v>
+        <v>813208.9897905793</v>
       </c>
       <c r="F42">
-        <v>840172.0180407576</v>
+        <v>839723.1094597828</v>
       </c>
       <c r="G42">
-        <v>817828.8636573192</v>
+        <v>817408.5284879456</v>
       </c>
       <c r="H42">
-        <v>814202.0109680177</v>
+        <v>813774.8452469804</v>
       </c>
       <c r="I42">
-        <v>843627.2366196446</v>
+        <v>843308.6977372591</v>
       </c>
       <c r="J42">
-        <v>851008.7485074758</v>
+        <v>850696.1392977856</v>
       </c>
       <c r="K42">
-        <v>847779.6446145696</v>
+        <v>847462.3795611078</v>
       </c>
     </row>
     <row r="43">
@@ -4510,34 +4510,34 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>808281.5481791621</v>
+        <v>829445.7391159805</v>
       </c>
       <c r="C43">
-        <v>774739.9935854535</v>
+        <v>770723.165793972</v>
       </c>
       <c r="D43">
-        <v>777692.1376372693</v>
+        <v>777264.6916982359</v>
       </c>
       <c r="E43">
-        <v>778986.8094961685</v>
+        <v>778740.2044101966</v>
       </c>
       <c r="F43">
-        <v>804254.7810837061</v>
+        <v>803797.0445108007</v>
       </c>
       <c r="G43">
-        <v>786880.0137068511</v>
+        <v>786486.5405513289</v>
       </c>
       <c r="H43">
-        <v>783450.1464529067</v>
+        <v>783043.7908033844</v>
       </c>
       <c r="I43">
-        <v>805888.9087513833</v>
+        <v>805627.4127964962</v>
       </c>
       <c r="J43">
-        <v>815644.5048911221</v>
+        <v>815411.2908807641</v>
       </c>
       <c r="K43">
-        <v>812560.3453505734</v>
+        <v>812318.3432618971</v>
       </c>
     </row>
     <row r="44">
@@ -4545,34 +4545,34 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>787647.5955494447</v>
+        <v>823003.5194000887</v>
       </c>
       <c r="C44">
-        <v>755078.2186938955</v>
+        <v>751160.6733870239</v>
       </c>
       <c r="D44">
-        <v>759416.6461492572</v>
+        <v>758981.8000637966</v>
       </c>
       <c r="E44">
-        <v>759064.6999897435</v>
+        <v>758850.3262122129</v>
       </c>
       <c r="F44">
-        <v>784521.0745292061</v>
+        <v>784052.0893721743</v>
       </c>
       <c r="G44">
-        <v>770007.331452078</v>
+        <v>769627.2020644346</v>
       </c>
       <c r="H44">
-        <v>766699.8163650732</v>
+        <v>766303.1062307052</v>
       </c>
       <c r="I44">
-        <v>784422.0481609819</v>
+        <v>784187.146935182</v>
       </c>
       <c r="J44">
-        <v>795924.1660190042</v>
+        <v>795736.1911569781</v>
       </c>
       <c r="K44">
-        <v>792898.3768875285</v>
+        <v>792699.4539215681</v>
       </c>
     </row>
     <row r="45">
@@ -4580,34 +4580,34 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>764506.6473120456</v>
+        <v>811434.5851945075</v>
       </c>
       <c r="C45">
-        <v>736676.6049150284</v>
+        <v>732864.1488705241</v>
       </c>
       <c r="D45">
-        <v>741560.6946576232</v>
+        <v>741125.8059030898</v>
       </c>
       <c r="E45">
-        <v>740161.1916720525</v>
+        <v>739966.4185087607</v>
       </c>
       <c r="F45">
-        <v>765690.2165279993</v>
+        <v>765206.4837871309</v>
       </c>
       <c r="G45">
-        <v>753090.754141839</v>
+        <v>752715.5796979605</v>
       </c>
       <c r="H45">
-        <v>749863.3106894514</v>
+        <v>749469.2998070974</v>
       </c>
       <c r="I45">
-        <v>764301.0877461438</v>
+        <v>764077.8822600939</v>
       </c>
       <c r="J45">
-        <v>777336.0402942862</v>
+        <v>777172.5171708703</v>
       </c>
       <c r="K45">
-        <v>774306.7186355286</v>
+        <v>774131.0782589886</v>
       </c>
     </row>
     <row r="46">
@@ -4615,34 +4615,34 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>737923.2360218903</v>
+        <v>781068.7330624585</v>
       </c>
       <c r="C46">
-        <v>720196.440764036</v>
+        <v>716244.8295165404</v>
       </c>
       <c r="D46">
-        <v>726867.996960915</v>
+        <v>726395.0911099854</v>
       </c>
       <c r="E46">
-        <v>724101.1996986707</v>
+        <v>723919.8638305437</v>
       </c>
       <c r="F46">
-        <v>753482.2446818175</v>
+        <v>752959.0334192642</v>
       </c>
       <c r="G46">
-        <v>740421.7042247769</v>
+        <v>740035.9915069832</v>
       </c>
       <c r="H46">
-        <v>737094.7569982166</v>
+        <v>736687.2342897276</v>
       </c>
       <c r="I46">
-        <v>750401.8034249388</v>
+        <v>750178.4316536631</v>
       </c>
       <c r="J46">
-        <v>765337.064984823</v>
+        <v>765184.339479747</v>
       </c>
       <c r="K46">
-        <v>762138.1366637533</v>
+        <v>761972.7166537471</v>
       </c>
     </row>
     <row r="47">
@@ -4650,34 +4650,34 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>724853.2040680789</v>
+        <v>750689.3397003618</v>
       </c>
       <c r="C47">
-        <v>722415.9306135171</v>
+        <v>717978.6794835596</v>
       </c>
       <c r="D47">
-        <v>729300.8325974124</v>
+        <v>728780.7981867999</v>
       </c>
       <c r="E47">
-        <v>725368.5564076899</v>
+        <v>725165.1356593157</v>
       </c>
       <c r="F47">
-        <v>759698.7439343135</v>
+        <v>759121.5061402626</v>
       </c>
       <c r="G47">
-        <v>743896.2729554829</v>
+        <v>743478.8118560329</v>
       </c>
       <c r="H47">
-        <v>740324.9535218326</v>
+        <v>739885.2326590568</v>
       </c>
       <c r="I47">
-        <v>755200.0923780837</v>
+        <v>754937.7992410815</v>
       </c>
       <c r="J47">
-        <v>771061.1020925633</v>
+        <v>770879.0637046852</v>
       </c>
       <c r="K47">
-        <v>767508.2216157548</v>
+        <v>767315.1907058581</v>
       </c>
     </row>
     <row r="48">
@@ -4685,34 +4685,34 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>716702.2369444078</v>
+        <v>703451.3901007739</v>
       </c>
       <c r="C48">
-        <v>733153.6660365923</v>
+        <v>727698.3155096094</v>
       </c>
       <c r="D48">
-        <v>738641.0217880518</v>
+        <v>738049.1908201203</v>
       </c>
       <c r="E48">
-        <v>735846.9585996445</v>
+        <v>735561.6640298757</v>
       </c>
       <c r="F48">
-        <v>773945.3919174089</v>
+        <v>773287.2334616265</v>
       </c>
       <c r="G48">
-        <v>753266.5404784899</v>
+        <v>752785.0690830101</v>
       </c>
       <c r="H48">
-        <v>749385.6447297478</v>
+        <v>748885.072201205</v>
       </c>
       <c r="I48">
-        <v>770554.9495428894</v>
+        <v>770190.0765083767</v>
       </c>
       <c r="J48">
-        <v>785919.8543595688</v>
+        <v>785646.5669501736</v>
       </c>
       <c r="K48">
-        <v>781931.1813634594</v>
+        <v>781651.8713595798</v>
       </c>
     </row>
     <row r="49">
@@ -4720,34 +4720,34 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>717084.9805191775</v>
+        <v>659228.5767542726</v>
       </c>
       <c r="C49">
-        <v>750013.026519359</v>
+        <v>743066.7917242413</v>
       </c>
       <c r="D49">
-        <v>753936.9890145172</v>
+        <v>753235.3561214572</v>
       </c>
       <c r="E49">
-        <v>754468.4020568507</v>
+        <v>754047.0316554696</v>
       </c>
       <c r="F49">
-        <v>794391.4882958052</v>
+        <v>793610.6606397508</v>
       </c>
       <c r="G49">
-        <v>768061.7542965428</v>
+        <v>767483.888276567</v>
       </c>
       <c r="H49">
-        <v>763977.5685067893</v>
+        <v>763385.0494520317</v>
       </c>
       <c r="I49">
-        <v>794682.9050368753</v>
+        <v>794157.7988904743</v>
       </c>
       <c r="J49">
-        <v>808697.8669673275</v>
+        <v>808284.1492978525</v>
       </c>
       <c r="K49">
-        <v>804387.7736829745</v>
+        <v>803974.1688913517</v>
       </c>
     </row>
     <row r="50">
@@ -4755,34 +4755,34 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>726666.1032370173</v>
+        <v>603258.258652782</v>
       </c>
       <c r="C50">
-        <v>753502.3081995877</v>
+        <v>744892.6203785092</v>
       </c>
       <c r="D50">
-        <v>757939.144014151</v>
+        <v>757083.4794124088</v>
       </c>
       <c r="E50">
-        <v>762781.7610043132</v>
+        <v>762211.4757505163</v>
       </c>
       <c r="F50">
-        <v>802557.5587577436</v>
+        <v>801605.678300111</v>
       </c>
       <c r="G50">
-        <v>772606.5097516632</v>
+        <v>771909.4408876628</v>
       </c>
       <c r="H50">
-        <v>768397.6814638064</v>
+        <v>767688.3503330592</v>
       </c>
       <c r="I50">
-        <v>807721.6667830356</v>
+        <v>807020.8006144512</v>
       </c>
       <c r="J50">
-        <v>821365.2571679463</v>
+        <v>820804.3981813219</v>
       </c>
       <c r="K50">
-        <v>816922.5198344819</v>
+        <v>816366.193933082</v>
       </c>
     </row>
     <row r="51">
@@ -4790,34 +4790,34 @@
         <v>2026</v>
       </c>
       <c r="B51">
-        <v>735406.0334080382</v>
+        <v>548859.7226640182</v>
       </c>
       <c r="C51">
-        <v>762905.1736837428</v>
+        <v>752661.1641525137</v>
       </c>
       <c r="D51">
-        <v>770673.1251160493</v>
+        <v>769624.7461705933</v>
       </c>
       <c r="E51">
-        <v>777946.2525570928</v>
+        <v>777244.0900883975</v>
       </c>
       <c r="F51">
-        <v>818177.3024917761</v>
+        <v>817013.3154065446</v>
       </c>
       <c r="G51">
-        <v>787461.5057158046</v>
+        <v>786631.8534426894</v>
       </c>
       <c r="H51">
-        <v>783191.0878057498</v>
+        <v>782348.141943867</v>
       </c>
       <c r="I51">
-        <v>826372.8070684612</v>
+        <v>825514.4562698634</v>
       </c>
       <c r="J51">
-        <v>841588.1322488773</v>
+        <v>840904.4609181711</v>
       </c>
       <c r="K51">
-        <v>837087.7284249328</v>
+        <v>836410.5312102168</v>
       </c>
     </row>
     <row r="52">
@@ -4825,34 +4825,34 @@
         <v>2027</v>
       </c>
       <c r="B52">
-        <v>744114.0949604358</v>
+        <v>486645.1391019871</v>
       </c>
       <c r="C52">
-        <v>765336.7906403395</v>
+        <v>753316.7629759915</v>
       </c>
       <c r="D52">
-        <v>778678.3208799902</v>
+        <v>777388.9157432663</v>
       </c>
       <c r="E52">
-        <v>787187.8767626106</v>
+        <v>786351.6022173653</v>
       </c>
       <c r="F52">
-        <v>827953.3536246524</v>
+        <v>826532.0963547141</v>
       </c>
       <c r="G52">
-        <v>798535.0120359762</v>
+        <v>797549.502536851</v>
       </c>
       <c r="H52">
-        <v>794202.3675624598</v>
+        <v>793200.2484334348</v>
       </c>
       <c r="I52">
-        <v>837847.2772368306</v>
+        <v>836833.1748250134</v>
       </c>
       <c r="J52">
-        <v>855963.3645086188</v>
+        <v>855167.7383083052</v>
       </c>
       <c r="K52">
-        <v>851428.4446468863</v>
+        <v>850639.6426257255</v>
       </c>
     </row>
     <row r="53">
@@ -4860,34 +4860,34 @@
         <v>2028</v>
       </c>
       <c r="B53">
-        <v>754477.525936779</v>
+        <v>435678.2255520091</v>
       </c>
       <c r="C53">
-        <v>766562.3953206657</v>
+        <v>752372.4721804792</v>
       </c>
       <c r="D53">
-        <v>786651.0841360036</v>
+        <v>785062.3139536423</v>
       </c>
       <c r="E53">
-        <v>795418.0346508649</v>
+        <v>794403.9269355481</v>
       </c>
       <c r="F53">
-        <v>836636.1063487517</v>
+        <v>834906.0501544464</v>
       </c>
       <c r="G53">
-        <v>809646.6954840404</v>
+        <v>808469.5930000294</v>
       </c>
       <c r="H53">
-        <v>805339.6315449984</v>
+        <v>804142.4479037968</v>
       </c>
       <c r="I53">
-        <v>847071.2798260753</v>
+        <v>845868.0433842523</v>
       </c>
       <c r="J53">
-        <v>868430.3234620448</v>
+        <v>867504.9336612354</v>
       </c>
       <c r="K53">
-        <v>863937.3158849636</v>
+        <v>863018.1664714726</v>
       </c>
     </row>
     <row r="54">
@@ -4895,34 +4895,34 @@
         <v>2029</v>
       </c>
       <c r="B54">
-        <v>766348.9952965893</v>
+        <v>393764.1139857216</v>
       </c>
       <c r="C54">
-        <v>768897.3493719987</v>
+        <v>752190.996131896</v>
       </c>
       <c r="D54">
-        <v>796533.9453934075</v>
+        <v>794587.6283792378</v>
       </c>
       <c r="E54">
-        <v>805104.9628080728</v>
+        <v>803848.4888878369</v>
       </c>
       <c r="F54">
-        <v>846840.2387234725</v>
+        <v>844752.8694371115</v>
       </c>
       <c r="G54">
-        <v>822003.4248927301</v>
+        <v>820599.2954432915</v>
       </c>
       <c r="H54">
-        <v>817835.5560259168</v>
+        <v>816408.6354619265</v>
       </c>
       <c r="I54">
-        <v>857257.954540719</v>
+        <v>855810.7101600659</v>
       </c>
       <c r="J54">
-        <v>881286.6416421256</v>
+        <v>880198.2471630534</v>
       </c>
       <c r="K54">
-        <v>876947.0782656193</v>
+        <v>875863.706924341</v>
       </c>
     </row>
     <row r="55">
@@ -4930,34 +4930,34 @@
         <v>2030</v>
       </c>
       <c r="B55">
-        <v>782133.188903661</v>
+        <v>381059.2984059468</v>
       </c>
       <c r="C55">
-        <v>775127.4869365044</v>
+        <v>755902.9575041068</v>
       </c>
       <c r="D55">
-        <v>809569.1722672426</v>
+        <v>807234.4757058737</v>
       </c>
       <c r="E55">
-        <v>817956.9121077996</v>
+        <v>816396.930137524</v>
       </c>
       <c r="F55">
-        <v>859884.1746903816</v>
+        <v>857417.683087991</v>
       </c>
       <c r="G55">
-        <v>836401.6914095557</v>
+        <v>834748.9894108864</v>
       </c>
       <c r="H55">
-        <v>832414.4519324681</v>
+        <v>830738.6274920852</v>
       </c>
       <c r="I55">
-        <v>870237.0222353939</v>
+        <v>868494.9639644567</v>
       </c>
       <c r="J55">
-        <v>895845.6960789922</v>
+        <v>894560.9761375369</v>
       </c>
       <c r="K55">
-        <v>891703.5135616723</v>
+        <v>890423.5139088588</v>
       </c>
     </row>
     <row r="56">
@@ -4965,34 +4965,34 @@
         <v>2031</v>
       </c>
       <c r="B56">
-        <v>801908.1778345566</v>
+        <v>392258.7882940907</v>
       </c>
       <c r="C56">
-        <v>787678.5379494631</v>
+        <v>766597.606646163</v>
       </c>
       <c r="D56">
-        <v>826147.171398851</v>
+        <v>823435.4971200381</v>
       </c>
       <c r="E56">
-        <v>834457.4634033942</v>
+        <v>832563.0995097517</v>
       </c>
       <c r="F56">
-        <v>876234.2883690943</v>
+        <v>873407.1369443431</v>
       </c>
       <c r="G56">
-        <v>853194.3861004002</v>
+        <v>851294.0475266865</v>
       </c>
       <c r="H56">
-        <v>849301.8167441115</v>
+        <v>847381.104436262</v>
       </c>
       <c r="I56">
-        <v>886594.6240830858</v>
+        <v>884535.3476688768</v>
       </c>
       <c r="J56">
-        <v>912569.8776889351</v>
+        <v>911070.6012488982</v>
       </c>
       <c r="K56">
-        <v>908554.5519917329</v>
+        <v>907061.79025335</v>
       </c>
     </row>
     <row r="57">
@@ -5000,34 +5000,34 @@
         <v>2032</v>
       </c>
       <c r="B57">
-        <v>822690.1587831541</v>
+        <v>420899.370021023</v>
       </c>
       <c r="C57">
-        <v>805055.0970099829</v>
+        <v>783037.0064639165</v>
       </c>
       <c r="D57">
-        <v>844737.7109821215</v>
+        <v>841684.6886667088</v>
       </c>
       <c r="E57">
-        <v>853123.3470314104</v>
+        <v>850896.7578093872</v>
       </c>
       <c r="F57">
-        <v>894573.8344097594</v>
+        <v>891427.3827098778</v>
       </c>
       <c r="G57">
-        <v>870972.0722120963</v>
+        <v>868841.8644838944</v>
       </c>
       <c r="H57">
-        <v>867135.5764315792</v>
+        <v>864989.3572586732</v>
       </c>
       <c r="I57">
-        <v>905005.8196356754</v>
+        <v>902637.1474478515</v>
       </c>
       <c r="J57">
-        <v>930320.2849427001</v>
+        <v>928608.8399265972</v>
       </c>
       <c r="K57">
-        <v>926378.9862029013</v>
+        <v>924677.0283290198</v>
       </c>
     </row>
     <row r="58">
@@ -5035,34 +5035,34 @@
         <v>2033</v>
       </c>
       <c r="B58">
-        <v>842681.8715421202</v>
+        <v>449325.5951672054</v>
       </c>
       <c r="C58">
-        <v>824004.0799767638</v>
+        <v>801588.958608675</v>
       </c>
       <c r="D58">
-        <v>863344.2811358831</v>
+        <v>859985.6469928008</v>
       </c>
       <c r="E58">
-        <v>871870.1752988687</v>
+        <v>869329.5443283583</v>
       </c>
       <c r="F58">
-        <v>912923.4594622715</v>
+        <v>909497.2703872498</v>
       </c>
       <c r="G58">
-        <v>888453.2782735466</v>
+        <v>886113.8984359673</v>
       </c>
       <c r="H58">
-        <v>884626.0178135624</v>
+        <v>882275.6247615891</v>
       </c>
       <c r="I58">
-        <v>923433.0749445333</v>
+        <v>920776.5347386062</v>
       </c>
       <c r="J58">
-        <v>947640.039498201</v>
+        <v>945729.4392004453</v>
       </c>
       <c r="K58">
-        <v>943735.4198443748</v>
+        <v>941837.7246577668</v>
       </c>
     </row>
     <row r="59">
@@ -5070,34 +5070,34 @@
         <v>2034</v>
       </c>
       <c r="B59">
-        <v>860454.7830581063</v>
+        <v>481921.5372174126</v>
       </c>
       <c r="C59">
-        <v>841891.8281200358</v>
+        <v>819354.4138139561</v>
       </c>
       <c r="D59">
-        <v>880407.6897748635</v>
+        <v>876774.6977297688</v>
       </c>
       <c r="E59">
-        <v>889033.9447313303</v>
+        <v>886206.7589374428</v>
       </c>
       <c r="F59">
-        <v>929995.6828840662</v>
+        <v>926323.7298997518</v>
       </c>
       <c r="G59">
-        <v>904244.9992349767</v>
+        <v>901717.539157226</v>
       </c>
       <c r="H59">
-        <v>900432.2157621604</v>
+        <v>897898.421882635</v>
       </c>
       <c r="I59">
-        <v>940544.2187585958</v>
+        <v>937626.8229443062</v>
       </c>
       <c r="J59">
-        <v>963456.430004466</v>
+        <v>961365.1366735243</v>
       </c>
       <c r="K59">
-        <v>959582.6030741407</v>
+        <v>957507.4870541808</v>
       </c>
     </row>
     <row r="60">
@@ -5105,34 +5105,34 @@
         <v>2035</v>
       </c>
       <c r="B60">
-        <v>876768.1438986205</v>
+        <v>509543.0270817641</v>
       </c>
       <c r="C60">
-        <v>858842.7655436336</v>
+        <v>836319.2212777862</v>
       </c>
       <c r="D60">
-        <v>896150.5488958587</v>
+        <v>892273.419960456</v>
       </c>
       <c r="E60">
-        <v>904852.8997292037</v>
+        <v>901765.1968468134</v>
       </c>
       <c r="F60">
-        <v>945625.4270717086</v>
+        <v>941738.9869167344</v>
       </c>
       <c r="G60">
-        <v>918724.9399245981</v>
+        <v>916029.0112838533</v>
       </c>
       <c r="H60">
-        <v>914886.9713913655</v>
+        <v>912189.309433028</v>
       </c>
       <c r="I60">
-        <v>956191.202593943</v>
+        <v>953039.9713683734</v>
       </c>
       <c r="J60">
-        <v>977783.1708585034</v>
+        <v>975529.4453413378</v>
       </c>
       <c r="K60">
-        <v>973917.8930433175</v>
+        <v>971683.5420563524</v>
       </c>
     </row>
     <row r="61">
@@ -5140,34 +5140,34 @@
         <v>2036</v>
       </c>
       <c r="B61">
-        <v>891868.8648309549</v>
+        <v>539229.0668749165</v>
       </c>
       <c r="C61">
-        <v>874991.165194961</v>
+        <v>852556.877205419</v>
       </c>
       <c r="D61">
-        <v>910848.5461117659</v>
+        <v>906755.4661559565</v>
       </c>
       <c r="E61">
-        <v>919635.7767475878</v>
+        <v>916311.2137214525</v>
       </c>
       <c r="F61">
-        <v>959826.0093858289</v>
+        <v>955753.7096931316</v>
       </c>
       <c r="G61">
-        <v>932029.7970113447</v>
+        <v>929183.5880894054</v>
       </c>
       <c r="H61">
-        <v>928197.6575121328</v>
+        <v>925354.1298454179</v>
       </c>
       <c r="I61">
-        <v>970409.3006317827</v>
+        <v>967050.0969391823</v>
       </c>
       <c r="J61">
-        <v>990654.983208015</v>
+        <v>988256.5592934182</v>
       </c>
       <c r="K61">
-        <v>986804.3272103323</v>
+        <v>984428.1925521321</v>
       </c>
     </row>
     <row r="62">
@@ -5175,34 +5175,34 @@
         <v>2037</v>
       </c>
       <c r="B62">
-        <v>905542.4163424436</v>
+        <v>565545.5535401836</v>
       </c>
       <c r="C62">
-        <v>889894.8181320555</v>
+        <v>867591.2737654775</v>
       </c>
       <c r="D62">
-        <v>924166.7900362826</v>
+        <v>919883.6584116054</v>
       </c>
       <c r="E62">
-        <v>933171.6149773363</v>
+        <v>929634.729033347</v>
       </c>
       <c r="F62">
-        <v>972438.3565946319</v>
+        <v>968205.8505270467</v>
       </c>
       <c r="G62">
-        <v>944069.2755104064</v>
+        <v>941089.7204489923</v>
       </c>
       <c r="H62">
-        <v>940212.1469872807</v>
+        <v>937239.5915716812</v>
       </c>
       <c r="I62">
-        <v>983089.8340038862</v>
+        <v>979547.8524639085</v>
       </c>
       <c r="J62">
-        <v>1002073.19104454</v>
+        <v>999547.0097710444</v>
       </c>
       <c r="K62">
-        <v>998221.4588875723</v>
+        <v>995720.3738197929</v>
       </c>
     </row>
     <row r="63">
@@ -5210,34 +5210,34 @@
         <v>2038</v>
       </c>
       <c r="B63">
-        <v>917897.5717441108</v>
+        <v>590868.7800545929</v>
       </c>
       <c r="C63">
-        <v>902984.3301377172</v>
+        <v>880842.2697661368</v>
       </c>
       <c r="D63">
-        <v>935802.8846641905</v>
+        <v>931352.1378957033</v>
       </c>
       <c r="E63">
-        <v>945071.0340344566</v>
+        <v>941344.3080025417</v>
       </c>
       <c r="F63">
-        <v>983361.6153669322</v>
+        <v>978991.504164583</v>
       </c>
       <c r="G63">
-        <v>954459.5242443979</v>
+        <v>951362.8102275548</v>
       </c>
       <c r="H63">
-        <v>950615.8961155267</v>
+        <v>947529.8475364195</v>
       </c>
       <c r="I63">
-        <v>994086.31422687</v>
+        <v>990385.0824750175</v>
       </c>
       <c r="J63">
-        <v>1011882.481024619</v>
+        <v>1009245.485383733</v>
       </c>
       <c r="K63">
-        <v>1008046.355070624</v>
+        <v>1005436.773225708</v>
       </c>
     </row>
     <row r="64">
@@ -5245,34 +5245,34 @@
         <v>2039</v>
       </c>
       <c r="B64">
-        <v>928010.2021182209</v>
+        <v>613352.4758683937</v>
       </c>
       <c r="C64">
-        <v>913594.7696743059</v>
+        <v>891677.2245604389</v>
       </c>
       <c r="D64">
-        <v>945225.1479398037</v>
+        <v>940629.2975866676</v>
       </c>
       <c r="E64">
-        <v>954579.7886349461</v>
+        <v>950692.6345727851</v>
       </c>
       <c r="F64">
-        <v>992508.6079345419</v>
+        <v>988021.6593341392</v>
       </c>
       <c r="G64">
-        <v>962954.0436809177</v>
+        <v>959756.7739883277</v>
       </c>
       <c r="H64">
-        <v>959108.9726797935</v>
+        <v>955925.4212781168</v>
       </c>
       <c r="I64">
-        <v>1003217.559899761</v>
+        <v>999381.434743281</v>
       </c>
       <c r="J64">
-        <v>1020044.699550697</v>
+        <v>1017313.93951279</v>
       </c>
       <c r="K64">
-        <v>1016214.48512161</v>
+        <v>1013513.161547046</v>
       </c>
     </row>
     <row r="65">
@@ -5280,34 +5280,34 @@
         <v>2040</v>
       </c>
       <c r="B65">
-        <v>937078.0134360138</v>
+        <v>634152.1143628854</v>
       </c>
       <c r="C65">
-        <v>922844.3380808802</v>
+        <v>901160.2223718838</v>
       </c>
       <c r="D65">
-        <v>953367.5670067391</v>
+        <v>948646.3561117788</v>
       </c>
       <c r="E65">
-        <v>962697.4592198342</v>
+        <v>958670.7474707061</v>
       </c>
       <c r="F65">
-        <v>1000394.044241938</v>
+        <v>995808.4427283499</v>
       </c>
       <c r="G65">
-        <v>970207.0079770877</v>
+        <v>966923.0253117805</v>
       </c>
       <c r="H65">
-        <v>966355.8676013964</v>
+        <v>963088.2141085262</v>
       </c>
       <c r="I65">
-        <v>1011040.358451933</v>
+        <v>1007088.819186375</v>
       </c>
       <c r="J65">
-        <v>1026977.658424906</v>
+        <v>1024166.941584994</v>
       </c>
       <c r="K65">
-        <v>1023148.571682237</v>
+        <v>1020369.053447895</v>
       </c>
     </row>
     <row r="66">
@@ -5315,34 +5315,34 @@
         <v>2041</v>
       </c>
       <c r="B66">
-        <v>944978.5718764915</v>
+        <v>653076.1318203756</v>
       </c>
       <c r="C66">
-        <v>931090.4403974414</v>
+        <v>909628.1863759588</v>
       </c>
       <c r="D66">
-        <v>960522.5750183482</v>
+        <v>955693.8841146933</v>
       </c>
       <c r="E66">
-        <v>969777.5446052094</v>
+        <v>965630.0124630255</v>
       </c>
       <c r="F66">
-        <v>1007227.401027987</v>
+        <v>1002558.957092579</v>
       </c>
       <c r="G66">
-        <v>976584.6784870722</v>
+        <v>973225.7393522086</v>
       </c>
       <c r="H66">
-        <v>972730.7198160002</v>
+        <v>969390.5336777383</v>
       </c>
       <c r="I66">
-        <v>1017798.292638899</v>
+        <v>1013748.371801528</v>
       </c>
       <c r="J66">
-        <v>1032948.678464522</v>
+        <v>1030069.519366523</v>
       </c>
       <c r="K66">
-        <v>1029120.259505558</v>
+        <v>1026273.852971671</v>
       </c>
     </row>
     <row r="67">
@@ -5350,34 +5350,34 @@
         <v>2042</v>
       </c>
       <c r="B67">
-        <v>951740.3046753434</v>
+        <v>670073.6054667915</v>
       </c>
       <c r="C67">
-        <v>938577.2085124686</v>
+        <v>917302.174990915</v>
       </c>
       <c r="D67">
-        <v>966991.2868483961</v>
+        <v>962068.6762667055</v>
       </c>
       <c r="E67">
-        <v>976167.4917924494</v>
+        <v>971912.391451641</v>
       </c>
       <c r="F67">
-        <v>1013191.556985788</v>
+        <v>1008453.239947849</v>
       </c>
       <c r="G67">
-        <v>982287.2273309258</v>
+        <v>978862.682435694</v>
       </c>
       <c r="H67">
-        <v>978429.6020251815</v>
+        <v>975026.0259259949</v>
       </c>
       <c r="I67">
-        <v>1023696.029347324</v>
+        <v>1019561.565338033</v>
       </c>
       <c r="J67">
-        <v>1038121.869789542</v>
+        <v>1035183.828328628</v>
       </c>
       <c r="K67">
-        <v>1034291.850002057</v>
+        <v>1031387.927857199</v>
       </c>
     </row>
     <row r="68">
@@ -5385,34 +5385,34 @@
         <v>2043</v>
       </c>
       <c r="B68">
-        <v>957506.8740447799</v>
+        <v>685178.8529223613</v>
       </c>
       <c r="C68">
-        <v>945127.2000551061</v>
+        <v>924037.281673286</v>
       </c>
       <c r="D68">
-        <v>972635.5512389415</v>
+        <v>967633.0770070815</v>
       </c>
       <c r="E68">
-        <v>981780.5032600061</v>
+        <v>977431.7346696008</v>
       </c>
       <c r="F68">
-        <v>1018288.391291727</v>
+        <v>1013492.149280897</v>
       </c>
       <c r="G68">
-        <v>987197.964607124</v>
+        <v>983717.7827241906</v>
       </c>
       <c r="H68">
-        <v>983351.8582499002</v>
+        <v>979894.535024991</v>
       </c>
       <c r="I68">
-        <v>1028754.826127243</v>
+        <v>1024548.831276598</v>
       </c>
       <c r="J68">
-        <v>1042525.544731795</v>
+        <v>1039537.745899076</v>
       </c>
       <c r="K68">
-        <v>1038699.393609994</v>
+        <v>1035746.832463796</v>
       </c>
     </row>
     <row r="69">
@@ -5420,34 +5420,34 @@
         <v>2044</v>
       </c>
       <c r="B69">
-        <v>962834.5798553249</v>
+        <v>700670.9457740904</v>
       </c>
       <c r="C69">
-        <v>950968.2834305452</v>
+        <v>930035.1268513014</v>
       </c>
       <c r="D69">
-        <v>977572.5380401083</v>
+        <v>972503.2499568295</v>
       </c>
       <c r="E69">
-        <v>986711.75423443</v>
+        <v>982282.0304621691</v>
       </c>
       <c r="F69">
-        <v>1022634.184455611</v>
+        <v>1017790.381659052</v>
       </c>
       <c r="G69">
-        <v>991482.3068631541</v>
+        <v>987955.0019532354</v>
       </c>
       <c r="H69">
-        <v>987626.0581177705</v>
+        <v>984123.550031325</v>
       </c>
       <c r="I69">
-        <v>1033078.03974286</v>
+        <v>1028811.91215279</v>
       </c>
       <c r="J69">
-        <v>1046278.879766039</v>
+        <v>1043249.025940472</v>
       </c>
       <c r="K69">
-        <v>1042447.360895124</v>
+        <v>1039453.831969023</v>
       </c>
     </row>
     <row r="70">
@@ -5455,34 +5455,34 @@
         <v>2045</v>
       </c>
       <c r="B70">
-        <v>967196.5364457704</v>
+        <v>713354.7986213404</v>
       </c>
       <c r="C70">
-        <v>956407.6082196048</v>
+        <v>935733.745535995</v>
       </c>
       <c r="D70">
-        <v>981926.0453351386</v>
+        <v>976805.1524926075</v>
       </c>
       <c r="E70">
-        <v>991059.5649079154</v>
+        <v>986563.8987802279</v>
       </c>
       <c r="F70">
-        <v>1026333.969172865</v>
+        <v>1021452.676913373</v>
       </c>
       <c r="G70">
-        <v>995209.739544729</v>
+        <v>991645.2021354075</v>
       </c>
       <c r="H70">
-        <v>991342.454661588</v>
+        <v>987804.3689272094</v>
       </c>
       <c r="I70">
-        <v>1036758.669322066</v>
+        <v>1032443.599841348</v>
       </c>
       <c r="J70">
-        <v>1049452.786672076</v>
+        <v>1046388.539374263</v>
       </c>
       <c r="K70">
-        <v>1045615.799678256</v>
+        <v>1042588.781871747</v>
       </c>
     </row>
     <row r="71">
@@ -5490,34 +5490,34 @@
         <v>2046</v>
       </c>
       <c r="B71">
-        <v>970767.8044499594</v>
+        <v>723739.4590148998</v>
       </c>
       <c r="C71">
-        <v>960860.9507003872</v>
+        <v>940399.3799032184</v>
       </c>
       <c r="D71">
-        <v>985490.3956413293</v>
+        <v>980327.252395393</v>
       </c>
       <c r="E71">
-        <v>994619.2512148585</v>
+        <v>990069.5960528528</v>
       </c>
       <c r="F71">
-        <v>1029363.096700649</v>
+        <v>1024451.110664936</v>
       </c>
       <c r="G71">
-        <v>998261.5033111623</v>
+        <v>994666.4825095658</v>
       </c>
       <c r="H71">
-        <v>994385.1828026441</v>
+        <v>990817.9685537805</v>
       </c>
       <c r="I71">
-        <v>1039772.11394925</v>
+        <v>1035416.974237545</v>
       </c>
       <c r="J71">
-        <v>1052051.361863455</v>
+        <v>1048958.95557221</v>
       </c>
       <c r="K71">
-        <v>1048209.897949251</v>
+        <v>1045155.461766466</v>
       </c>
     </row>
     <row r="72">
@@ -5525,34 +5525,34 @@
         <v>2047</v>
       </c>
       <c r="B72">
-        <v>973691.7113924723</v>
+        <v>732241.6998393778</v>
       </c>
       <c r="C72">
-        <v>964507.0391433925</v>
+        <v>944219.2782422816</v>
       </c>
       <c r="D72">
-        <v>988408.6388517505</v>
+        <v>983210.9039012165</v>
       </c>
       <c r="E72">
-        <v>997533.6758656634</v>
+        <v>992939.8182209325</v>
       </c>
       <c r="F72">
-        <v>1031843.136562641</v>
+        <v>1026906.020588409</v>
       </c>
       <c r="G72">
-        <v>1000760.07615787</v>
+        <v>997140.0976655602</v>
       </c>
       <c r="H72">
-        <v>996876.3579049825</v>
+        <v>993285.2952455186</v>
       </c>
       <c r="I72">
-        <v>1042239.313738224</v>
+        <v>1037851.367296126</v>
       </c>
       <c r="J72">
-        <v>1054178.895286822</v>
+        <v>1051063.434361679</v>
       </c>
       <c r="K72">
-        <v>1050333.765980221</v>
+        <v>1047256.88152958</v>
       </c>
     </row>
     <row r="73">
@@ -5560,34 +5560,34 @@
         <v>2048</v>
       </c>
       <c r="B73">
-        <v>976085.6039254458</v>
+        <v>739202.745872453</v>
       </c>
       <c r="C73">
-        <v>967492.203880123</v>
+        <v>947346.7464861043</v>
       </c>
       <c r="D73">
-        <v>990797.8943130835</v>
+        <v>985571.8380701938</v>
       </c>
       <c r="E73">
-        <v>999919.8049548061</v>
+        <v>995289.7573781055</v>
       </c>
       <c r="F73">
-        <v>1033873.621466513</v>
+        <v>1028915.930838792</v>
       </c>
       <c r="G73">
-        <v>1002805.734586276</v>
+        <v>999165.3224650525</v>
       </c>
       <c r="H73">
-        <v>998915.9595725692</v>
+        <v>995305.3714859347</v>
       </c>
       <c r="I73">
-        <v>1044259.286079444</v>
+        <v>1039844.479758266</v>
       </c>
       <c r="J73">
-        <v>1055920.772328734</v>
+        <v>1052786.435865817</v>
       </c>
       <c r="K73">
-        <v>1052072.642052656</v>
+        <v>1048977.378514767</v>
       </c>
     </row>
     <row r="74">
@@ -5595,34 +5595,34 @@
         <v>2049</v>
       </c>
       <c r="B74">
-        <v>978045.5573617549</v>
+        <v>744901.9683333231</v>
       </c>
       <c r="C74">
-        <v>969936.2500530883</v>
+        <v>949907.3009165968</v>
       </c>
       <c r="D74">
-        <v>992754.0512362362</v>
+        <v>987504.807480328</v>
       </c>
       <c r="E74">
-        <v>1001873.402220901</v>
+        <v>997213.7248339453</v>
       </c>
       <c r="F74">
-        <v>1035536.041900974</v>
+        <v>1030561.506171707</v>
       </c>
       <c r="G74">
-        <v>1004480.578051905</v>
+        <v>1000823.436290293</v>
       </c>
       <c r="H74">
-        <v>1000585.844181851</v>
+        <v>996959.2700275256</v>
       </c>
       <c r="I74">
-        <v>1045913.099555568</v>
+        <v>1041476.302225363</v>
       </c>
       <c r="J74">
-        <v>1057346.900631029</v>
+        <v>1054197.110184855</v>
       </c>
       <c r="K74">
-        <v>1053496.313368949</v>
+        <v>1050386.002307118</v>
       </c>
     </row>
     <row r="75">
@@ -5630,34 +5630,34 @@
         <v>2050</v>
       </c>
       <c r="B75">
-        <v>979650.2315146622</v>
+        <v>749568.0970306704</v>
       </c>
       <c r="C75">
-        <v>971937.2658168374</v>
+        <v>952003.7055737709</v>
       </c>
       <c r="D75">
-        <v>994355.6170670678</v>
+        <v>989087.388981164</v>
       </c>
       <c r="E75">
-        <v>1003472.872381782</v>
+        <v>998788.9361579624</v>
       </c>
       <c r="F75">
-        <v>1036897.116635212</v>
+        <v>1031908.789303271</v>
       </c>
       <c r="G75">
-        <v>1005851.823903807</v>
+        <v>1002180.985071121</v>
       </c>
       <c r="H75">
-        <v>1001953.030065563</v>
+        <v>998313.3676259968</v>
       </c>
       <c r="I75">
-        <v>1047267.127508325</v>
+        <v>1042812.325462739</v>
       </c>
       <c r="J75">
-        <v>1058514.515729952</v>
+        <v>1055352.072632429</v>
       </c>
       <c r="K75">
-        <v>1054661.916857874</v>
+        <v>1051539.285925432</v>
       </c>
     </row>
   </sheetData>
@@ -5732,34 +5732,34 @@
         <v>1977</v>
       </c>
       <c r="B2">
-        <v>561923.5906346415</v>
+        <v>795730.85198596</v>
       </c>
       <c r="C2">
-        <v>561960.6585428691</v>
+        <v>490467.4415955291</v>
       </c>
       <c r="D2">
-        <v>766173.0230304888</v>
+        <v>756238.8056718165</v>
       </c>
       <c r="E2">
-        <v>760629.3122990479</v>
+        <v>753234.9040242136</v>
       </c>
       <c r="F2">
-        <v>681643.611268725</v>
+        <v>673578.5724180037</v>
       </c>
       <c r="G2">
-        <v>792270.0872658272</v>
+        <v>785660.771863125</v>
       </c>
       <c r="H2">
-        <v>789981.0644502919</v>
+        <v>783405.5301798581</v>
       </c>
       <c r="I2">
-        <v>678029.668701601</v>
+        <v>671966.7023707853</v>
       </c>
       <c r="J2">
-        <v>701916.7299246681</v>
+        <v>697696.9450402025</v>
       </c>
       <c r="K2">
-        <v>699771.8222530062</v>
+        <v>695589.7944324365</v>
       </c>
     </row>
     <row r="3">
@@ -5767,34 +5767,34 @@
         <v>1978</v>
       </c>
       <c r="B3">
-        <v>620526.1004852419</v>
+        <v>9852.731411128578</v>
       </c>
       <c r="C3">
-        <v>617905.0333456716</v>
+        <v>546672.1999453766</v>
       </c>
       <c r="D3">
-        <v>770044.2461150923</v>
+        <v>759004.8429995069</v>
       </c>
       <c r="E3">
-        <v>762902.9757833814</v>
+        <v>754362.8102748668</v>
       </c>
       <c r="F3">
-        <v>685567.5531919083</v>
+        <v>676506.723833918</v>
       </c>
       <c r="G3">
-        <v>793120.9318651621</v>
+        <v>785973.82957678</v>
       </c>
       <c r="H3">
-        <v>790839.9819149839</v>
+        <v>783768.9458923707</v>
       </c>
       <c r="I3">
-        <v>680468.1813300729</v>
+        <v>673381.3053714822</v>
       </c>
       <c r="J3">
-        <v>702205.8829975673</v>
+        <v>697481.2748854386</v>
       </c>
       <c r="K3">
-        <v>700233.1970856884</v>
+        <v>695565.1444518287</v>
       </c>
     </row>
     <row r="4">
@@ -5802,34 +5802,34 @@
         <v>1979</v>
       </c>
       <c r="B4">
-        <v>696002.8680737212</v>
+        <v>3003389.770222277</v>
       </c>
       <c r="C4">
-        <v>688601.3460891246</v>
+        <v>613084.6298995935</v>
       </c>
       <c r="D4">
-        <v>774556.034100285</v>
+        <v>762589.6278328333</v>
       </c>
       <c r="E4">
-        <v>766016.3151393451</v>
+        <v>756469.3389264325</v>
       </c>
       <c r="F4">
-        <v>690131.3773367979</v>
+        <v>680215.9195259226</v>
       </c>
       <c r="G4">
-        <v>794117.6471406514</v>
+        <v>786498.3129583589</v>
       </c>
       <c r="H4">
-        <v>792995.100541655</v>
+        <v>785446.0300745986</v>
       </c>
       <c r="I4">
-        <v>683686.3585346502</v>
+        <v>675685.6203415846</v>
       </c>
       <c r="J4">
-        <v>702252.7535179198</v>
+        <v>697081.501018404</v>
       </c>
       <c r="K4">
-        <v>700951.2142135487</v>
+        <v>695826.7934783368</v>
       </c>
     </row>
     <row r="5">
@@ -5837,34 +5837,34 @@
         <v>1980</v>
       </c>
       <c r="B5">
-        <v>643847.20981868</v>
+        <v>1006611.295300783</v>
       </c>
       <c r="C5">
-        <v>640799.3938950825</v>
+        <v>580885.1322847453</v>
       </c>
       <c r="D5">
-        <v>788102.251674366</v>
+        <v>775178.32566274</v>
       </c>
       <c r="E5">
-        <v>779587.7622680233</v>
+        <v>768915.7754721413</v>
       </c>
       <c r="F5">
-        <v>698549.4909186731</v>
+        <v>687941.6961929426</v>
       </c>
       <c r="G5">
-        <v>807049.1679912538</v>
+        <v>798765.8559892708</v>
       </c>
       <c r="H5">
-        <v>803618.2331094729</v>
+        <v>795526.3245607214</v>
       </c>
       <c r="I5">
-        <v>692127.0709302608</v>
+        <v>683310.8965996705</v>
       </c>
       <c r="J5">
-        <v>710707.253231336</v>
+        <v>704969.0798614766</v>
       </c>
       <c r="K5">
-        <v>708297.1800649411</v>
+        <v>702687.880375925</v>
       </c>
     </row>
     <row r="6">
@@ -5872,34 +5872,34 @@
         <v>1981</v>
       </c>
       <c r="B6">
-        <v>540059.9039221653</v>
+        <v>11450.98703576095</v>
       </c>
       <c r="C6">
-        <v>543788.947710557</v>
+        <v>505754.9981111226</v>
       </c>
       <c r="D6">
-        <v>797744.7661480475</v>
+        <v>784444.7793014121</v>
       </c>
       <c r="E6">
-        <v>793185.6386228956</v>
+        <v>781805.5236564736</v>
       </c>
       <c r="F6">
-        <v>705969.9740335639</v>
+        <v>695053.7496608127</v>
       </c>
       <c r="G6">
-        <v>814492.2836837011</v>
+        <v>805958.5149577924</v>
       </c>
       <c r="H6">
-        <v>810201.2302387072</v>
+        <v>801831.9826718566</v>
       </c>
       <c r="I6">
-        <v>702816.2704764669</v>
+        <v>693435.2957284654</v>
       </c>
       <c r="J6">
-        <v>720254.8405632512</v>
+        <v>714082.9971838898</v>
       </c>
       <c r="K6">
-        <v>716218.5252080044</v>
+        <v>710202.6716794611</v>
       </c>
     </row>
     <row r="7">
@@ -5907,34 +5907,34 @@
         <v>1982</v>
       </c>
       <c r="B7">
-        <v>514936.7750239923</v>
+        <v>676885.6423825875</v>
       </c>
       <c r="C7">
-        <v>524143.0987062187</v>
+        <v>499677.1253123154</v>
       </c>
       <c r="D7">
-        <v>803997.5894316459</v>
+        <v>790776.3874841264</v>
       </c>
       <c r="E7">
-        <v>810219.8675427468</v>
+        <v>798291.7682009902</v>
       </c>
       <c r="F7">
-        <v>710492.9624484114</v>
+        <v>699658.4315547221</v>
       </c>
       <c r="G7">
-        <v>816457.4637569713</v>
+        <v>807909.3643596204</v>
       </c>
       <c r="H7">
-        <v>817981.0762512421</v>
+        <v>809490.5328977419</v>
       </c>
       <c r="I7">
-        <v>716379.0808278025</v>
+        <v>706589.9935513214</v>
       </c>
       <c r="J7">
-        <v>730746.5470988005</v>
+        <v>724259.1420206028</v>
       </c>
       <c r="K7">
-        <v>731475.8807596328</v>
+        <v>725042.7709690671</v>
       </c>
     </row>
     <row r="8">
@@ -5942,34 +5942,34 @@
         <v>1983</v>
       </c>
       <c r="B8">
-        <v>599540.7372996985</v>
+        <v>14990.80223481455</v>
       </c>
       <c r="C8">
-        <v>605071.22767136</v>
+        <v>589938.9536503283</v>
       </c>
       <c r="D8">
-        <v>806919.6520932118</v>
+        <v>794093.5419360269</v>
       </c>
       <c r="E8">
-        <v>828774.2707265893</v>
+        <v>816515.4961517586</v>
       </c>
       <c r="F8">
-        <v>711678.5300759072</v>
+        <v>701189.0867687501</v>
       </c>
       <c r="G8">
-        <v>814331.3552380853</v>
+        <v>805961.3940876883</v>
       </c>
       <c r="H8">
-        <v>813679.0550833651</v>
+        <v>805385.7641406131</v>
       </c>
       <c r="I8">
-        <v>730578.3228268104</v>
+        <v>720581.887951304</v>
       </c>
       <c r="J8">
-        <v>735720.0081205536</v>
+        <v>729167.6214520941</v>
       </c>
       <c r="K8">
-        <v>734352.7047301127</v>
+        <v>727912.0569792922</v>
       </c>
     </row>
     <row r="9">
@@ -5977,34 +5977,34 @@
         <v>1984</v>
       </c>
       <c r="B9">
-        <v>785411.22593608</v>
+        <v>22853.00753771785</v>
       </c>
       <c r="C9">
-        <v>785605.2858448214</v>
+        <v>762587.9011476435</v>
       </c>
       <c r="D9">
-        <v>818131.0030351487</v>
+        <v>805529.3496781153</v>
       </c>
       <c r="E9">
-        <v>846551.3614004275</v>
+        <v>834199.2952578127</v>
       </c>
       <c r="F9">
-        <v>722867.3270745638</v>
+        <v>712504.7678064242</v>
       </c>
       <c r="G9">
-        <v>817605.7520214285</v>
+        <v>809355.8555746033</v>
       </c>
       <c r="H9">
-        <v>820021.7669704068</v>
+        <v>811765.4097730862</v>
       </c>
       <c r="I9">
-        <v>747274.0766543894</v>
+        <v>737145.1841367221</v>
       </c>
       <c r="J9">
-        <v>740563.5655595175</v>
+        <v>734038.2166872802</v>
       </c>
       <c r="K9">
-        <v>740852.0520168897</v>
+        <v>734377.5729303426</v>
       </c>
     </row>
     <row r="10">
@@ -6012,34 +6012,34 @@
         <v>1985</v>
       </c>
       <c r="B10">
-        <v>1260214.359066644</v>
+        <v>1083726.825429597</v>
       </c>
       <c r="C10">
-        <v>1262341.537531293</v>
+        <v>1213063.346278254</v>
       </c>
       <c r="D10">
-        <v>869533.5233763509</v>
+        <v>855981.7309497386</v>
       </c>
       <c r="E10">
-        <v>885021.5187065529</v>
+        <v>871776.2925420299</v>
       </c>
       <c r="F10">
-        <v>765577.301616089</v>
+        <v>754548.9133428507</v>
       </c>
       <c r="G10">
-        <v>897217.3567723101</v>
+        <v>887490.9064799615</v>
       </c>
       <c r="H10">
-        <v>894346.9633949387</v>
+        <v>884783.8648283628</v>
       </c>
       <c r="I10">
-        <v>778665.4432360913</v>
+        <v>767936.8004714373</v>
       </c>
       <c r="J10">
-        <v>796403.6198074564</v>
+        <v>788683.7041715111</v>
       </c>
       <c r="K10">
-        <v>792661.8061597114</v>
+        <v>785121.6186303702</v>
       </c>
     </row>
     <row r="11">
@@ -6047,34 +6047,34 @@
         <v>1986</v>
       </c>
       <c r="B11">
-        <v>1106850.776433271</v>
+        <v>15231.41114944922</v>
       </c>
       <c r="C11">
-        <v>1099960.334730157</v>
+        <v>1084035.323709208</v>
       </c>
       <c r="D11">
-        <v>917168.2131022401</v>
+        <v>902816.6257643141</v>
       </c>
       <c r="E11">
-        <v>911995.2956770303</v>
+        <v>898333.3570426846</v>
       </c>
       <c r="F11">
-        <v>807899.31472286</v>
+        <v>796302.3516839821</v>
       </c>
       <c r="G11">
-        <v>893216.010009618</v>
+        <v>883739.1150130871</v>
       </c>
       <c r="H11">
-        <v>886911.4163958058</v>
+        <v>877665.5698460753</v>
       </c>
       <c r="I11">
-        <v>803346.5931050171</v>
+        <v>792325.2322791807</v>
       </c>
       <c r="J11">
-        <v>791183.1953936046</v>
+        <v>783779.9106226732</v>
       </c>
       <c r="K11">
-        <v>787917.6804689857</v>
+        <v>780678.4946475337</v>
       </c>
     </row>
     <row r="12">
@@ -6082,34 +6082,34 @@
         <v>1987</v>
       </c>
       <c r="B12">
-        <v>1055377.576325869</v>
+        <v>9480.982063337453</v>
       </c>
       <c r="C12">
-        <v>1057830.520055088</v>
+        <v>1048913.09476875</v>
       </c>
       <c r="D12">
-        <v>985788.1908803172</v>
+        <v>970328.2595756293</v>
       </c>
       <c r="E12">
-        <v>971669.9164608979</v>
+        <v>956536.9455291743</v>
       </c>
       <c r="F12">
-        <v>865303.1804240661</v>
+        <v>853116.3872330948</v>
       </c>
       <c r="G12">
-        <v>965290.4435730698</v>
+        <v>954725.7378828551</v>
       </c>
       <c r="H12">
-        <v>969525.5734478108</v>
+        <v>959063.5451395351</v>
       </c>
       <c r="I12">
-        <v>852909.2587863802</v>
+        <v>840997.8654787907</v>
       </c>
       <c r="J12">
-        <v>841440.6899594511</v>
+        <v>833235.9231701028</v>
       </c>
       <c r="K12">
-        <v>844883.4946388074</v>
+        <v>836722.0980666531</v>
       </c>
     </row>
     <row r="13">
@@ -6117,34 +6117,34 @@
         <v>1988</v>
       </c>
       <c r="B13">
-        <v>1106064.560374558</v>
+        <v>1362490.875953541</v>
       </c>
       <c r="C13">
-        <v>1118950.802753006</v>
+        <v>1107777.014776315</v>
       </c>
       <c r="D13">
-        <v>1056263.62488602</v>
+        <v>1040274.103998267</v>
       </c>
       <c r="E13">
-        <v>1040668.777126369</v>
+        <v>1023920.06184398</v>
       </c>
       <c r="F13">
-        <v>927304.9884646139</v>
+        <v>915196.6429986646</v>
       </c>
       <c r="G13">
-        <v>1020684.37291691</v>
+        <v>1009718.095795308</v>
       </c>
       <c r="H13">
-        <v>1014612.430949728</v>
+        <v>1004003.634607904</v>
       </c>
       <c r="I13">
-        <v>913526.0814137519</v>
+        <v>900769.6034674544</v>
       </c>
       <c r="J13">
-        <v>886472.0874996006</v>
+        <v>877886.2190108342</v>
       </c>
       <c r="K13">
-        <v>881664.423568156</v>
+        <v>873338.5706805199</v>
       </c>
     </row>
     <row r="14">
@@ -6152,34 +6152,34 @@
         <v>1989</v>
       </c>
       <c r="B14">
-        <v>1040065.584001866</v>
+        <v>39980.48457381279</v>
       </c>
       <c r="C14">
-        <v>1031386.702961154</v>
+        <v>1033762.316725835</v>
       </c>
       <c r="D14">
-        <v>925115.5714808611</v>
+        <v>913848.1580891996</v>
       </c>
       <c r="E14">
-        <v>924022.3110907099</v>
+        <v>912720.5745984346</v>
       </c>
       <c r="F14">
-        <v>815810.1047695224</v>
+        <v>807648.2352477716</v>
       </c>
       <c r="G14">
-        <v>912764.9994947168</v>
+        <v>904766.5373201973</v>
       </c>
       <c r="H14">
-        <v>903702.8384092971</v>
+        <v>895894.855413672</v>
       </c>
       <c r="I14">
-        <v>815017.4693803196</v>
+        <v>806751.8001035845</v>
       </c>
       <c r="J14">
-        <v>805446.562354184</v>
+        <v>799549.5599401171</v>
       </c>
       <c r="K14">
-        <v>799374.0362236155</v>
+        <v>793610.4004550803</v>
       </c>
     </row>
     <row r="15">
@@ -6187,34 +6187,34 @@
         <v>1990</v>
       </c>
       <c r="B15">
-        <v>827559.4051862862</v>
+        <v>8917.68421083618</v>
       </c>
       <c r="C15">
-        <v>816071.9194701194</v>
+        <v>818543.0598113923</v>
       </c>
       <c r="D15">
-        <v>835465.9071772583</v>
+        <v>827255.8302504063</v>
       </c>
       <c r="E15">
-        <v>847655.3342829627</v>
+        <v>839817.3759635971</v>
       </c>
       <c r="F15">
-        <v>740334.5865077795</v>
+        <v>734798.7317384755</v>
       </c>
       <c r="G15">
-        <v>841654.2905293123</v>
+        <v>836012.1269160472</v>
       </c>
       <c r="H15">
-        <v>837256.2821747691</v>
+        <v>831535.4767025819</v>
       </c>
       <c r="I15">
-        <v>751594.0987355176</v>
+        <v>746277.3926870673</v>
       </c>
       <c r="J15">
-        <v>757886.1662868896</v>
+        <v>754096.158984306</v>
       </c>
       <c r="K15">
-        <v>752684.5476756908</v>
+        <v>748858.841320538</v>
       </c>
     </row>
     <row r="16">
@@ -6222,34 +6222,34 @@
         <v>1991</v>
       </c>
       <c r="B16">
-        <v>997424.6920651441</v>
+        <v>2485211.200970339</v>
       </c>
       <c r="C16">
-        <v>996373.2493916542</v>
+        <v>990398.0758564828</v>
       </c>
       <c r="D16">
-        <v>912006.5243848326</v>
+        <v>906561.3527491803</v>
       </c>
       <c r="E16">
-        <v>942399.3310389725</v>
+        <v>936367.1985667476</v>
       </c>
       <c r="F16">
-        <v>805501.4977770491</v>
+        <v>802549.036853664</v>
       </c>
       <c r="G16">
-        <v>920528.4647039227</v>
+        <v>916402.1147690249</v>
       </c>
       <c r="H16">
-        <v>915539.001329805</v>
+        <v>911342.6194524089</v>
       </c>
       <c r="I16">
-        <v>832825.9873179883</v>
+        <v>829356.0924688254</v>
       </c>
       <c r="J16">
-        <v>840014.3077919789</v>
+        <v>837117.5305275496</v>
       </c>
       <c r="K16">
-        <v>836287.6993163816</v>
+        <v>833348.939479564</v>
       </c>
     </row>
     <row r="17">
@@ -6257,34 +6257,34 @@
         <v>1992</v>
       </c>
       <c r="B17">
-        <v>961738.6176977737</v>
+        <v>638022.0665341264</v>
       </c>
       <c r="C17">
-        <v>939290.2883543206</v>
+        <v>935680.7123433327</v>
       </c>
       <c r="D17">
-        <v>913102.9586888021</v>
+        <v>912219.5423077065</v>
       </c>
       <c r="E17">
-        <v>952629.0990143124</v>
+        <v>951042.5280092835</v>
       </c>
       <c r="F17">
-        <v>803217.3914376685</v>
+        <v>803112.5214052807</v>
       </c>
       <c r="G17">
-        <v>899322.5417005122</v>
+        <v>897492.8334246047</v>
       </c>
       <c r="H17">
-        <v>890554.5343692324</v>
+        <v>888780.5560413152</v>
       </c>
       <c r="I17">
-        <v>839089.7590278975</v>
+        <v>838460.7322051084</v>
       </c>
       <c r="J17">
-        <v>824404.2056111573</v>
+        <v>823133.8245613975</v>
       </c>
       <c r="K17">
-        <v>818319.6355295469</v>
+        <v>817088.429573184</v>
       </c>
     </row>
     <row r="18">
@@ -6292,34 +6292,34 @@
         <v>1993</v>
       </c>
       <c r="B18">
-        <v>727633.3452602997</v>
+        <v>12128.35804561961</v>
       </c>
       <c r="C18">
-        <v>723811.0658767476</v>
+        <v>724012.6733295694</v>
       </c>
       <c r="D18">
-        <v>767720.2110049432</v>
+        <v>766693.8545773239</v>
       </c>
       <c r="E18">
-        <v>793110.9888532776</v>
+        <v>792784.6617070807</v>
       </c>
       <c r="F18">
-        <v>679643.2309651504</v>
+        <v>679046.1803651518</v>
       </c>
       <c r="G18">
-        <v>787024.4144185254</v>
+        <v>786058.9376365887</v>
       </c>
       <c r="H18">
-        <v>786448.8014289533</v>
+        <v>785399.5485522862</v>
       </c>
       <c r="I18">
-        <v>704123.904737439</v>
+        <v>704094.4388037914</v>
       </c>
       <c r="J18">
-        <v>722079.7095885773</v>
+        <v>721799.0537810285</v>
       </c>
       <c r="K18">
-        <v>721838.0419334044</v>
+        <v>721488.071118621</v>
       </c>
     </row>
     <row r="19">
@@ -6327,34 +6327,34 @@
         <v>1994</v>
       </c>
       <c r="B19">
-        <v>732954.2138904615</v>
+        <v>688939.050377063</v>
       </c>
       <c r="C19">
-        <v>730468.347347995</v>
+        <v>726868.5214491438</v>
       </c>
       <c r="D19">
-        <v>753038.6296270355</v>
+        <v>752198.7856848711</v>
       </c>
       <c r="E19">
-        <v>775070.4748630805</v>
+        <v>774954.040973987</v>
       </c>
       <c r="F19">
-        <v>670967.8225331504</v>
+        <v>670433.4900400536</v>
       </c>
       <c r="G19">
-        <v>769828.6370156278</v>
+        <v>769205.8661670417</v>
       </c>
       <c r="H19">
-        <v>771116.9312311891</v>
+        <v>770396.2676365277</v>
       </c>
       <c r="I19">
-        <v>692308.5243736538</v>
+        <v>692359.456983109</v>
       </c>
       <c r="J19">
-        <v>707044.4514928568</v>
+        <v>707004.9357839021</v>
       </c>
       <c r="K19">
-        <v>708311.9005935716</v>
+        <v>708203.5782182839</v>
       </c>
     </row>
     <row r="20">
@@ -6362,34 +6362,34 @@
         <v>1995</v>
       </c>
       <c r="B20">
-        <v>809796.1812723188</v>
+        <v>441989.6830836674</v>
       </c>
       <c r="C20">
-        <v>811932.8828583201</v>
+        <v>806670.4043713697</v>
       </c>
       <c r="D20">
-        <v>818392.2475926311</v>
+        <v>818314.2865574138</v>
       </c>
       <c r="E20">
-        <v>843159.5668612189</v>
+        <v>843120.9612227936</v>
       </c>
       <c r="F20">
-        <v>737285.0650847021</v>
+        <v>737240.1412888602</v>
       </c>
       <c r="G20">
-        <v>849863.6949900705</v>
+        <v>849510.8478110074</v>
       </c>
       <c r="H20">
-        <v>836106.6974734742</v>
+        <v>835733.4418870176</v>
       </c>
       <c r="I20">
-        <v>759587.5952173326</v>
+        <v>759574.3658006658</v>
       </c>
       <c r="J20">
-        <v>782349.1125758801</v>
+        <v>782084.8126826156</v>
       </c>
       <c r="K20">
-        <v>770986.9227132081</v>
+        <v>770753.7284860184</v>
       </c>
     </row>
     <row r="21">
@@ -6397,34 +6397,34 @@
         <v>1996</v>
       </c>
       <c r="B21">
-        <v>750515.1978848138</v>
+        <v>13439.70945306445</v>
       </c>
       <c r="C21">
-        <v>747177.4990212391</v>
+        <v>744554.5870808179</v>
       </c>
       <c r="D21">
-        <v>787194.505234795</v>
+        <v>786896.4447537332</v>
       </c>
       <c r="E21">
-        <v>804317.6995519499</v>
+        <v>804629.9445904042</v>
       </c>
       <c r="F21">
-        <v>722202.4833249882</v>
+        <v>721910.3819633124</v>
       </c>
       <c r="G21">
-        <v>799111.4676600005</v>
+        <v>798867.6697769156</v>
       </c>
       <c r="H21">
-        <v>801985.2782215232</v>
+        <v>801684.8781624587</v>
       </c>
       <c r="I21">
-        <v>736739.3891149675</v>
+        <v>736895.9656121765</v>
       </c>
       <c r="J21">
-        <v>738340.7206665809</v>
+        <v>738397.6663701488</v>
       </c>
       <c r="K21">
-        <v>740448.077349105</v>
+        <v>740450.9354833644</v>
       </c>
     </row>
     <row r="22">
@@ -6432,34 +6432,34 @@
         <v>1997</v>
       </c>
       <c r="B22">
-        <v>890368.2511621655</v>
+        <v>889131.4384555413</v>
       </c>
       <c r="C22">
-        <v>888650.8345938203</v>
+        <v>878695.5065149992</v>
       </c>
       <c r="D22">
-        <v>883471.3226251489</v>
+        <v>883236.0200162572</v>
       </c>
       <c r="E22">
-        <v>874607.5326161797</v>
+        <v>874897.5029137313</v>
       </c>
       <c r="F22">
-        <v>817252.3488171932</v>
+        <v>817005.8441608874</v>
       </c>
       <c r="G22">
-        <v>913887.6025402569</v>
+        <v>913635.7294133124</v>
       </c>
       <c r="H22">
-        <v>896284.8790125641</v>
+        <v>896003.5072917928</v>
       </c>
       <c r="I22">
-        <v>805622.0486014561</v>
+        <v>805683.0919327085</v>
       </c>
       <c r="J22">
-        <v>819349.2186457807</v>
+        <v>819153.4019122609</v>
       </c>
       <c r="K22">
-        <v>806013.7856682248</v>
+        <v>805855.6607685584</v>
       </c>
     </row>
     <row r="23">
@@ -6467,34 +6467,34 @@
         <v>1998</v>
       </c>
       <c r="B23">
-        <v>1221272.287707215</v>
+        <v>573280.8600229283</v>
       </c>
       <c r="C23">
-        <v>1220510.833868332</v>
+        <v>1210696.909285713</v>
       </c>
       <c r="D23">
-        <v>1149954.329702107</v>
+        <v>1150734.440908838</v>
       </c>
       <c r="E23">
-        <v>1073982.749540753</v>
+        <v>1073652.59485307</v>
       </c>
       <c r="F23">
-        <v>1033529.134973044</v>
+        <v>1034156.641110948</v>
       </c>
       <c r="G23">
-        <v>1120882.776009266</v>
+        <v>1120708.889321589</v>
       </c>
       <c r="H23">
-        <v>1123005.612978752</v>
+        <v>1122916.956181427</v>
       </c>
       <c r="I23">
-        <v>964092.9919689926</v>
+        <v>963752.0722038619</v>
       </c>
       <c r="J23">
-        <v>955047.972198106</v>
+        <v>954431.0893902914</v>
       </c>
       <c r="K23">
-        <v>956018.0779382843</v>
+        <v>955395.1415662095</v>
       </c>
     </row>
     <row r="24">
@@ -6502,34 +6502,34 @@
         <v>1999</v>
       </c>
       <c r="B24">
-        <v>1057955.766130074</v>
+        <v>11321.35318143287</v>
       </c>
       <c r="C24">
-        <v>1064029.599516423</v>
+        <v>1044773.524595793</v>
       </c>
       <c r="D24">
-        <v>1102732.659081487</v>
+        <v>1101943.777256862</v>
       </c>
       <c r="E24">
-        <v>1074185.851662026</v>
+        <v>1074279.549253928</v>
       </c>
       <c r="F24">
-        <v>986255.6155454299</v>
+        <v>985525.6126400896</v>
       </c>
       <c r="G24">
-        <v>1141592.716613676</v>
+        <v>1141499.846998258</v>
       </c>
       <c r="H24">
-        <v>1127601.461950746</v>
+        <v>1127552.827238235</v>
       </c>
       <c r="I24">
-        <v>963029.7680714683</v>
+        <v>962918.9900318705</v>
       </c>
       <c r="J24">
-        <v>991033.1876373584</v>
+        <v>990532.6687589471</v>
       </c>
       <c r="K24">
-        <v>977904.9651783159</v>
+        <v>977465.5708258958</v>
       </c>
     </row>
     <row r="25">
@@ -6537,34 +6537,34 @@
         <v>2000</v>
       </c>
       <c r="B25">
-        <v>2162765.865755301</v>
+        <v>2859260.232951426</v>
       </c>
       <c r="C25">
-        <v>2097570.883804205</v>
+        <v>2113699.980240742</v>
       </c>
       <c r="D25">
-        <v>1822942.842775583</v>
+        <v>1828992.45067004</v>
       </c>
       <c r="E25">
-        <v>1833022.594139485</v>
+        <v>1832994.876057447</v>
       </c>
       <c r="F25">
-        <v>1557320.336322657</v>
+        <v>1561688.014265495</v>
       </c>
       <c r="G25">
-        <v>1600153.686064799</v>
+        <v>1601094.543888378</v>
       </c>
       <c r="H25">
-        <v>1600024.006586145</v>
+        <v>1601300.722778036</v>
       </c>
       <c r="I25">
-        <v>1573188.112232541</v>
+        <v>1572875.001759013</v>
       </c>
       <c r="J25">
-        <v>1391666.143064165</v>
+        <v>1390007.310617868</v>
       </c>
       <c r="K25">
-        <v>1390202.921885924</v>
+        <v>1388680.543298784</v>
       </c>
     </row>
     <row r="26">
@@ -6572,34 +6572,34 @@
         <v>2001</v>
       </c>
       <c r="B26">
-        <v>843484.3435993973</v>
+        <v>9655.583388783729</v>
       </c>
       <c r="C26">
-        <v>842085.6110870413</v>
+        <v>833323.0500045202</v>
       </c>
       <c r="D26">
-        <v>919676.8118238322</v>
+        <v>918793.7213231487</v>
       </c>
       <c r="E26">
-        <v>929548.3542706938</v>
+        <v>929856.4908316705</v>
       </c>
       <c r="F26">
-        <v>802885.1611013472</v>
+        <v>801983.4051065061</v>
       </c>
       <c r="G26">
-        <v>960419.686193775</v>
+        <v>960380.140146495</v>
       </c>
       <c r="H26">
-        <v>960611.9959481186</v>
+        <v>960575.4475758079</v>
       </c>
       <c r="I26">
-        <v>813073.2860925888</v>
+        <v>813124.6259909043</v>
       </c>
       <c r="J26">
-        <v>847599.8329670093</v>
+        <v>847533.0659231483</v>
       </c>
       <c r="K26">
-        <v>849700.5786280051</v>
+        <v>849600.3777600904</v>
       </c>
     </row>
     <row r="27">
@@ -6607,34 +6607,34 @@
         <v>2002</v>
       </c>
       <c r="B27">
-        <v>921908.0250308808</v>
+        <v>1935235.061906548</v>
       </c>
       <c r="C27">
-        <v>902025.8464086915</v>
+        <v>896735.291244916</v>
       </c>
       <c r="D27">
-        <v>910171.1609550553</v>
+        <v>910271.7292940362</v>
       </c>
       <c r="E27">
-        <v>891414.0931799787</v>
+        <v>891626.4837194271</v>
       </c>
       <c r="F27">
-        <v>792627.616039867</v>
+        <v>792473.3575309558</v>
       </c>
       <c r="G27">
-        <v>908336.5581219624</v>
+        <v>908328.4542434813</v>
       </c>
       <c r="H27">
-        <v>908159.4123901847</v>
+        <v>908146.8718065062</v>
       </c>
       <c r="I27">
-        <v>777197.4535626476</v>
+        <v>777165.5667179537</v>
       </c>
       <c r="J27">
-        <v>779362.541423823</v>
+        <v>779318.7894589065</v>
       </c>
       <c r="K27">
-        <v>779168.1746666988</v>
+        <v>779114.1883413158</v>
       </c>
     </row>
     <row r="28">
@@ -6642,34 +6642,34 @@
         <v>2003</v>
       </c>
       <c r="B28">
-        <v>840087.2753160645</v>
+        <v>11928.12918932901</v>
       </c>
       <c r="C28">
-        <v>841107.9367481634</v>
+        <v>836374.2095162355</v>
       </c>
       <c r="D28">
-        <v>851910.0341783423</v>
+        <v>851785.2588967842</v>
       </c>
       <c r="E28">
-        <v>835149.0414327766</v>
+        <v>835373.7105614782</v>
       </c>
       <c r="F28">
-        <v>742566.9047295516</v>
+        <v>742249.172158755</v>
       </c>
       <c r="G28">
-        <v>888117.905433716</v>
+        <v>887983.9120745311</v>
       </c>
       <c r="H28">
-        <v>878044.5887681674</v>
+        <v>877925.9087143564</v>
       </c>
       <c r="I28">
-        <v>728652.913923631</v>
+        <v>728633.6824342287</v>
       </c>
       <c r="J28">
-        <v>757681.4765218371</v>
+        <v>757521.170850919</v>
       </c>
       <c r="K28">
-        <v>750211.8282668341</v>
+        <v>750082.5690744807</v>
       </c>
     </row>
     <row r="29">
@@ -6677,34 +6677,34 @@
         <v>2004</v>
       </c>
       <c r="B29">
-        <v>924113.3100813554</v>
+        <v>3053909.891370616</v>
       </c>
       <c r="C29">
-        <v>883900.7177104757</v>
+        <v>878520.2826277844</v>
       </c>
       <c r="D29">
-        <v>877974.9625166809</v>
+        <v>877735.344969761</v>
       </c>
       <c r="E29">
-        <v>883411.4048343698</v>
+        <v>883045.4405604703</v>
       </c>
       <c r="F29">
-        <v>764635.2513559358</v>
+        <v>764348.1022936584</v>
       </c>
       <c r="G29">
-        <v>854719.5240610155</v>
+        <v>854431.895705728</v>
       </c>
       <c r="H29">
-        <v>857868.8312107577</v>
+        <v>857584.5674760101</v>
       </c>
       <c r="I29">
-        <v>769681.2049074256</v>
+        <v>769299.3357829968</v>
       </c>
       <c r="J29">
-        <v>750308.8347313332</v>
+        <v>750045.9322790272</v>
       </c>
       <c r="K29">
-        <v>752981.5540735114</v>
+        <v>752692.3311199168</v>
       </c>
     </row>
     <row r="30">
@@ -6712,34 +6712,34 @@
         <v>2005</v>
       </c>
       <c r="B30">
-        <v>943795.2277700031</v>
+        <v>10918.51730718199</v>
       </c>
       <c r="C30">
-        <v>897777.3487054852</v>
+        <v>891740.6104015475</v>
       </c>
       <c r="D30">
-        <v>876058.267342825</v>
+        <v>875872.1513867246</v>
       </c>
       <c r="E30">
-        <v>900320.6089750333</v>
+        <v>899820.0243026061</v>
       </c>
       <c r="F30">
-        <v>762656.9720453562</v>
+        <v>762450.536928158</v>
       </c>
       <c r="G30">
-        <v>867662.4056403576</v>
+        <v>867301.9402568208</v>
       </c>
       <c r="H30">
-        <v>857691.9020772905</v>
+        <v>857368.8493349784</v>
       </c>
       <c r="I30">
-        <v>784022.2002069285</v>
+        <v>783561.7073190679</v>
       </c>
       <c r="J30">
-        <v>780409.8293057502</v>
+        <v>779899.7598959368</v>
       </c>
       <c r="K30">
-        <v>771418.2290568642</v>
+        <v>770969.7628677775</v>
       </c>
     </row>
     <row r="31">
@@ -6747,34 +6747,34 @@
         <v>2006</v>
       </c>
       <c r="B31">
-        <v>914611.1515397528</v>
+        <v>1829295.529845413</v>
       </c>
       <c r="C31">
-        <v>864858.3265795326</v>
+        <v>858279.0749166281</v>
       </c>
       <c r="D31">
-        <v>835539.3591457964</v>
+        <v>835324.9665351114</v>
       </c>
       <c r="E31">
-        <v>884679.7687972876</v>
+        <v>883858.2114817052</v>
       </c>
       <c r="F31">
-        <v>730611.5702827087</v>
+        <v>730457.7100534375</v>
       </c>
       <c r="G31">
-        <v>835278.3599022321</v>
+        <v>834889.835612891</v>
       </c>
       <c r="H31">
-        <v>841143.696786917</v>
+        <v>840788.1844998585</v>
       </c>
       <c r="I31">
-        <v>773206.5257107619</v>
+        <v>772562.0612185601</v>
       </c>
       <c r="J31">
-        <v>770182.7923848811</v>
+        <v>769586.2925521982</v>
       </c>
       <c r="K31">
-        <v>776005.437184789</v>
+        <v>775399.3625815266</v>
       </c>
     </row>
     <row r="32">
@@ -6782,34 +6782,34 @@
         <v>2007</v>
       </c>
       <c r="B32">
-        <v>619399.3787195022</v>
+        <v>10150.71610739861</v>
       </c>
       <c r="C32">
-        <v>590489.6510387339</v>
+        <v>590467.4814689101</v>
       </c>
       <c r="D32">
-        <v>625377.9634679946</v>
+        <v>624819.7651966356</v>
       </c>
       <c r="E32">
-        <v>675431.6829679803</v>
+        <v>675574.0177961517</v>
       </c>
       <c r="F32">
-        <v>550765.3246489601</v>
+        <v>550257.2001440148</v>
       </c>
       <c r="G32">
-        <v>640259.3401067323</v>
+        <v>640044.1699127903</v>
       </c>
       <c r="H32">
-        <v>638113.4156971587</v>
+        <v>637836.308176219</v>
       </c>
       <c r="I32">
-        <v>594519.1720090244</v>
+        <v>594571.5262439017</v>
       </c>
       <c r="J32">
-        <v>603027.3464100875</v>
+        <v>603162.5663969081</v>
       </c>
       <c r="K32">
-        <v>601124.3080072493</v>
+        <v>601234.2630397446</v>
       </c>
     </row>
     <row r="33">
@@ -6817,34 +6817,34 @@
         <v>2008</v>
       </c>
       <c r="B33">
-        <v>644171.7275632756</v>
+        <v>1180638.249153336</v>
       </c>
       <c r="C33">
-        <v>600919.0417754283</v>
+        <v>598132.4097496053</v>
       </c>
       <c r="D33">
-        <v>613098.8734707613</v>
+        <v>612659.9445127975</v>
       </c>
       <c r="E33">
-        <v>658535.2924434659</v>
+        <v>658341.2977599009</v>
       </c>
       <c r="F33">
-        <v>539117.368640599</v>
+        <v>538738.7639431423</v>
       </c>
       <c r="G33">
-        <v>633631.566385998</v>
+        <v>633398.3088605738</v>
       </c>
       <c r="H33">
-        <v>631695.2395223547</v>
+        <v>631413.9956477005</v>
       </c>
       <c r="I33">
-        <v>578623.2788080079</v>
+        <v>578471.5072602145</v>
       </c>
       <c r="J33">
-        <v>592896.0076016118</v>
+        <v>592902.240920658</v>
       </c>
       <c r="K33">
-        <v>592052.5731316567</v>
+        <v>592043.3840953726</v>
       </c>
     </row>
     <row r="34">
@@ -6852,34 +6852,34 @@
         <v>2009</v>
       </c>
       <c r="B34">
-        <v>469452.533549617</v>
+        <v>12549.31070143823</v>
       </c>
       <c r="C34">
-        <v>447397.7149075911</v>
+        <v>449444.9339561569</v>
       </c>
       <c r="D34">
-        <v>492646.9037233643</v>
+        <v>492122.259595481</v>
       </c>
       <c r="E34">
-        <v>509985.467525759</v>
+        <v>510491.171386064</v>
       </c>
       <c r="F34">
-        <v>435954.2888043239</v>
+        <v>435457.1016131666</v>
       </c>
       <c r="G34">
-        <v>533254.0960311708</v>
+        <v>533148.3214044456</v>
       </c>
       <c r="H34">
-        <v>529522.1223784345</v>
+        <v>529326.1295866632</v>
       </c>
       <c r="I34">
-        <v>451552.5496676348</v>
+        <v>451897.7269323862</v>
       </c>
       <c r="J34">
-        <v>485151.2405741951</v>
+        <v>485605.8297024131</v>
       </c>
       <c r="K34">
-        <v>482999.5794095679</v>
+        <v>483412.5728215014</v>
       </c>
     </row>
     <row r="35">
@@ -6887,34 +6887,34 @@
         <v>2010</v>
       </c>
       <c r="B35">
-        <v>460841.3530126021</v>
+        <v>594283.1622312244</v>
       </c>
       <c r="C35">
-        <v>437265.2968404989</v>
+        <v>439557.2647535812</v>
       </c>
       <c r="D35">
-        <v>484248.7870451087</v>
+        <v>483732.8759219245</v>
       </c>
       <c r="E35">
-        <v>476553.5392442295</v>
+        <v>477156.405715406</v>
       </c>
       <c r="F35">
-        <v>429841.372517664</v>
+        <v>429352.0761968055</v>
       </c>
       <c r="G35">
-        <v>514242.2831999339</v>
+        <v>514164.2765061012</v>
       </c>
       <c r="H35">
-        <v>513505.8354182811</v>
+        <v>513326.9310283003</v>
       </c>
       <c r="I35">
-        <v>423658.4001687376</v>
+        <v>424072.2751934156</v>
       </c>
       <c r="J35">
-        <v>449197.1868375277</v>
+        <v>449772.4381963438</v>
       </c>
       <c r="K35">
-        <v>449061.1859352351</v>
+        <v>449580.0967036641</v>
       </c>
     </row>
     <row r="36">
@@ -6922,34 +6922,34 @@
         <v>2011</v>
       </c>
       <c r="B36">
-        <v>614411.5592907257</v>
+        <v>216892.9470447438</v>
       </c>
       <c r="C36">
-        <v>572460.4075658174</v>
+        <v>569999.724879218</v>
       </c>
       <c r="D36">
-        <v>582298.4617497765</v>
+        <v>581907.587727649</v>
       </c>
       <c r="E36">
-        <v>555684.9722224884</v>
+        <v>555946.8088623217</v>
       </c>
       <c r="F36">
-        <v>514267.7776450799</v>
+        <v>513911.9109765532</v>
       </c>
       <c r="G36">
-        <v>612057.7502889388</v>
+        <v>611860.0574198035</v>
       </c>
       <c r="H36">
-        <v>607540.7226069537</v>
+        <v>607300.0834920343</v>
       </c>
       <c r="I36">
-        <v>492059.4246359341</v>
+        <v>492214.1686613454</v>
       </c>
       <c r="J36">
-        <v>519974.3298349709</v>
+        <v>520223.2685121669</v>
       </c>
       <c r="K36">
-        <v>516506.9614595235</v>
+        <v>516741.2871692137</v>
       </c>
     </row>
     <row r="37">
@@ -6957,34 +6957,34 @@
         <v>2012</v>
       </c>
       <c r="B37">
-        <v>695655.593159543</v>
+        <v>1347907.347258587</v>
       </c>
       <c r="C37">
-        <v>652066.0921679436</v>
+        <v>649429.8698189408</v>
       </c>
       <c r="D37">
-        <v>656132.1775205741</v>
+        <v>655748.2819906495</v>
       </c>
       <c r="E37">
-        <v>648024.5320761258</v>
+        <v>647890.9798313383</v>
       </c>
       <c r="F37">
-        <v>574083.9862042085</v>
+        <v>573755.2401605831</v>
       </c>
       <c r="G37">
-        <v>648451.8478476132</v>
+        <v>648184.3968323437</v>
       </c>
       <c r="H37">
-        <v>649617.5172032006</v>
+        <v>649315.8893438893</v>
       </c>
       <c r="I37">
-        <v>568877.7638058958</v>
+        <v>568760.8439020516</v>
       </c>
       <c r="J37">
-        <v>567301.8918126307</v>
+        <v>567371.2360333956</v>
       </c>
       <c r="K37">
-        <v>567721.1122591466</v>
+        <v>567757.8105652521</v>
       </c>
     </row>
     <row r="38">
@@ -6992,34 +6992,34 @@
         <v>2013</v>
       </c>
       <c r="B38">
-        <v>742670.0950666618</v>
+        <v>420727.9729077879</v>
       </c>
       <c r="C38">
-        <v>727087.0941490248</v>
+        <v>722287.39893346</v>
       </c>
       <c r="D38">
-        <v>713953.9313034834</v>
+        <v>713592.5419694337</v>
       </c>
       <c r="E38">
-        <v>721531.1126351382</v>
+        <v>720963.8423023807</v>
       </c>
       <c r="F38">
-        <v>626835.5802820614</v>
+        <v>626541.1810707416</v>
       </c>
       <c r="G38">
-        <v>730431.2597408859</v>
+        <v>730027.9289083586</v>
       </c>
       <c r="H38">
-        <v>726872.9889092104</v>
+        <v>726484.1428806746</v>
       </c>
       <c r="I38">
-        <v>635376.8184260166</v>
+        <v>634948.2076260806</v>
       </c>
       <c r="J38">
-        <v>651868.9818937167</v>
+        <v>651512.0632633485</v>
       </c>
       <c r="K38">
-        <v>648019.9333832494</v>
+        <v>647684.9538883507</v>
       </c>
     </row>
     <row r="39">
@@ -7027,34 +7027,34 @@
         <v>2014</v>
       </c>
       <c r="B39">
-        <v>545972.8202091842</v>
+        <v>1100788.056392994</v>
       </c>
       <c r="C39">
-        <v>583187.0595648569</v>
+        <v>581269.5693911695</v>
       </c>
       <c r="D39">
-        <v>612379.8475240294</v>
+        <v>611776.1715087662</v>
       </c>
       <c r="E39">
-        <v>608008.4561199724</v>
+        <v>608096.3089068661</v>
       </c>
       <c r="F39">
-        <v>553892.0324650056</v>
+        <v>553345.8733137406</v>
       </c>
       <c r="G39">
-        <v>633185.6653916533</v>
+        <v>632872.0832658574</v>
       </c>
       <c r="H39">
-        <v>633471.1442689997</v>
+        <v>633100.4083486652</v>
       </c>
       <c r="I39">
-        <v>550567.4273111586</v>
+        <v>550541.1656896611</v>
       </c>
       <c r="J39">
-        <v>567219.5066210459</v>
+        <v>567295.1610832044</v>
       </c>
       <c r="K39">
-        <v>567668.5474353894</v>
+        <v>567706.0133169318</v>
       </c>
     </row>
     <row r="40">
@@ -7062,34 +7062,34 @@
         <v>2015</v>
       </c>
       <c r="B40">
-        <v>525481.2159379956</v>
+        <v>27162.54812518814</v>
       </c>
       <c r="C40">
-        <v>603406.926389319</v>
+        <v>599691.787255625</v>
       </c>
       <c r="D40">
-        <v>622084.5220817773</v>
+        <v>621450.0646758971</v>
       </c>
       <c r="E40">
-        <v>610248.1491112586</v>
+        <v>610379.2543576112</v>
       </c>
       <c r="F40">
-        <v>569242.1795992949</v>
+        <v>568623.2559009275</v>
       </c>
       <c r="G40">
-        <v>658400.1629020597</v>
+        <v>658011.4350301599</v>
       </c>
       <c r="H40">
-        <v>649588.9012866777</v>
+        <v>649162.3462792565</v>
       </c>
       <c r="I40">
-        <v>557877.7298475323</v>
+        <v>557838.3594381481</v>
       </c>
       <c r="J40">
-        <v>588204.1395732759</v>
+        <v>588185.4531663494</v>
       </c>
       <c r="K40">
-        <v>581010.1415673428</v>
+        <v>580997.3087207219</v>
       </c>
     </row>
     <row r="41">
@@ -7097,34 +7097,34 @@
         <v>2016</v>
       </c>
       <c r="B41">
-        <v>599380.7240177552</v>
+        <v>571937.5646940027</v>
       </c>
       <c r="C41">
-        <v>755834.98923788</v>
+        <v>747303.6332482267</v>
       </c>
       <c r="D41">
-        <v>750800.2021532436</v>
+        <v>750068.1177883927</v>
       </c>
       <c r="E41">
-        <v>742677.4384215784</v>
+        <v>742075.1250018008</v>
       </c>
       <c r="F41">
-        <v>685079.4658860408</v>
+        <v>684401.0060834732</v>
       </c>
       <c r="G41">
-        <v>750251.3178260189</v>
+        <v>749595.830778865</v>
       </c>
       <c r="H41">
-        <v>748136.1490698991</v>
+        <v>747472.0740843259</v>
       </c>
       <c r="I41">
-        <v>676947.9264967263</v>
+        <v>676322.5884130081</v>
       </c>
       <c r="J41">
-        <v>679469.8066221754</v>
+        <v>678991.0317933315</v>
       </c>
       <c r="K41">
-        <v>676808.0408606656</v>
+        <v>676317.4048259903</v>
       </c>
     </row>
     <row r="42">
@@ -7132,34 +7132,34 @@
         <v>2017</v>
       </c>
       <c r="B42">
-        <v>658405.429190198</v>
+        <v>142186.8007456985</v>
       </c>
       <c r="C42">
-        <v>880788.3775130452</v>
+        <v>864674.5440910994</v>
       </c>
       <c r="D42">
-        <v>844118.909526949</v>
+        <v>843152.8203181756</v>
       </c>
       <c r="E42">
-        <v>877390.6378620641</v>
+        <v>876161.4726256349</v>
       </c>
       <c r="F42">
-        <v>771427.9913985695</v>
+        <v>770492.7649733039</v>
       </c>
       <c r="G42">
-        <v>848089.0950155349</v>
+        <v>847015.1886688469</v>
       </c>
       <c r="H42">
-        <v>838463.3207741057</v>
+        <v>837463.9416154604</v>
       </c>
       <c r="I42">
-        <v>801414.8150083758</v>
+        <v>800175.5919155403</v>
       </c>
       <c r="J42">
-        <v>800399.5743194459</v>
+        <v>799138.9649059715</v>
       </c>
       <c r="K42">
-        <v>790710.3227773898</v>
+        <v>789544.5456344809</v>
       </c>
     </row>
     <row r="43">
@@ -7167,34 +7167,34 @@
         <v>2018</v>
       </c>
       <c r="B43">
-        <v>757543.2788952539</v>
+        <v>250291.3975161435</v>
       </c>
       <c r="C43">
-        <v>886275.2177379505</v>
+        <v>863543.8999734322</v>
       </c>
       <c r="D43">
-        <v>863625.8897316613</v>
+        <v>861977.0827170764</v>
       </c>
       <c r="E43">
-        <v>929204.4699961104</v>
+        <v>926919.3386949244</v>
       </c>
       <c r="F43">
-        <v>779440.4572307202</v>
+        <v>777933.007297801</v>
       </c>
       <c r="G43">
-        <v>848354.7521613783</v>
+        <v>846886.9151512519</v>
       </c>
       <c r="H43">
-        <v>846952.6613433647</v>
+        <v>845524.8753813319</v>
       </c>
       <c r="I43">
-        <v>839663.6037897756</v>
+        <v>837607.5759093364</v>
       </c>
       <c r="J43">
-        <v>815153.6209311748</v>
+        <v>813487.0624853154</v>
       </c>
       <c r="K43">
-        <v>814216.4217619833</v>
+        <v>812577.5793463311</v>
       </c>
     </row>
     <row r="44">
@@ -7202,34 +7202,34 @@
         <v>2019</v>
       </c>
       <c r="B44">
-        <v>607371.4033129427</v>
+        <v>7810.209352344797</v>
       </c>
       <c r="C44">
-        <v>659894.0674735022</v>
+        <v>643027.2805452581</v>
       </c>
       <c r="D44">
-        <v>690898.5861037765</v>
+        <v>688961.347755671</v>
       </c>
       <c r="E44">
-        <v>732747.7506756919</v>
+        <v>731530.5574466146</v>
       </c>
       <c r="F44">
-        <v>624405.1042972073</v>
+        <v>622586.803734196</v>
       </c>
       <c r="G44">
-        <v>726442.0812285928</v>
+        <v>725023.9760322933</v>
       </c>
       <c r="H44">
-        <v>722917.2563931383</v>
+        <v>721484.2663138184</v>
       </c>
       <c r="I44">
-        <v>663263.7666468789</v>
+        <v>662006.5738354747</v>
       </c>
       <c r="J44">
-        <v>689716.3625860517</v>
+        <v>688654.2773147838</v>
       </c>
       <c r="K44">
-        <v>687258.8753613359</v>
+        <v>686208.5068604865</v>
       </c>
     </row>
     <row r="45">
@@ -7237,34 +7237,34 @@
         <v>2020</v>
       </c>
       <c r="B45">
-        <v>662290.7321375252</v>
+        <v>10045.69120707362</v>
       </c>
       <c r="C45">
-        <v>590465.9981243273</v>
+        <v>573014.9007957769</v>
       </c>
       <c r="D45">
-        <v>644401.6439953907</v>
+        <v>642045.3161431665</v>
       </c>
       <c r="E45">
-        <v>665749.2932153469</v>
+        <v>664514.8953875154</v>
       </c>
       <c r="F45">
-        <v>579419.0788069696</v>
+        <v>577280.8533283276</v>
       </c>
       <c r="G45">
-        <v>679427.473976257</v>
+        <v>677861.622337388</v>
       </c>
       <c r="H45">
-        <v>675048.1952028353</v>
+        <v>673425.1822164099</v>
       </c>
       <c r="I45">
-        <v>599681.5781598345</v>
+        <v>598453.4392422676</v>
       </c>
       <c r="J45">
-        <v>628392.08401567</v>
+        <v>627544.3120502173</v>
       </c>
       <c r="K45">
-        <v>625027.7204674558</v>
+        <v>624176.5103610429</v>
       </c>
     </row>
     <row r="46">
@@ -7272,34 +7272,34 @@
         <v>2021</v>
       </c>
       <c r="B46">
-        <v>682870.253485114</v>
+        <v>9580.538464600835</v>
       </c>
       <c r="C46">
-        <v>577209.8859458219</v>
+        <v>556380.0878659167</v>
       </c>
       <c r="D46">
-        <v>635738.2728699222</v>
+        <v>632999.7964328879</v>
       </c>
       <c r="E46">
-        <v>642389.3330772658</v>
+        <v>641119.4956198763</v>
       </c>
       <c r="F46">
-        <v>571558.7684272034</v>
+        <v>569102.7528947025</v>
       </c>
       <c r="G46">
-        <v>685597.3639808764</v>
+        <v>683721.9904641808</v>
       </c>
       <c r="H46">
-        <v>682024.0894633392</v>
+        <v>680099.5449055571</v>
       </c>
       <c r="I46">
-        <v>578688.5948402593</v>
+        <v>577411.5124307423</v>
       </c>
       <c r="J46">
-        <v>620295.6402874604</v>
+        <v>619357.542607488</v>
       </c>
       <c r="K46">
-        <v>617502.9479939488</v>
+        <v>616560.9706723116</v>
       </c>
     </row>
     <row r="47">
@@ -7307,34 +7307,34 @@
         <v>2022</v>
       </c>
       <c r="B47">
-        <v>682812.401837012</v>
+        <v>9345.03999263404</v>
       </c>
       <c r="C47">
-        <v>619906.7574358068</v>
+        <v>589797.5668788714</v>
       </c>
       <c r="D47">
-        <v>690176.864984879</v>
+        <v>686408.3295682982</v>
       </c>
       <c r="E47">
-        <v>688937.3184151435</v>
+        <v>686645.7127729971</v>
       </c>
       <c r="F47">
-        <v>617332.2351346025</v>
+        <v>614124.4663921475</v>
       </c>
       <c r="G47">
-        <v>731181.4093575744</v>
+        <v>728641.2468404047</v>
       </c>
       <c r="H47">
-        <v>727690.3752967871</v>
+        <v>725111.1463162591</v>
       </c>
       <c r="I47">
-        <v>617359.2940850477</v>
+        <v>615316.9691662642</v>
       </c>
       <c r="J47">
-        <v>652566.7229714891</v>
+        <v>651114.1322256065</v>
       </c>
       <c r="K47">
-        <v>649330.3348929016</v>
+        <v>647879.7912763291</v>
       </c>
     </row>
     <row r="48">
@@ -7342,34 +7342,34 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>682628.6758057827</v>
+        <v>9344.411229151197</v>
       </c>
       <c r="C48">
-        <v>622884.9962652557</v>
+        <v>589970.8509539057</v>
       </c>
       <c r="D48">
-        <v>714070.6034561738</v>
+        <v>709618.913339125</v>
       </c>
       <c r="E48">
-        <v>717743.6555850119</v>
+        <v>714646.1976369293</v>
       </c>
       <c r="F48">
-        <v>636421.1254027762</v>
+        <v>632746.4087296111</v>
       </c>
       <c r="G48">
-        <v>744091.0837970693</v>
+        <v>741200.6847902776</v>
       </c>
       <c r="H48">
-        <v>745112.8339425968</v>
+        <v>742164.4611458577</v>
       </c>
       <c r="I48">
-        <v>640574.8946063978</v>
+        <v>637967.2406203054</v>
       </c>
       <c r="J48">
-        <v>666449.2384629973</v>
+        <v>664700.1814689544</v>
       </c>
       <c r="K48">
-        <v>667107.8515300057</v>
+        <v>665321.6762609486</v>
       </c>
     </row>
     <row r="49">
@@ -7377,34 +7377,34 @@
         <v>2024</v>
       </c>
       <c r="B49">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C49">
-        <v>667848.6427872791</v>
+        <v>626126.8862596515</v>
       </c>
       <c r="D49">
-        <v>752876.7683792991</v>
+        <v>747911.5293809085</v>
       </c>
       <c r="E49">
-        <v>760487.2635565726</v>
+        <v>756522.7903800665</v>
       </c>
       <c r="F49">
-        <v>669914.6482584235</v>
+        <v>665880.9059786142</v>
       </c>
       <c r="G49">
-        <v>779498.6080186814</v>
+        <v>776197.1742926753</v>
       </c>
       <c r="H49">
-        <v>776855.0069926161</v>
+        <v>773567.719730446</v>
       </c>
       <c r="I49">
-        <v>677327.1684587302</v>
+        <v>674078.362973148</v>
       </c>
       <c r="J49">
-        <v>699377.1991295036</v>
+        <v>697133.4530090159</v>
       </c>
       <c r="K49">
-        <v>697102.4857624809</v>
+        <v>694881.997638127</v>
       </c>
     </row>
     <row r="50">
@@ -7412,34 +7412,34 @@
         <v>2025</v>
       </c>
       <c r="B50">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C50">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D50">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E50">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F50">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G50">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H50">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I50">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J50">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K50">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="51">
@@ -7447,34 +7447,34 @@
         <v>2026</v>
       </c>
       <c r="B51">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C51">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D51">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E51">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F51">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G51">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H51">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I51">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J51">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K51">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="52">
@@ -7482,34 +7482,34 @@
         <v>2027</v>
       </c>
       <c r="B52">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C52">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D52">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E52">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F52">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G52">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H52">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I52">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J52">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K52">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="53">
@@ -7517,34 +7517,34 @@
         <v>2028</v>
       </c>
       <c r="B53">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C53">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D53">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E53">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F53">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G53">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H53">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I53">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J53">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K53">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="54">
@@ -7552,34 +7552,34 @@
         <v>2029</v>
       </c>
       <c r="B54">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C54">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D54">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E54">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F54">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G54">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H54">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I54">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J54">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K54">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="55">
@@ -7587,34 +7587,34 @@
         <v>2030</v>
       </c>
       <c r="B55">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C55">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D55">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E55">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F55">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G55">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H55">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I55">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J55">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K55">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="56">
@@ -7622,34 +7622,34 @@
         <v>2031</v>
       </c>
       <c r="B56">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C56">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D56">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E56">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F56">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G56">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H56">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I56">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J56">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K56">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="57">
@@ -7657,34 +7657,34 @@
         <v>2032</v>
       </c>
       <c r="B57">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C57">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D57">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E57">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F57">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G57">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H57">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I57">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J57">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K57">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="58">
@@ -7692,34 +7692,34 @@
         <v>2033</v>
       </c>
       <c r="B58">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C58">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D58">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E58">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F58">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G58">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H58">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I58">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J58">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K58">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="59">
@@ -7727,34 +7727,34 @@
         <v>2034</v>
       </c>
       <c r="B59">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C59">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D59">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E59">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F59">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G59">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H59">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I59">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J59">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K59">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="60">
@@ -7762,34 +7762,34 @@
         <v>2035</v>
       </c>
       <c r="B60">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C60">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D60">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E60">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F60">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G60">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H60">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I60">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J60">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K60">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="61">
@@ -7797,34 +7797,34 @@
         <v>2036</v>
       </c>
       <c r="B61">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C61">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D61">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E61">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F61">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G61">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H61">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I61">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J61">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K61">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="62">
@@ -7832,34 +7832,34 @@
         <v>2037</v>
       </c>
       <c r="B62">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C62">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D62">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E62">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F62">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G62">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H62">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I62">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J62">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K62">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="63">
@@ -7867,34 +7867,34 @@
         <v>2038</v>
       </c>
       <c r="B63">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C63">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D63">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E63">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F63">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G63">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H63">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I63">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J63">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K63">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="64">
@@ -7902,34 +7902,34 @@
         <v>2039</v>
       </c>
       <c r="B64">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C64">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D64">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E64">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F64">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G64">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H64">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I64">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J64">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K64">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="65">
@@ -7937,34 +7937,34 @@
         <v>2040</v>
       </c>
       <c r="B65">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C65">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D65">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E65">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F65">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G65">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H65">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I65">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J65">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K65">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="66">
@@ -7972,34 +7972,34 @@
         <v>2041</v>
       </c>
       <c r="B66">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C66">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D66">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E66">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F66">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G66">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H66">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I66">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J66">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K66">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="67">
@@ -8007,34 +8007,34 @@
         <v>2042</v>
       </c>
       <c r="B67">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C67">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D67">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E67">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F67">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G67">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H67">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I67">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J67">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K67">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="68">
@@ -8042,34 +8042,34 @@
         <v>2043</v>
       </c>
       <c r="B68">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C68">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D68">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E68">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F68">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G68">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H68">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I68">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J68">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K68">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="69">
@@ -8077,34 +8077,34 @@
         <v>2044</v>
       </c>
       <c r="B69">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C69">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D69">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E69">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F69">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G69">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H69">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I69">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J69">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K69">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="70">
@@ -8112,34 +8112,34 @@
         <v>2045</v>
       </c>
       <c r="B70">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C70">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D70">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E70">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F70">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G70">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H70">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I70">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J70">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K70">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="71">
@@ -8147,34 +8147,34 @@
         <v>2046</v>
       </c>
       <c r="B71">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C71">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D71">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E71">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F71">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G71">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H71">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I71">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J71">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K71">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="72">
@@ -8182,34 +8182,34 @@
         <v>2047</v>
       </c>
       <c r="B72">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C72">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D72">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E72">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F72">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G72">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H72">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I72">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J72">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K72">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="73">
@@ -8217,34 +8217,34 @@
         <v>2048</v>
       </c>
       <c r="B73">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C73">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D73">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E73">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F73">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G73">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H73">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I73">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J73">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K73">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="74">
@@ -8252,34 +8252,34 @@
         <v>2049</v>
       </c>
       <c r="B74">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C74">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D74">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E74">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F74">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G74">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H74">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I74">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J74">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K74">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
     <row r="75">
@@ -8287,34 +8287,34 @@
         <v>2050</v>
       </c>
       <c r="B75">
-        <v>802343.9063816267</v>
+        <v>626529.829376575</v>
       </c>
       <c r="C75">
-        <v>797528.6728770635</v>
+        <v>781673.042554475</v>
       </c>
       <c r="D75">
-        <v>814287.9090062374</v>
+        <v>809935.1509088513</v>
       </c>
       <c r="E75">
-        <v>821692.5037897824</v>
+        <v>817795.4044078087</v>
       </c>
       <c r="F75">
-        <v>722235.156059145</v>
+        <v>718737.9568938208</v>
       </c>
       <c r="G75">
-        <v>822788.5366788681</v>
+        <v>819753.864239958</v>
       </c>
       <c r="H75">
-        <v>819603.9254347135</v>
+        <v>816596.8347468933</v>
       </c>
       <c r="I75">
-        <v>729393.6218078918</v>
+        <v>726252.6750678536</v>
       </c>
       <c r="J75">
-        <v>736598.6483209771</v>
+        <v>734369.3078027198</v>
       </c>
       <c r="K75">
-        <v>733924.7028967908</v>
+        <v>731723.9702678703</v>
       </c>
     </row>
   </sheetData>
